--- a/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Projections_COMPLETED.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Projections_COMPLETED.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4175" uniqueCount="1254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4415" uniqueCount="1254">
   <si>
     <t>Mode.Operation</t>
   </si>
@@ -18708,7 +18708,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH503"/>
+  <dimension ref="A1:AH551"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:34">
@@ -71020,6 +71020,4998 @@
         <v>0.95</v>
       </c>
       <c r="AH503">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="504" spans="1:34">
+      <c r="A504">
+        <v>1</v>
+      </c>
+      <c r="B504" t="s">
+        <v>750</v>
+      </c>
+      <c r="C504" t="s">
+        <v>925</v>
+      </c>
+      <c r="D504" t="s">
+        <v>395</v>
+      </c>
+      <c r="E504" t="s">
+        <v>534</v>
+      </c>
+      <c r="F504" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G504">
+        <v>1</v>
+      </c>
+      <c r="H504">
+        <v>1</v>
+      </c>
+      <c r="I504">
+        <v>1</v>
+      </c>
+      <c r="J504">
+        <v>1</v>
+      </c>
+      <c r="K504">
+        <v>1</v>
+      </c>
+      <c r="L504">
+        <v>1</v>
+      </c>
+      <c r="M504">
+        <v>1</v>
+      </c>
+      <c r="N504">
+        <v>1</v>
+      </c>
+      <c r="O504">
+        <v>1</v>
+      </c>
+      <c r="P504">
+        <v>1</v>
+      </c>
+      <c r="Q504">
+        <v>1</v>
+      </c>
+      <c r="R504">
+        <v>1</v>
+      </c>
+      <c r="S504">
+        <v>1</v>
+      </c>
+      <c r="T504">
+        <v>1</v>
+      </c>
+      <c r="U504">
+        <v>1</v>
+      </c>
+      <c r="V504">
+        <v>1</v>
+      </c>
+      <c r="W504">
+        <v>1</v>
+      </c>
+      <c r="X504">
+        <v>1</v>
+      </c>
+      <c r="Y504">
+        <v>1</v>
+      </c>
+      <c r="Z504">
+        <v>1</v>
+      </c>
+      <c r="AA504">
+        <v>1</v>
+      </c>
+      <c r="AB504">
+        <v>1</v>
+      </c>
+      <c r="AC504">
+        <v>1</v>
+      </c>
+      <c r="AD504">
+        <v>1</v>
+      </c>
+      <c r="AE504">
+        <v>1</v>
+      </c>
+      <c r="AF504">
+        <v>1</v>
+      </c>
+      <c r="AG504">
+        <v>1</v>
+      </c>
+      <c r="AH504">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505" spans="1:34">
+      <c r="A505">
+        <v>1</v>
+      </c>
+      <c r="B505" t="s">
+        <v>750</v>
+      </c>
+      <c r="C505" t="s">
+        <v>925</v>
+      </c>
+      <c r="D505" t="s">
+        <v>954</v>
+      </c>
+      <c r="E505" t="s">
+        <v>994</v>
+      </c>
+      <c r="F505" t="s">
+        <v>590</v>
+      </c>
+      <c r="G505">
+        <v>1</v>
+      </c>
+      <c r="H505">
+        <v>1</v>
+      </c>
+      <c r="I505">
+        <v>1</v>
+      </c>
+      <c r="J505">
+        <v>1</v>
+      </c>
+      <c r="K505">
+        <v>1</v>
+      </c>
+      <c r="L505">
+        <v>1</v>
+      </c>
+      <c r="M505">
+        <v>1</v>
+      </c>
+      <c r="N505">
+        <v>1</v>
+      </c>
+      <c r="O505">
+        <v>1</v>
+      </c>
+      <c r="P505">
+        <v>1</v>
+      </c>
+      <c r="Q505">
+        <v>1</v>
+      </c>
+      <c r="R505">
+        <v>1</v>
+      </c>
+      <c r="S505">
+        <v>1</v>
+      </c>
+      <c r="T505">
+        <v>1</v>
+      </c>
+      <c r="U505">
+        <v>1</v>
+      </c>
+      <c r="V505">
+        <v>1</v>
+      </c>
+      <c r="W505">
+        <v>1</v>
+      </c>
+      <c r="X505">
+        <v>1</v>
+      </c>
+      <c r="Y505">
+        <v>1</v>
+      </c>
+      <c r="Z505">
+        <v>1</v>
+      </c>
+      <c r="AA505">
+        <v>1</v>
+      </c>
+      <c r="AB505">
+        <v>1</v>
+      </c>
+      <c r="AC505">
+        <v>1</v>
+      </c>
+      <c r="AD505">
+        <v>1</v>
+      </c>
+      <c r="AE505">
+        <v>1</v>
+      </c>
+      <c r="AF505">
+        <v>1</v>
+      </c>
+      <c r="AG505">
+        <v>1</v>
+      </c>
+      <c r="AH505">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506" spans="1:34">
+      <c r="A506">
+        <v>1</v>
+      </c>
+      <c r="B506" t="s">
+        <v>751</v>
+      </c>
+      <c r="C506" t="s">
+        <v>926</v>
+      </c>
+      <c r="D506" t="s">
+        <v>328</v>
+      </c>
+      <c r="E506" t="s">
+        <v>467</v>
+      </c>
+      <c r="F506" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G506">
+        <v>2.3376</v>
+      </c>
+      <c r="H506">
+        <v>2.3376</v>
+      </c>
+      <c r="I506">
+        <v>2.3376</v>
+      </c>
+      <c r="J506">
+        <v>2.3376</v>
+      </c>
+      <c r="K506">
+        <v>2.3376</v>
+      </c>
+      <c r="L506">
+        <v>2.3376</v>
+      </c>
+      <c r="M506">
+        <v>2.3376</v>
+      </c>
+      <c r="N506">
+        <v>2.3376</v>
+      </c>
+      <c r="O506">
+        <v>2.3376</v>
+      </c>
+      <c r="P506">
+        <v>2.3376</v>
+      </c>
+      <c r="Q506">
+        <v>2.3376</v>
+      </c>
+      <c r="R506">
+        <v>2.3376</v>
+      </c>
+      <c r="S506">
+        <v>2.3376</v>
+      </c>
+      <c r="T506">
+        <v>2.3376</v>
+      </c>
+      <c r="U506">
+        <v>2.3376</v>
+      </c>
+      <c r="V506">
+        <v>2.3376</v>
+      </c>
+      <c r="W506">
+        <v>2.3376</v>
+      </c>
+      <c r="X506">
+        <v>2.3376</v>
+      </c>
+      <c r="Y506">
+        <v>2.3376</v>
+      </c>
+      <c r="Z506">
+        <v>2.3376</v>
+      </c>
+      <c r="AA506">
+        <v>2.3376</v>
+      </c>
+      <c r="AB506">
+        <v>2.3376</v>
+      </c>
+      <c r="AC506">
+        <v>2.3376</v>
+      </c>
+      <c r="AD506">
+        <v>2.3376</v>
+      </c>
+      <c r="AE506">
+        <v>2.3376</v>
+      </c>
+      <c r="AF506">
+        <v>2.3376</v>
+      </c>
+      <c r="AG506">
+        <v>2.3376</v>
+      </c>
+      <c r="AH506">
+        <v>2.3376</v>
+      </c>
+    </row>
+    <row r="507" spans="1:34">
+      <c r="A507">
+        <v>2</v>
+      </c>
+      <c r="B507" t="s">
+        <v>751</v>
+      </c>
+      <c r="C507" t="s">
+        <v>926</v>
+      </c>
+      <c r="D507" t="s">
+        <v>329</v>
+      </c>
+      <c r="E507" t="s">
+        <v>468</v>
+      </c>
+      <c r="F507" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G507">
+        <v>2.3376</v>
+      </c>
+      <c r="H507">
+        <v>2.3376</v>
+      </c>
+      <c r="I507">
+        <v>2.3376</v>
+      </c>
+      <c r="J507">
+        <v>2.3376</v>
+      </c>
+      <c r="K507">
+        <v>2.3376</v>
+      </c>
+      <c r="L507">
+        <v>2.3376</v>
+      </c>
+      <c r="M507">
+        <v>2.3376</v>
+      </c>
+      <c r="N507">
+        <v>2.3376</v>
+      </c>
+      <c r="O507">
+        <v>2.3376</v>
+      </c>
+      <c r="P507">
+        <v>2.3376</v>
+      </c>
+      <c r="Q507">
+        <v>2.3376</v>
+      </c>
+      <c r="R507">
+        <v>2.3376</v>
+      </c>
+      <c r="S507">
+        <v>2.3376</v>
+      </c>
+      <c r="T507">
+        <v>2.3376</v>
+      </c>
+      <c r="U507">
+        <v>2.3376</v>
+      </c>
+      <c r="V507">
+        <v>2.3376</v>
+      </c>
+      <c r="W507">
+        <v>2.3376</v>
+      </c>
+      <c r="X507">
+        <v>2.3376</v>
+      </c>
+      <c r="Y507">
+        <v>2.3376</v>
+      </c>
+      <c r="Z507">
+        <v>2.3376</v>
+      </c>
+      <c r="AA507">
+        <v>2.3376</v>
+      </c>
+      <c r="AB507">
+        <v>2.3376</v>
+      </c>
+      <c r="AC507">
+        <v>2.3376</v>
+      </c>
+      <c r="AD507">
+        <v>2.3376</v>
+      </c>
+      <c r="AE507">
+        <v>2.3376</v>
+      </c>
+      <c r="AF507">
+        <v>2.3376</v>
+      </c>
+      <c r="AG507">
+        <v>2.3376</v>
+      </c>
+      <c r="AH507">
+        <v>2.3376</v>
+      </c>
+    </row>
+    <row r="508" spans="1:34">
+      <c r="A508">
+        <v>1</v>
+      </c>
+      <c r="B508" t="s">
+        <v>751</v>
+      </c>
+      <c r="C508" t="s">
+        <v>926</v>
+      </c>
+      <c r="D508" t="s">
+        <v>941</v>
+      </c>
+      <c r="E508" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F508" t="s">
+        <v>590</v>
+      </c>
+      <c r="G508">
+        <v>1</v>
+      </c>
+      <c r="H508">
+        <v>1</v>
+      </c>
+      <c r="I508">
+        <v>1</v>
+      </c>
+      <c r="J508">
+        <v>1</v>
+      </c>
+      <c r="K508">
+        <v>1</v>
+      </c>
+      <c r="L508">
+        <v>1</v>
+      </c>
+      <c r="M508">
+        <v>1</v>
+      </c>
+      <c r="N508">
+        <v>1</v>
+      </c>
+      <c r="O508">
+        <v>1</v>
+      </c>
+      <c r="P508">
+        <v>1</v>
+      </c>
+      <c r="Q508">
+        <v>1</v>
+      </c>
+      <c r="R508">
+        <v>1</v>
+      </c>
+      <c r="S508">
+        <v>1</v>
+      </c>
+      <c r="T508">
+        <v>1</v>
+      </c>
+      <c r="U508">
+        <v>1</v>
+      </c>
+      <c r="V508">
+        <v>1</v>
+      </c>
+      <c r="W508">
+        <v>1</v>
+      </c>
+      <c r="X508">
+        <v>1</v>
+      </c>
+      <c r="Y508">
+        <v>1</v>
+      </c>
+      <c r="Z508">
+        <v>1</v>
+      </c>
+      <c r="AA508">
+        <v>1</v>
+      </c>
+      <c r="AB508">
+        <v>1</v>
+      </c>
+      <c r="AC508">
+        <v>1</v>
+      </c>
+      <c r="AD508">
+        <v>1</v>
+      </c>
+      <c r="AE508">
+        <v>1</v>
+      </c>
+      <c r="AF508">
+        <v>1</v>
+      </c>
+      <c r="AG508">
+        <v>1</v>
+      </c>
+      <c r="AH508">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="509" spans="1:34">
+      <c r="A509">
+        <v>2</v>
+      </c>
+      <c r="B509" t="s">
+        <v>751</v>
+      </c>
+      <c r="C509" t="s">
+        <v>926</v>
+      </c>
+      <c r="D509" t="s">
+        <v>941</v>
+      </c>
+      <c r="E509" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F509" t="s">
+        <v>590</v>
+      </c>
+      <c r="G509">
+        <v>1</v>
+      </c>
+      <c r="H509">
+        <v>1</v>
+      </c>
+      <c r="I509">
+        <v>1</v>
+      </c>
+      <c r="J509">
+        <v>1</v>
+      </c>
+      <c r="K509">
+        <v>1</v>
+      </c>
+      <c r="L509">
+        <v>1</v>
+      </c>
+      <c r="M509">
+        <v>1</v>
+      </c>
+      <c r="N509">
+        <v>1</v>
+      </c>
+      <c r="O509">
+        <v>1</v>
+      </c>
+      <c r="P509">
+        <v>1</v>
+      </c>
+      <c r="Q509">
+        <v>1</v>
+      </c>
+      <c r="R509">
+        <v>1</v>
+      </c>
+      <c r="S509">
+        <v>1</v>
+      </c>
+      <c r="T509">
+        <v>1</v>
+      </c>
+      <c r="U509">
+        <v>1</v>
+      </c>
+      <c r="V509">
+        <v>1</v>
+      </c>
+      <c r="W509">
+        <v>1</v>
+      </c>
+      <c r="X509">
+        <v>1</v>
+      </c>
+      <c r="Y509">
+        <v>1</v>
+      </c>
+      <c r="Z509">
+        <v>1</v>
+      </c>
+      <c r="AA509">
+        <v>1</v>
+      </c>
+      <c r="AB509">
+        <v>1</v>
+      </c>
+      <c r="AC509">
+        <v>1</v>
+      </c>
+      <c r="AD509">
+        <v>1</v>
+      </c>
+      <c r="AE509">
+        <v>1</v>
+      </c>
+      <c r="AF509">
+        <v>1</v>
+      </c>
+      <c r="AG509">
+        <v>1</v>
+      </c>
+      <c r="AH509">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="510" spans="1:34">
+      <c r="A510">
+        <v>1</v>
+      </c>
+      <c r="B510" t="s">
+        <v>752</v>
+      </c>
+      <c r="C510" t="s">
+        <v>927</v>
+      </c>
+      <c r="D510" t="s">
+        <v>328</v>
+      </c>
+      <c r="E510" t="s">
+        <v>467</v>
+      </c>
+      <c r="F510" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G510">
+        <v>2.3376</v>
+      </c>
+      <c r="H510">
+        <v>2.3376</v>
+      </c>
+      <c r="I510">
+        <v>2.3376</v>
+      </c>
+      <c r="J510">
+        <v>2.3376</v>
+      </c>
+      <c r="K510">
+        <v>2.3376</v>
+      </c>
+      <c r="L510">
+        <v>2.3376</v>
+      </c>
+      <c r="M510">
+        <v>2.3376</v>
+      </c>
+      <c r="N510">
+        <v>2.3376</v>
+      </c>
+      <c r="O510">
+        <v>2.3376</v>
+      </c>
+      <c r="P510">
+        <v>2.3376</v>
+      </c>
+      <c r="Q510">
+        <v>2.3376</v>
+      </c>
+      <c r="R510">
+        <v>2.3376</v>
+      </c>
+      <c r="S510">
+        <v>2.3376</v>
+      </c>
+      <c r="T510">
+        <v>2.3376</v>
+      </c>
+      <c r="U510">
+        <v>2.3376</v>
+      </c>
+      <c r="V510">
+        <v>2.3376</v>
+      </c>
+      <c r="W510">
+        <v>2.3376</v>
+      </c>
+      <c r="X510">
+        <v>2.3376</v>
+      </c>
+      <c r="Y510">
+        <v>2.3376</v>
+      </c>
+      <c r="Z510">
+        <v>2.3376</v>
+      </c>
+      <c r="AA510">
+        <v>2.3376</v>
+      </c>
+      <c r="AB510">
+        <v>2.3376</v>
+      </c>
+      <c r="AC510">
+        <v>2.3376</v>
+      </c>
+      <c r="AD510">
+        <v>2.3376</v>
+      </c>
+      <c r="AE510">
+        <v>2.3376</v>
+      </c>
+      <c r="AF510">
+        <v>2.3376</v>
+      </c>
+      <c r="AG510">
+        <v>2.3376</v>
+      </c>
+      <c r="AH510">
+        <v>2.3376</v>
+      </c>
+    </row>
+    <row r="511" spans="1:34">
+      <c r="A511">
+        <v>2</v>
+      </c>
+      <c r="B511" t="s">
+        <v>752</v>
+      </c>
+      <c r="C511" t="s">
+        <v>927</v>
+      </c>
+      <c r="D511" t="s">
+        <v>329</v>
+      </c>
+      <c r="E511" t="s">
+        <v>468</v>
+      </c>
+      <c r="F511" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G511">
+        <v>2.3376</v>
+      </c>
+      <c r="H511">
+        <v>2.3376</v>
+      </c>
+      <c r="I511">
+        <v>2.3376</v>
+      </c>
+      <c r="J511">
+        <v>2.3376</v>
+      </c>
+      <c r="K511">
+        <v>2.3376</v>
+      </c>
+      <c r="L511">
+        <v>2.3376</v>
+      </c>
+      <c r="M511">
+        <v>2.3376</v>
+      </c>
+      <c r="N511">
+        <v>2.3376</v>
+      </c>
+      <c r="O511">
+        <v>2.3376</v>
+      </c>
+      <c r="P511">
+        <v>2.3376</v>
+      </c>
+      <c r="Q511">
+        <v>2.3376</v>
+      </c>
+      <c r="R511">
+        <v>2.3376</v>
+      </c>
+      <c r="S511">
+        <v>2.3376</v>
+      </c>
+      <c r="T511">
+        <v>2.3376</v>
+      </c>
+      <c r="U511">
+        <v>2.3376</v>
+      </c>
+      <c r="V511">
+        <v>2.3376</v>
+      </c>
+      <c r="W511">
+        <v>2.3376</v>
+      </c>
+      <c r="X511">
+        <v>2.3376</v>
+      </c>
+      <c r="Y511">
+        <v>2.3376</v>
+      </c>
+      <c r="Z511">
+        <v>2.3376</v>
+      </c>
+      <c r="AA511">
+        <v>2.3376</v>
+      </c>
+      <c r="AB511">
+        <v>2.3376</v>
+      </c>
+      <c r="AC511">
+        <v>2.3376</v>
+      </c>
+      <c r="AD511">
+        <v>2.3376</v>
+      </c>
+      <c r="AE511">
+        <v>2.3376</v>
+      </c>
+      <c r="AF511">
+        <v>2.3376</v>
+      </c>
+      <c r="AG511">
+        <v>2.3376</v>
+      </c>
+      <c r="AH511">
+        <v>2.3376</v>
+      </c>
+    </row>
+    <row r="512" spans="1:34">
+      <c r="A512">
+        <v>1</v>
+      </c>
+      <c r="B512" t="s">
+        <v>752</v>
+      </c>
+      <c r="C512" t="s">
+        <v>927</v>
+      </c>
+      <c r="D512" t="s">
+        <v>949</v>
+      </c>
+      <c r="E512" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F512" t="s">
+        <v>590</v>
+      </c>
+      <c r="G512">
+        <v>1</v>
+      </c>
+      <c r="H512">
+        <v>1</v>
+      </c>
+      <c r="I512">
+        <v>1</v>
+      </c>
+      <c r="J512">
+        <v>1</v>
+      </c>
+      <c r="K512">
+        <v>1</v>
+      </c>
+      <c r="L512">
+        <v>1</v>
+      </c>
+      <c r="M512">
+        <v>1</v>
+      </c>
+      <c r="N512">
+        <v>1</v>
+      </c>
+      <c r="O512">
+        <v>1</v>
+      </c>
+      <c r="P512">
+        <v>1</v>
+      </c>
+      <c r="Q512">
+        <v>1</v>
+      </c>
+      <c r="R512">
+        <v>1</v>
+      </c>
+      <c r="S512">
+        <v>1</v>
+      </c>
+      <c r="T512">
+        <v>1</v>
+      </c>
+      <c r="U512">
+        <v>1</v>
+      </c>
+      <c r="V512">
+        <v>1</v>
+      </c>
+      <c r="W512">
+        <v>1</v>
+      </c>
+      <c r="X512">
+        <v>1</v>
+      </c>
+      <c r="Y512">
+        <v>1</v>
+      </c>
+      <c r="Z512">
+        <v>1</v>
+      </c>
+      <c r="AA512">
+        <v>1</v>
+      </c>
+      <c r="AB512">
+        <v>1</v>
+      </c>
+      <c r="AC512">
+        <v>1</v>
+      </c>
+      <c r="AD512">
+        <v>1</v>
+      </c>
+      <c r="AE512">
+        <v>1</v>
+      </c>
+      <c r="AF512">
+        <v>1</v>
+      </c>
+      <c r="AG512">
+        <v>1</v>
+      </c>
+      <c r="AH512">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="513" spans="1:34">
+      <c r="A513">
+        <v>2</v>
+      </c>
+      <c r="B513" t="s">
+        <v>752</v>
+      </c>
+      <c r="C513" t="s">
+        <v>927</v>
+      </c>
+      <c r="D513" t="s">
+        <v>949</v>
+      </c>
+      <c r="E513" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F513" t="s">
+        <v>590</v>
+      </c>
+      <c r="G513">
+        <v>1</v>
+      </c>
+      <c r="H513">
+        <v>1</v>
+      </c>
+      <c r="I513">
+        <v>1</v>
+      </c>
+      <c r="J513">
+        <v>1</v>
+      </c>
+      <c r="K513">
+        <v>1</v>
+      </c>
+      <c r="L513">
+        <v>1</v>
+      </c>
+      <c r="M513">
+        <v>1</v>
+      </c>
+      <c r="N513">
+        <v>1</v>
+      </c>
+      <c r="O513">
+        <v>1</v>
+      </c>
+      <c r="P513">
+        <v>1</v>
+      </c>
+      <c r="Q513">
+        <v>1</v>
+      </c>
+      <c r="R513">
+        <v>1</v>
+      </c>
+      <c r="S513">
+        <v>1</v>
+      </c>
+      <c r="T513">
+        <v>1</v>
+      </c>
+      <c r="U513">
+        <v>1</v>
+      </c>
+      <c r="V513">
+        <v>1</v>
+      </c>
+      <c r="W513">
+        <v>1</v>
+      </c>
+      <c r="X513">
+        <v>1</v>
+      </c>
+      <c r="Y513">
+        <v>1</v>
+      </c>
+      <c r="Z513">
+        <v>1</v>
+      </c>
+      <c r="AA513">
+        <v>1</v>
+      </c>
+      <c r="AB513">
+        <v>1</v>
+      </c>
+      <c r="AC513">
+        <v>1</v>
+      </c>
+      <c r="AD513">
+        <v>1</v>
+      </c>
+      <c r="AE513">
+        <v>1</v>
+      </c>
+      <c r="AF513">
+        <v>1</v>
+      </c>
+      <c r="AG513">
+        <v>1</v>
+      </c>
+      <c r="AH513">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="514" spans="1:34">
+      <c r="A514">
+        <v>1</v>
+      </c>
+      <c r="B514" t="s">
+        <v>753</v>
+      </c>
+      <c r="C514" t="s">
+        <v>928</v>
+      </c>
+      <c r="D514" t="s">
+        <v>333</v>
+      </c>
+      <c r="E514" t="s">
+        <v>472</v>
+      </c>
+      <c r="F514" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G514">
+        <v>2.8571</v>
+      </c>
+      <c r="H514">
+        <v>2.8571</v>
+      </c>
+      <c r="I514">
+        <v>2.8571</v>
+      </c>
+      <c r="J514">
+        <v>2.8571</v>
+      </c>
+      <c r="K514">
+        <v>2.8571</v>
+      </c>
+      <c r="L514">
+        <v>2.8571</v>
+      </c>
+      <c r="M514">
+        <v>2.8571</v>
+      </c>
+      <c r="N514">
+        <v>2.8571</v>
+      </c>
+      <c r="O514">
+        <v>2.8571</v>
+      </c>
+      <c r="P514">
+        <v>2.8571</v>
+      </c>
+      <c r="Q514">
+        <v>2.8571</v>
+      </c>
+      <c r="R514">
+        <v>2.8571</v>
+      </c>
+      <c r="S514">
+        <v>2.8571</v>
+      </c>
+      <c r="T514">
+        <v>2.8571</v>
+      </c>
+      <c r="U514">
+        <v>2.8571</v>
+      </c>
+      <c r="V514">
+        <v>2.8571</v>
+      </c>
+      <c r="W514">
+        <v>2.8571</v>
+      </c>
+      <c r="X514">
+        <v>2.8571</v>
+      </c>
+      <c r="Y514">
+        <v>2.8571</v>
+      </c>
+      <c r="Z514">
+        <v>2.8571</v>
+      </c>
+      <c r="AA514">
+        <v>2.8571</v>
+      </c>
+      <c r="AB514">
+        <v>2.8571</v>
+      </c>
+      <c r="AC514">
+        <v>2.8571</v>
+      </c>
+      <c r="AD514">
+        <v>2.8571</v>
+      </c>
+      <c r="AE514">
+        <v>2.8571</v>
+      </c>
+      <c r="AF514">
+        <v>2.8571</v>
+      </c>
+      <c r="AG514">
+        <v>2.8571</v>
+      </c>
+      <c r="AH514">
+        <v>2.8571</v>
+      </c>
+    </row>
+    <row r="515" spans="1:34">
+      <c r="A515">
+        <v>2</v>
+      </c>
+      <c r="B515" t="s">
+        <v>753</v>
+      </c>
+      <c r="C515" t="s">
+        <v>928</v>
+      </c>
+      <c r="D515" t="s">
+        <v>336</v>
+      </c>
+      <c r="E515" t="s">
+        <v>475</v>
+      </c>
+      <c r="F515" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G515">
+        <v>2.8571</v>
+      </c>
+      <c r="H515">
+        <v>2.8571</v>
+      </c>
+      <c r="I515">
+        <v>2.8571</v>
+      </c>
+      <c r="J515">
+        <v>2.8571</v>
+      </c>
+      <c r="K515">
+        <v>2.8571</v>
+      </c>
+      <c r="L515">
+        <v>2.8571</v>
+      </c>
+      <c r="M515">
+        <v>2.8571</v>
+      </c>
+      <c r="N515">
+        <v>2.8571</v>
+      </c>
+      <c r="O515">
+        <v>2.8571</v>
+      </c>
+      <c r="P515">
+        <v>2.8571</v>
+      </c>
+      <c r="Q515">
+        <v>2.8571</v>
+      </c>
+      <c r="R515">
+        <v>2.8571</v>
+      </c>
+      <c r="S515">
+        <v>2.8571</v>
+      </c>
+      <c r="T515">
+        <v>2.8571</v>
+      </c>
+      <c r="U515">
+        <v>2.8571</v>
+      </c>
+      <c r="V515">
+        <v>2.8571</v>
+      </c>
+      <c r="W515">
+        <v>2.8571</v>
+      </c>
+      <c r="X515">
+        <v>2.8571</v>
+      </c>
+      <c r="Y515">
+        <v>2.8571</v>
+      </c>
+      <c r="Z515">
+        <v>2.8571</v>
+      </c>
+      <c r="AA515">
+        <v>2.8571</v>
+      </c>
+      <c r="AB515">
+        <v>2.8571</v>
+      </c>
+      <c r="AC515">
+        <v>2.8571</v>
+      </c>
+      <c r="AD515">
+        <v>2.8571</v>
+      </c>
+      <c r="AE515">
+        <v>2.8571</v>
+      </c>
+      <c r="AF515">
+        <v>2.8571</v>
+      </c>
+      <c r="AG515">
+        <v>2.8571</v>
+      </c>
+      <c r="AH515">
+        <v>2.8571</v>
+      </c>
+    </row>
+    <row r="516" spans="1:34">
+      <c r="A516">
+        <v>1</v>
+      </c>
+      <c r="B516" t="s">
+        <v>753</v>
+      </c>
+      <c r="C516" t="s">
+        <v>928</v>
+      </c>
+      <c r="D516" t="s">
+        <v>949</v>
+      </c>
+      <c r="E516" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F516" t="s">
+        <v>590</v>
+      </c>
+      <c r="G516">
+        <v>1</v>
+      </c>
+      <c r="H516">
+        <v>1</v>
+      </c>
+      <c r="I516">
+        <v>1</v>
+      </c>
+      <c r="J516">
+        <v>1</v>
+      </c>
+      <c r="K516">
+        <v>1</v>
+      </c>
+      <c r="L516">
+        <v>1</v>
+      </c>
+      <c r="M516">
+        <v>1</v>
+      </c>
+      <c r="N516">
+        <v>1</v>
+      </c>
+      <c r="O516">
+        <v>1</v>
+      </c>
+      <c r="P516">
+        <v>1</v>
+      </c>
+      <c r="Q516">
+        <v>1</v>
+      </c>
+      <c r="R516">
+        <v>1</v>
+      </c>
+      <c r="S516">
+        <v>1</v>
+      </c>
+      <c r="T516">
+        <v>1</v>
+      </c>
+      <c r="U516">
+        <v>1</v>
+      </c>
+      <c r="V516">
+        <v>1</v>
+      </c>
+      <c r="W516">
+        <v>1</v>
+      </c>
+      <c r="X516">
+        <v>1</v>
+      </c>
+      <c r="Y516">
+        <v>1</v>
+      </c>
+      <c r="Z516">
+        <v>1</v>
+      </c>
+      <c r="AA516">
+        <v>1</v>
+      </c>
+      <c r="AB516">
+        <v>1</v>
+      </c>
+      <c r="AC516">
+        <v>1</v>
+      </c>
+      <c r="AD516">
+        <v>1</v>
+      </c>
+      <c r="AE516">
+        <v>1</v>
+      </c>
+      <c r="AF516">
+        <v>1</v>
+      </c>
+      <c r="AG516">
+        <v>1</v>
+      </c>
+      <c r="AH516">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517" spans="1:34">
+      <c r="A517">
+        <v>2</v>
+      </c>
+      <c r="B517" t="s">
+        <v>753</v>
+      </c>
+      <c r="C517" t="s">
+        <v>928</v>
+      </c>
+      <c r="D517" t="s">
+        <v>949</v>
+      </c>
+      <c r="E517" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F517" t="s">
+        <v>590</v>
+      </c>
+      <c r="G517">
+        <v>1</v>
+      </c>
+      <c r="H517">
+        <v>1</v>
+      </c>
+      <c r="I517">
+        <v>1</v>
+      </c>
+      <c r="J517">
+        <v>1</v>
+      </c>
+      <c r="K517">
+        <v>1</v>
+      </c>
+      <c r="L517">
+        <v>1</v>
+      </c>
+      <c r="M517">
+        <v>1</v>
+      </c>
+      <c r="N517">
+        <v>1</v>
+      </c>
+      <c r="O517">
+        <v>1</v>
+      </c>
+      <c r="P517">
+        <v>1</v>
+      </c>
+      <c r="Q517">
+        <v>1</v>
+      </c>
+      <c r="R517">
+        <v>1</v>
+      </c>
+      <c r="S517">
+        <v>1</v>
+      </c>
+      <c r="T517">
+        <v>1</v>
+      </c>
+      <c r="U517">
+        <v>1</v>
+      </c>
+      <c r="V517">
+        <v>1</v>
+      </c>
+      <c r="W517">
+        <v>1</v>
+      </c>
+      <c r="X517">
+        <v>1</v>
+      </c>
+      <c r="Y517">
+        <v>1</v>
+      </c>
+      <c r="Z517">
+        <v>1</v>
+      </c>
+      <c r="AA517">
+        <v>1</v>
+      </c>
+      <c r="AB517">
+        <v>1</v>
+      </c>
+      <c r="AC517">
+        <v>1</v>
+      </c>
+      <c r="AD517">
+        <v>1</v>
+      </c>
+      <c r="AE517">
+        <v>1</v>
+      </c>
+      <c r="AF517">
+        <v>1</v>
+      </c>
+      <c r="AG517">
+        <v>1</v>
+      </c>
+      <c r="AH517">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518" spans="1:34">
+      <c r="A518">
+        <v>1</v>
+      </c>
+      <c r="B518" t="s">
+        <v>754</v>
+      </c>
+      <c r="C518" t="s">
+        <v>929</v>
+      </c>
+      <c r="D518" t="s">
+        <v>333</v>
+      </c>
+      <c r="E518" t="s">
+        <v>472</v>
+      </c>
+      <c r="F518" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G518">
+        <v>2.88</v>
+      </c>
+      <c r="H518">
+        <v>2.88</v>
+      </c>
+      <c r="I518">
+        <v>2.88</v>
+      </c>
+      <c r="J518">
+        <v>2.88</v>
+      </c>
+      <c r="K518">
+        <v>2.88</v>
+      </c>
+      <c r="L518">
+        <v>2.88</v>
+      </c>
+      <c r="M518">
+        <v>2.88</v>
+      </c>
+      <c r="N518">
+        <v>2.88</v>
+      </c>
+      <c r="O518">
+        <v>2.88</v>
+      </c>
+      <c r="P518">
+        <v>2.88</v>
+      </c>
+      <c r="Q518">
+        <v>2.88</v>
+      </c>
+      <c r="R518">
+        <v>2.88</v>
+      </c>
+      <c r="S518">
+        <v>2.88</v>
+      </c>
+      <c r="T518">
+        <v>2.88</v>
+      </c>
+      <c r="U518">
+        <v>2.88</v>
+      </c>
+      <c r="V518">
+        <v>2.88</v>
+      </c>
+      <c r="W518">
+        <v>2.88</v>
+      </c>
+      <c r="X518">
+        <v>2.88</v>
+      </c>
+      <c r="Y518">
+        <v>2.88</v>
+      </c>
+      <c r="Z518">
+        <v>2.88</v>
+      </c>
+      <c r="AA518">
+        <v>2.88</v>
+      </c>
+      <c r="AB518">
+        <v>2.88</v>
+      </c>
+      <c r="AC518">
+        <v>2.88</v>
+      </c>
+      <c r="AD518">
+        <v>2.88</v>
+      </c>
+      <c r="AE518">
+        <v>2.88</v>
+      </c>
+      <c r="AF518">
+        <v>2.88</v>
+      </c>
+      <c r="AG518">
+        <v>2.88</v>
+      </c>
+      <c r="AH518">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="519" spans="1:34">
+      <c r="A519">
+        <v>2</v>
+      </c>
+      <c r="B519" t="s">
+        <v>754</v>
+      </c>
+      <c r="C519" t="s">
+        <v>929</v>
+      </c>
+      <c r="D519" t="s">
+        <v>336</v>
+      </c>
+      <c r="E519" t="s">
+        <v>475</v>
+      </c>
+      <c r="F519" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G519">
+        <v>2.88</v>
+      </c>
+      <c r="H519">
+        <v>2.88</v>
+      </c>
+      <c r="I519">
+        <v>2.88</v>
+      </c>
+      <c r="J519">
+        <v>2.88</v>
+      </c>
+      <c r="K519">
+        <v>2.88</v>
+      </c>
+      <c r="L519">
+        <v>2.88</v>
+      </c>
+      <c r="M519">
+        <v>2.88</v>
+      </c>
+      <c r="N519">
+        <v>2.88</v>
+      </c>
+      <c r="O519">
+        <v>2.88</v>
+      </c>
+      <c r="P519">
+        <v>2.88</v>
+      </c>
+      <c r="Q519">
+        <v>2.88</v>
+      </c>
+      <c r="R519">
+        <v>2.88</v>
+      </c>
+      <c r="S519">
+        <v>2.88</v>
+      </c>
+      <c r="T519">
+        <v>2.88</v>
+      </c>
+      <c r="U519">
+        <v>2.88</v>
+      </c>
+      <c r="V519">
+        <v>2.88</v>
+      </c>
+      <c r="W519">
+        <v>2.88</v>
+      </c>
+      <c r="X519">
+        <v>2.88</v>
+      </c>
+      <c r="Y519">
+        <v>2.88</v>
+      </c>
+      <c r="Z519">
+        <v>2.88</v>
+      </c>
+      <c r="AA519">
+        <v>2.88</v>
+      </c>
+      <c r="AB519">
+        <v>2.88</v>
+      </c>
+      <c r="AC519">
+        <v>2.88</v>
+      </c>
+      <c r="AD519">
+        <v>2.88</v>
+      </c>
+      <c r="AE519">
+        <v>2.88</v>
+      </c>
+      <c r="AF519">
+        <v>2.88</v>
+      </c>
+      <c r="AG519">
+        <v>2.88</v>
+      </c>
+      <c r="AH519">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="520" spans="1:34">
+      <c r="A520">
+        <v>1</v>
+      </c>
+      <c r="B520" t="s">
+        <v>754</v>
+      </c>
+      <c r="C520" t="s">
+        <v>929</v>
+      </c>
+      <c r="D520" t="s">
+        <v>950</v>
+      </c>
+      <c r="E520" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F520" t="s">
+        <v>590</v>
+      </c>
+      <c r="G520">
+        <v>1</v>
+      </c>
+      <c r="H520">
+        <v>1</v>
+      </c>
+      <c r="I520">
+        <v>1</v>
+      </c>
+      <c r="J520">
+        <v>1</v>
+      </c>
+      <c r="K520">
+        <v>1</v>
+      </c>
+      <c r="L520">
+        <v>1</v>
+      </c>
+      <c r="M520">
+        <v>1</v>
+      </c>
+      <c r="N520">
+        <v>1</v>
+      </c>
+      <c r="O520">
+        <v>1</v>
+      </c>
+      <c r="P520">
+        <v>1</v>
+      </c>
+      <c r="Q520">
+        <v>1</v>
+      </c>
+      <c r="R520">
+        <v>1</v>
+      </c>
+      <c r="S520">
+        <v>1</v>
+      </c>
+      <c r="T520">
+        <v>1</v>
+      </c>
+      <c r="U520">
+        <v>1</v>
+      </c>
+      <c r="V520">
+        <v>1</v>
+      </c>
+      <c r="W520">
+        <v>1</v>
+      </c>
+      <c r="X520">
+        <v>1</v>
+      </c>
+      <c r="Y520">
+        <v>1</v>
+      </c>
+      <c r="Z520">
+        <v>1</v>
+      </c>
+      <c r="AA520">
+        <v>1</v>
+      </c>
+      <c r="AB520">
+        <v>1</v>
+      </c>
+      <c r="AC520">
+        <v>1</v>
+      </c>
+      <c r="AD520">
+        <v>1</v>
+      </c>
+      <c r="AE520">
+        <v>1</v>
+      </c>
+      <c r="AF520">
+        <v>1</v>
+      </c>
+      <c r="AG520">
+        <v>1</v>
+      </c>
+      <c r="AH520">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="521" spans="1:34">
+      <c r="A521">
+        <v>2</v>
+      </c>
+      <c r="B521" t="s">
+        <v>754</v>
+      </c>
+      <c r="C521" t="s">
+        <v>929</v>
+      </c>
+      <c r="D521" t="s">
+        <v>950</v>
+      </c>
+      <c r="E521" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F521" t="s">
+        <v>590</v>
+      </c>
+      <c r="G521">
+        <v>1</v>
+      </c>
+      <c r="H521">
+        <v>1</v>
+      </c>
+      <c r="I521">
+        <v>1</v>
+      </c>
+      <c r="J521">
+        <v>1</v>
+      </c>
+      <c r="K521">
+        <v>1</v>
+      </c>
+      <c r="L521">
+        <v>1</v>
+      </c>
+      <c r="M521">
+        <v>1</v>
+      </c>
+      <c r="N521">
+        <v>1</v>
+      </c>
+      <c r="O521">
+        <v>1</v>
+      </c>
+      <c r="P521">
+        <v>1</v>
+      </c>
+      <c r="Q521">
+        <v>1</v>
+      </c>
+      <c r="R521">
+        <v>1</v>
+      </c>
+      <c r="S521">
+        <v>1</v>
+      </c>
+      <c r="T521">
+        <v>1</v>
+      </c>
+      <c r="U521">
+        <v>1</v>
+      </c>
+      <c r="V521">
+        <v>1</v>
+      </c>
+      <c r="W521">
+        <v>1</v>
+      </c>
+      <c r="X521">
+        <v>1</v>
+      </c>
+      <c r="Y521">
+        <v>1</v>
+      </c>
+      <c r="Z521">
+        <v>1</v>
+      </c>
+      <c r="AA521">
+        <v>1</v>
+      </c>
+      <c r="AB521">
+        <v>1</v>
+      </c>
+      <c r="AC521">
+        <v>1</v>
+      </c>
+      <c r="AD521">
+        <v>1</v>
+      </c>
+      <c r="AE521">
+        <v>1</v>
+      </c>
+      <c r="AF521">
+        <v>1</v>
+      </c>
+      <c r="AG521">
+        <v>1</v>
+      </c>
+      <c r="AH521">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="522" spans="1:34">
+      <c r="A522">
+        <v>1</v>
+      </c>
+      <c r="B522" t="s">
+        <v>755</v>
+      </c>
+      <c r="C522" t="s">
+        <v>930</v>
+      </c>
+      <c r="D522" t="s">
+        <v>393</v>
+      </c>
+      <c r="E522" t="s">
+        <v>532</v>
+      </c>
+      <c r="F522" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G522">
+        <v>1</v>
+      </c>
+      <c r="H522">
+        <v>1</v>
+      </c>
+      <c r="I522">
+        <v>1</v>
+      </c>
+      <c r="J522">
+        <v>1</v>
+      </c>
+      <c r="K522">
+        <v>1</v>
+      </c>
+      <c r="L522">
+        <v>1</v>
+      </c>
+      <c r="M522">
+        <v>1</v>
+      </c>
+      <c r="N522">
+        <v>1</v>
+      </c>
+      <c r="O522">
+        <v>1</v>
+      </c>
+      <c r="P522">
+        <v>1</v>
+      </c>
+      <c r="Q522">
+        <v>1</v>
+      </c>
+      <c r="R522">
+        <v>1</v>
+      </c>
+      <c r="S522">
+        <v>1</v>
+      </c>
+      <c r="T522">
+        <v>1</v>
+      </c>
+      <c r="U522">
+        <v>1</v>
+      </c>
+      <c r="V522">
+        <v>1</v>
+      </c>
+      <c r="W522">
+        <v>1</v>
+      </c>
+      <c r="X522">
+        <v>1</v>
+      </c>
+      <c r="Y522">
+        <v>1</v>
+      </c>
+      <c r="Z522">
+        <v>1</v>
+      </c>
+      <c r="AA522">
+        <v>1</v>
+      </c>
+      <c r="AB522">
+        <v>1</v>
+      </c>
+      <c r="AC522">
+        <v>1</v>
+      </c>
+      <c r="AD522">
+        <v>1</v>
+      </c>
+      <c r="AE522">
+        <v>1</v>
+      </c>
+      <c r="AF522">
+        <v>1</v>
+      </c>
+      <c r="AG522">
+        <v>1</v>
+      </c>
+      <c r="AH522">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523" spans="1:34">
+      <c r="A523">
+        <v>1</v>
+      </c>
+      <c r="B523" t="s">
+        <v>755</v>
+      </c>
+      <c r="C523" t="s">
+        <v>930</v>
+      </c>
+      <c r="D523" t="s">
+        <v>952</v>
+      </c>
+      <c r="E523" t="s">
+        <v>992</v>
+      </c>
+      <c r="F523" t="s">
+        <v>590</v>
+      </c>
+      <c r="G523">
+        <v>1</v>
+      </c>
+      <c r="H523">
+        <v>1</v>
+      </c>
+      <c r="I523">
+        <v>1</v>
+      </c>
+      <c r="J523">
+        <v>1</v>
+      </c>
+      <c r="K523">
+        <v>1</v>
+      </c>
+      <c r="L523">
+        <v>1</v>
+      </c>
+      <c r="M523">
+        <v>1</v>
+      </c>
+      <c r="N523">
+        <v>1</v>
+      </c>
+      <c r="O523">
+        <v>1</v>
+      </c>
+      <c r="P523">
+        <v>1</v>
+      </c>
+      <c r="Q523">
+        <v>1</v>
+      </c>
+      <c r="R523">
+        <v>1</v>
+      </c>
+      <c r="S523">
+        <v>1</v>
+      </c>
+      <c r="T523">
+        <v>1</v>
+      </c>
+      <c r="U523">
+        <v>1</v>
+      </c>
+      <c r="V523">
+        <v>1</v>
+      </c>
+      <c r="W523">
+        <v>1</v>
+      </c>
+      <c r="X523">
+        <v>1</v>
+      </c>
+      <c r="Y523">
+        <v>1</v>
+      </c>
+      <c r="Z523">
+        <v>1</v>
+      </c>
+      <c r="AA523">
+        <v>1</v>
+      </c>
+      <c r="AB523">
+        <v>1</v>
+      </c>
+      <c r="AC523">
+        <v>1</v>
+      </c>
+      <c r="AD523">
+        <v>1</v>
+      </c>
+      <c r="AE523">
+        <v>1</v>
+      </c>
+      <c r="AF523">
+        <v>1</v>
+      </c>
+      <c r="AG523">
+        <v>1</v>
+      </c>
+      <c r="AH523">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="524" spans="1:34">
+      <c r="A524">
+        <v>1</v>
+      </c>
+      <c r="B524" t="s">
+        <v>756</v>
+      </c>
+      <c r="C524" t="s">
+        <v>931</v>
+      </c>
+      <c r="D524" t="s">
+        <v>394</v>
+      </c>
+      <c r="E524" t="s">
+        <v>533</v>
+      </c>
+      <c r="F524" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G524">
+        <v>1</v>
+      </c>
+      <c r="H524">
+        <v>1</v>
+      </c>
+      <c r="I524">
+        <v>1</v>
+      </c>
+      <c r="J524">
+        <v>1</v>
+      </c>
+      <c r="K524">
+        <v>1</v>
+      </c>
+      <c r="L524">
+        <v>1</v>
+      </c>
+      <c r="M524">
+        <v>1</v>
+      </c>
+      <c r="N524">
+        <v>1</v>
+      </c>
+      <c r="O524">
+        <v>1</v>
+      </c>
+      <c r="P524">
+        <v>1</v>
+      </c>
+      <c r="Q524">
+        <v>1</v>
+      </c>
+      <c r="R524">
+        <v>1</v>
+      </c>
+      <c r="S524">
+        <v>1</v>
+      </c>
+      <c r="T524">
+        <v>1</v>
+      </c>
+      <c r="U524">
+        <v>1</v>
+      </c>
+      <c r="V524">
+        <v>1</v>
+      </c>
+      <c r="W524">
+        <v>1</v>
+      </c>
+      <c r="X524">
+        <v>1</v>
+      </c>
+      <c r="Y524">
+        <v>1</v>
+      </c>
+      <c r="Z524">
+        <v>1</v>
+      </c>
+      <c r="AA524">
+        <v>1</v>
+      </c>
+      <c r="AB524">
+        <v>1</v>
+      </c>
+      <c r="AC524">
+        <v>1</v>
+      </c>
+      <c r="AD524">
+        <v>1</v>
+      </c>
+      <c r="AE524">
+        <v>1</v>
+      </c>
+      <c r="AF524">
+        <v>1</v>
+      </c>
+      <c r="AG524">
+        <v>1</v>
+      </c>
+      <c r="AH524">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="525" spans="1:34">
+      <c r="A525">
+        <v>1</v>
+      </c>
+      <c r="B525" t="s">
+        <v>756</v>
+      </c>
+      <c r="C525" t="s">
+        <v>931</v>
+      </c>
+      <c r="D525" t="s">
+        <v>953</v>
+      </c>
+      <c r="E525" t="s">
+        <v>993</v>
+      </c>
+      <c r="F525" t="s">
+        <v>590</v>
+      </c>
+      <c r="G525">
+        <v>1</v>
+      </c>
+      <c r="H525">
+        <v>1</v>
+      </c>
+      <c r="I525">
+        <v>1</v>
+      </c>
+      <c r="J525">
+        <v>1</v>
+      </c>
+      <c r="K525">
+        <v>1</v>
+      </c>
+      <c r="L525">
+        <v>1</v>
+      </c>
+      <c r="M525">
+        <v>1</v>
+      </c>
+      <c r="N525">
+        <v>1</v>
+      </c>
+      <c r="O525">
+        <v>1</v>
+      </c>
+      <c r="P525">
+        <v>1</v>
+      </c>
+      <c r="Q525">
+        <v>1</v>
+      </c>
+      <c r="R525">
+        <v>1</v>
+      </c>
+      <c r="S525">
+        <v>1</v>
+      </c>
+      <c r="T525">
+        <v>1</v>
+      </c>
+      <c r="U525">
+        <v>1</v>
+      </c>
+      <c r="V525">
+        <v>1</v>
+      </c>
+      <c r="W525">
+        <v>1</v>
+      </c>
+      <c r="X525">
+        <v>1</v>
+      </c>
+      <c r="Y525">
+        <v>1</v>
+      </c>
+      <c r="Z525">
+        <v>1</v>
+      </c>
+      <c r="AA525">
+        <v>1</v>
+      </c>
+      <c r="AB525">
+        <v>1</v>
+      </c>
+      <c r="AC525">
+        <v>1</v>
+      </c>
+      <c r="AD525">
+        <v>1</v>
+      </c>
+      <c r="AE525">
+        <v>1</v>
+      </c>
+      <c r="AF525">
+        <v>1</v>
+      </c>
+      <c r="AG525">
+        <v>1</v>
+      </c>
+      <c r="AH525">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526" spans="1:34">
+      <c r="A526">
+        <v>1</v>
+      </c>
+      <c r="B526" t="s">
+        <v>757</v>
+      </c>
+      <c r="C526" t="s">
+        <v>932</v>
+      </c>
+      <c r="D526" t="s">
+        <v>395</v>
+      </c>
+      <c r="E526" t="s">
+        <v>534</v>
+      </c>
+      <c r="F526" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G526">
+        <v>1</v>
+      </c>
+      <c r="H526">
+        <v>1</v>
+      </c>
+      <c r="I526">
+        <v>1</v>
+      </c>
+      <c r="J526">
+        <v>1</v>
+      </c>
+      <c r="K526">
+        <v>1</v>
+      </c>
+      <c r="L526">
+        <v>1</v>
+      </c>
+      <c r="M526">
+        <v>1</v>
+      </c>
+      <c r="N526">
+        <v>1</v>
+      </c>
+      <c r="O526">
+        <v>1</v>
+      </c>
+      <c r="P526">
+        <v>1</v>
+      </c>
+      <c r="Q526">
+        <v>1</v>
+      </c>
+      <c r="R526">
+        <v>1</v>
+      </c>
+      <c r="S526">
+        <v>1</v>
+      </c>
+      <c r="T526">
+        <v>1</v>
+      </c>
+      <c r="U526">
+        <v>1</v>
+      </c>
+      <c r="V526">
+        <v>1</v>
+      </c>
+      <c r="W526">
+        <v>1</v>
+      </c>
+      <c r="X526">
+        <v>1</v>
+      </c>
+      <c r="Y526">
+        <v>1</v>
+      </c>
+      <c r="Z526">
+        <v>1</v>
+      </c>
+      <c r="AA526">
+        <v>1</v>
+      </c>
+      <c r="AB526">
+        <v>1</v>
+      </c>
+      <c r="AC526">
+        <v>1</v>
+      </c>
+      <c r="AD526">
+        <v>1</v>
+      </c>
+      <c r="AE526">
+        <v>1</v>
+      </c>
+      <c r="AF526">
+        <v>1</v>
+      </c>
+      <c r="AG526">
+        <v>1</v>
+      </c>
+      <c r="AH526">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="527" spans="1:34">
+      <c r="A527">
+        <v>1</v>
+      </c>
+      <c r="B527" t="s">
+        <v>757</v>
+      </c>
+      <c r="C527" t="s">
+        <v>932</v>
+      </c>
+      <c r="D527" t="s">
+        <v>954</v>
+      </c>
+      <c r="E527" t="s">
+        <v>994</v>
+      </c>
+      <c r="F527" t="s">
+        <v>590</v>
+      </c>
+      <c r="G527">
+        <v>1</v>
+      </c>
+      <c r="H527">
+        <v>1</v>
+      </c>
+      <c r="I527">
+        <v>1</v>
+      </c>
+      <c r="J527">
+        <v>1</v>
+      </c>
+      <c r="K527">
+        <v>1</v>
+      </c>
+      <c r="L527">
+        <v>1</v>
+      </c>
+      <c r="M527">
+        <v>1</v>
+      </c>
+      <c r="N527">
+        <v>1</v>
+      </c>
+      <c r="O527">
+        <v>1</v>
+      </c>
+      <c r="P527">
+        <v>1</v>
+      </c>
+      <c r="Q527">
+        <v>1</v>
+      </c>
+      <c r="R527">
+        <v>1</v>
+      </c>
+      <c r="S527">
+        <v>1</v>
+      </c>
+      <c r="T527">
+        <v>1</v>
+      </c>
+      <c r="U527">
+        <v>1</v>
+      </c>
+      <c r="V527">
+        <v>1</v>
+      </c>
+      <c r="W527">
+        <v>1</v>
+      </c>
+      <c r="X527">
+        <v>1</v>
+      </c>
+      <c r="Y527">
+        <v>1</v>
+      </c>
+      <c r="Z527">
+        <v>1</v>
+      </c>
+      <c r="AA527">
+        <v>1</v>
+      </c>
+      <c r="AB527">
+        <v>1</v>
+      </c>
+      <c r="AC527">
+        <v>1</v>
+      </c>
+      <c r="AD527">
+        <v>1</v>
+      </c>
+      <c r="AE527">
+        <v>1</v>
+      </c>
+      <c r="AF527">
+        <v>1</v>
+      </c>
+      <c r="AG527">
+        <v>1</v>
+      </c>
+      <c r="AH527">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="528" spans="1:34">
+      <c r="A528">
+        <v>1</v>
+      </c>
+      <c r="B528" t="s">
+        <v>758</v>
+      </c>
+      <c r="C528" t="s">
+        <v>933</v>
+      </c>
+      <c r="D528" t="s">
+        <v>396</v>
+      </c>
+      <c r="E528" t="s">
+        <v>535</v>
+      </c>
+      <c r="F528" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G528">
+        <v>1</v>
+      </c>
+      <c r="H528">
+        <v>1</v>
+      </c>
+      <c r="I528">
+        <v>1</v>
+      </c>
+      <c r="J528">
+        <v>1</v>
+      </c>
+      <c r="K528">
+        <v>1</v>
+      </c>
+      <c r="L528">
+        <v>1</v>
+      </c>
+      <c r="M528">
+        <v>1</v>
+      </c>
+      <c r="N528">
+        <v>1</v>
+      </c>
+      <c r="O528">
+        <v>1</v>
+      </c>
+      <c r="P528">
+        <v>1</v>
+      </c>
+      <c r="Q528">
+        <v>1</v>
+      </c>
+      <c r="R528">
+        <v>1</v>
+      </c>
+      <c r="S528">
+        <v>1</v>
+      </c>
+      <c r="T528">
+        <v>1</v>
+      </c>
+      <c r="U528">
+        <v>1</v>
+      </c>
+      <c r="V528">
+        <v>1</v>
+      </c>
+      <c r="W528">
+        <v>1</v>
+      </c>
+      <c r="X528">
+        <v>1</v>
+      </c>
+      <c r="Y528">
+        <v>1</v>
+      </c>
+      <c r="Z528">
+        <v>1</v>
+      </c>
+      <c r="AA528">
+        <v>1</v>
+      </c>
+      <c r="AB528">
+        <v>1</v>
+      </c>
+      <c r="AC528">
+        <v>1</v>
+      </c>
+      <c r="AD528">
+        <v>1</v>
+      </c>
+      <c r="AE528">
+        <v>1</v>
+      </c>
+      <c r="AF528">
+        <v>1</v>
+      </c>
+      <c r="AG528">
+        <v>1</v>
+      </c>
+      <c r="AH528">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="529" spans="1:34">
+      <c r="A529">
+        <v>1</v>
+      </c>
+      <c r="B529" t="s">
+        <v>758</v>
+      </c>
+      <c r="C529" t="s">
+        <v>933</v>
+      </c>
+      <c r="D529" t="s">
+        <v>955</v>
+      </c>
+      <c r="E529" t="s">
+        <v>995</v>
+      </c>
+      <c r="F529" t="s">
+        <v>590</v>
+      </c>
+      <c r="G529">
+        <v>1</v>
+      </c>
+      <c r="H529">
+        <v>1</v>
+      </c>
+      <c r="I529">
+        <v>1</v>
+      </c>
+      <c r="J529">
+        <v>1</v>
+      </c>
+      <c r="K529">
+        <v>1</v>
+      </c>
+      <c r="L529">
+        <v>1</v>
+      </c>
+      <c r="M529">
+        <v>1</v>
+      </c>
+      <c r="N529">
+        <v>1</v>
+      </c>
+      <c r="O529">
+        <v>1</v>
+      </c>
+      <c r="P529">
+        <v>1</v>
+      </c>
+      <c r="Q529">
+        <v>1</v>
+      </c>
+      <c r="R529">
+        <v>1</v>
+      </c>
+      <c r="S529">
+        <v>1</v>
+      </c>
+      <c r="T529">
+        <v>1</v>
+      </c>
+      <c r="U529">
+        <v>1</v>
+      </c>
+      <c r="V529">
+        <v>1</v>
+      </c>
+      <c r="W529">
+        <v>1</v>
+      </c>
+      <c r="X529">
+        <v>1</v>
+      </c>
+      <c r="Y529">
+        <v>1</v>
+      </c>
+      <c r="Z529">
+        <v>1</v>
+      </c>
+      <c r="AA529">
+        <v>1</v>
+      </c>
+      <c r="AB529">
+        <v>1</v>
+      </c>
+      <c r="AC529">
+        <v>1</v>
+      </c>
+      <c r="AD529">
+        <v>1</v>
+      </c>
+      <c r="AE529">
+        <v>1</v>
+      </c>
+      <c r="AF529">
+        <v>1</v>
+      </c>
+      <c r="AG529">
+        <v>1</v>
+      </c>
+      <c r="AH529">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530" spans="1:34">
+      <c r="A530">
+        <v>1</v>
+      </c>
+      <c r="B530" t="s">
+        <v>759</v>
+      </c>
+      <c r="C530" t="s">
+        <v>934</v>
+      </c>
+      <c r="D530" t="s">
+        <v>397</v>
+      </c>
+      <c r="E530" t="s">
+        <v>536</v>
+      </c>
+      <c r="F530" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G530">
+        <v>1</v>
+      </c>
+      <c r="H530">
+        <v>1</v>
+      </c>
+      <c r="I530">
+        <v>1</v>
+      </c>
+      <c r="J530">
+        <v>1</v>
+      </c>
+      <c r="K530">
+        <v>1</v>
+      </c>
+      <c r="L530">
+        <v>1</v>
+      </c>
+      <c r="M530">
+        <v>1</v>
+      </c>
+      <c r="N530">
+        <v>1</v>
+      </c>
+      <c r="O530">
+        <v>1</v>
+      </c>
+      <c r="P530">
+        <v>1</v>
+      </c>
+      <c r="Q530">
+        <v>1</v>
+      </c>
+      <c r="R530">
+        <v>1</v>
+      </c>
+      <c r="S530">
+        <v>1</v>
+      </c>
+      <c r="T530">
+        <v>1</v>
+      </c>
+      <c r="U530">
+        <v>1</v>
+      </c>
+      <c r="V530">
+        <v>1</v>
+      </c>
+      <c r="W530">
+        <v>1</v>
+      </c>
+      <c r="X530">
+        <v>1</v>
+      </c>
+      <c r="Y530">
+        <v>1</v>
+      </c>
+      <c r="Z530">
+        <v>1</v>
+      </c>
+      <c r="AA530">
+        <v>1</v>
+      </c>
+      <c r="AB530">
+        <v>1</v>
+      </c>
+      <c r="AC530">
+        <v>1</v>
+      </c>
+      <c r="AD530">
+        <v>1</v>
+      </c>
+      <c r="AE530">
+        <v>1</v>
+      </c>
+      <c r="AF530">
+        <v>1</v>
+      </c>
+      <c r="AG530">
+        <v>1</v>
+      </c>
+      <c r="AH530">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531" spans="1:34">
+      <c r="A531">
+        <v>1</v>
+      </c>
+      <c r="B531" t="s">
+        <v>759</v>
+      </c>
+      <c r="C531" t="s">
+        <v>934</v>
+      </c>
+      <c r="D531" t="s">
+        <v>956</v>
+      </c>
+      <c r="E531" t="s">
+        <v>996</v>
+      </c>
+      <c r="F531" t="s">
+        <v>590</v>
+      </c>
+      <c r="G531">
+        <v>1</v>
+      </c>
+      <c r="H531">
+        <v>1</v>
+      </c>
+      <c r="I531">
+        <v>1</v>
+      </c>
+      <c r="J531">
+        <v>1</v>
+      </c>
+      <c r="K531">
+        <v>1</v>
+      </c>
+      <c r="L531">
+        <v>1</v>
+      </c>
+      <c r="M531">
+        <v>1</v>
+      </c>
+      <c r="N531">
+        <v>1</v>
+      </c>
+      <c r="O531">
+        <v>1</v>
+      </c>
+      <c r="P531">
+        <v>1</v>
+      </c>
+      <c r="Q531">
+        <v>1</v>
+      </c>
+      <c r="R531">
+        <v>1</v>
+      </c>
+      <c r="S531">
+        <v>1</v>
+      </c>
+      <c r="T531">
+        <v>1</v>
+      </c>
+      <c r="U531">
+        <v>1</v>
+      </c>
+      <c r="V531">
+        <v>1</v>
+      </c>
+      <c r="W531">
+        <v>1</v>
+      </c>
+      <c r="X531">
+        <v>1</v>
+      </c>
+      <c r="Y531">
+        <v>1</v>
+      </c>
+      <c r="Z531">
+        <v>1</v>
+      </c>
+      <c r="AA531">
+        <v>1</v>
+      </c>
+      <c r="AB531">
+        <v>1</v>
+      </c>
+      <c r="AC531">
+        <v>1</v>
+      </c>
+      <c r="AD531">
+        <v>1</v>
+      </c>
+      <c r="AE531">
+        <v>1</v>
+      </c>
+      <c r="AF531">
+        <v>1</v>
+      </c>
+      <c r="AG531">
+        <v>1</v>
+      </c>
+      <c r="AH531">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="532" spans="1:34">
+      <c r="A532">
+        <v>1</v>
+      </c>
+      <c r="B532" t="s">
+        <v>760</v>
+      </c>
+      <c r="C532" t="s">
+        <v>935</v>
+      </c>
+      <c r="D532" t="s">
+        <v>439</v>
+      </c>
+      <c r="E532" t="s">
+        <v>578</v>
+      </c>
+      <c r="F532" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G532">
+        <v>1</v>
+      </c>
+      <c r="H532">
+        <v>1</v>
+      </c>
+      <c r="I532">
+        <v>1</v>
+      </c>
+      <c r="J532">
+        <v>1</v>
+      </c>
+      <c r="K532">
+        <v>1</v>
+      </c>
+      <c r="L532">
+        <v>1</v>
+      </c>
+      <c r="M532">
+        <v>1</v>
+      </c>
+      <c r="N532">
+        <v>1</v>
+      </c>
+      <c r="O532">
+        <v>1</v>
+      </c>
+      <c r="P532">
+        <v>1</v>
+      </c>
+      <c r="Q532">
+        <v>1</v>
+      </c>
+      <c r="R532">
+        <v>1</v>
+      </c>
+      <c r="S532">
+        <v>1</v>
+      </c>
+      <c r="T532">
+        <v>1</v>
+      </c>
+      <c r="U532">
+        <v>1</v>
+      </c>
+      <c r="V532">
+        <v>1</v>
+      </c>
+      <c r="W532">
+        <v>1</v>
+      </c>
+      <c r="X532">
+        <v>1</v>
+      </c>
+      <c r="Y532">
+        <v>1</v>
+      </c>
+      <c r="Z532">
+        <v>1</v>
+      </c>
+      <c r="AA532">
+        <v>1</v>
+      </c>
+      <c r="AB532">
+        <v>1</v>
+      </c>
+      <c r="AC532">
+        <v>1</v>
+      </c>
+      <c r="AD532">
+        <v>1</v>
+      </c>
+      <c r="AE532">
+        <v>1</v>
+      </c>
+      <c r="AF532">
+        <v>1</v>
+      </c>
+      <c r="AG532">
+        <v>1</v>
+      </c>
+      <c r="AH532">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="533" spans="1:34">
+      <c r="A533">
+        <v>1</v>
+      </c>
+      <c r="B533" t="s">
+        <v>760</v>
+      </c>
+      <c r="C533" t="s">
+        <v>935</v>
+      </c>
+      <c r="D533" t="s">
+        <v>960</v>
+      </c>
+      <c r="E533" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F533" t="s">
+        <v>590</v>
+      </c>
+      <c r="G533">
+        <v>1</v>
+      </c>
+      <c r="H533">
+        <v>1</v>
+      </c>
+      <c r="I533">
+        <v>1</v>
+      </c>
+      <c r="J533">
+        <v>1</v>
+      </c>
+      <c r="K533">
+        <v>1</v>
+      </c>
+      <c r="L533">
+        <v>1</v>
+      </c>
+      <c r="M533">
+        <v>1</v>
+      </c>
+      <c r="N533">
+        <v>1</v>
+      </c>
+      <c r="O533">
+        <v>1</v>
+      </c>
+      <c r="P533">
+        <v>1</v>
+      </c>
+      <c r="Q533">
+        <v>1</v>
+      </c>
+      <c r="R533">
+        <v>1</v>
+      </c>
+      <c r="S533">
+        <v>1</v>
+      </c>
+      <c r="T533">
+        <v>1</v>
+      </c>
+      <c r="U533">
+        <v>1</v>
+      </c>
+      <c r="V533">
+        <v>1</v>
+      </c>
+      <c r="W533">
+        <v>1</v>
+      </c>
+      <c r="X533">
+        <v>1</v>
+      </c>
+      <c r="Y533">
+        <v>1</v>
+      </c>
+      <c r="Z533">
+        <v>1</v>
+      </c>
+      <c r="AA533">
+        <v>1</v>
+      </c>
+      <c r="AB533">
+        <v>1</v>
+      </c>
+      <c r="AC533">
+        <v>1</v>
+      </c>
+      <c r="AD533">
+        <v>1</v>
+      </c>
+      <c r="AE533">
+        <v>1</v>
+      </c>
+      <c r="AF533">
+        <v>1</v>
+      </c>
+      <c r="AG533">
+        <v>1</v>
+      </c>
+      <c r="AH533">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="534" spans="1:34">
+      <c r="A534">
+        <v>1</v>
+      </c>
+      <c r="B534" t="s">
+        <v>761</v>
+      </c>
+      <c r="C534" t="s">
+        <v>936</v>
+      </c>
+      <c r="D534" t="s">
+        <v>449</v>
+      </c>
+      <c r="E534" t="s">
+        <v>588</v>
+      </c>
+      <c r="F534" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G534">
+        <v>1</v>
+      </c>
+      <c r="H534">
+        <v>1</v>
+      </c>
+      <c r="I534">
+        <v>1</v>
+      </c>
+      <c r="J534">
+        <v>1</v>
+      </c>
+      <c r="K534">
+        <v>1</v>
+      </c>
+      <c r="L534">
+        <v>1</v>
+      </c>
+      <c r="M534">
+        <v>1</v>
+      </c>
+      <c r="N534">
+        <v>1</v>
+      </c>
+      <c r="O534">
+        <v>1</v>
+      </c>
+      <c r="P534">
+        <v>1</v>
+      </c>
+      <c r="Q534">
+        <v>1</v>
+      </c>
+      <c r="R534">
+        <v>1</v>
+      </c>
+      <c r="S534">
+        <v>1</v>
+      </c>
+      <c r="T534">
+        <v>1</v>
+      </c>
+      <c r="U534">
+        <v>1</v>
+      </c>
+      <c r="V534">
+        <v>1</v>
+      </c>
+      <c r="W534">
+        <v>1</v>
+      </c>
+      <c r="X534">
+        <v>1</v>
+      </c>
+      <c r="Y534">
+        <v>1</v>
+      </c>
+      <c r="Z534">
+        <v>1</v>
+      </c>
+      <c r="AA534">
+        <v>1</v>
+      </c>
+      <c r="AB534">
+        <v>1</v>
+      </c>
+      <c r="AC534">
+        <v>1</v>
+      </c>
+      <c r="AD534">
+        <v>1</v>
+      </c>
+      <c r="AE534">
+        <v>1</v>
+      </c>
+      <c r="AF534">
+        <v>1</v>
+      </c>
+      <c r="AG534">
+        <v>1</v>
+      </c>
+      <c r="AH534">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="535" spans="1:34">
+      <c r="A535">
+        <v>1</v>
+      </c>
+      <c r="B535" t="s">
+        <v>761</v>
+      </c>
+      <c r="C535" t="s">
+        <v>936</v>
+      </c>
+      <c r="D535" t="s">
+        <v>960</v>
+      </c>
+      <c r="E535" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F535" t="s">
+        <v>590</v>
+      </c>
+      <c r="G535">
+        <v>1</v>
+      </c>
+      <c r="H535">
+        <v>1</v>
+      </c>
+      <c r="I535">
+        <v>1</v>
+      </c>
+      <c r="J535">
+        <v>1</v>
+      </c>
+      <c r="K535">
+        <v>1</v>
+      </c>
+      <c r="L535">
+        <v>1</v>
+      </c>
+      <c r="M535">
+        <v>1</v>
+      </c>
+      <c r="N535">
+        <v>1</v>
+      </c>
+      <c r="O535">
+        <v>1</v>
+      </c>
+      <c r="P535">
+        <v>1</v>
+      </c>
+      <c r="Q535">
+        <v>1</v>
+      </c>
+      <c r="R535">
+        <v>1</v>
+      </c>
+      <c r="S535">
+        <v>1</v>
+      </c>
+      <c r="T535">
+        <v>1</v>
+      </c>
+      <c r="U535">
+        <v>1</v>
+      </c>
+      <c r="V535">
+        <v>1</v>
+      </c>
+      <c r="W535">
+        <v>1</v>
+      </c>
+      <c r="X535">
+        <v>1</v>
+      </c>
+      <c r="Y535">
+        <v>1</v>
+      </c>
+      <c r="Z535">
+        <v>1</v>
+      </c>
+      <c r="AA535">
+        <v>1</v>
+      </c>
+      <c r="AB535">
+        <v>1</v>
+      </c>
+      <c r="AC535">
+        <v>1</v>
+      </c>
+      <c r="AD535">
+        <v>1</v>
+      </c>
+      <c r="AE535">
+        <v>1</v>
+      </c>
+      <c r="AF535">
+        <v>1</v>
+      </c>
+      <c r="AG535">
+        <v>1</v>
+      </c>
+      <c r="AH535">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="536" spans="1:34">
+      <c r="A536">
+        <v>1</v>
+      </c>
+      <c r="B536" t="s">
+        <v>762</v>
+      </c>
+      <c r="C536" t="s">
+        <v>937</v>
+      </c>
+      <c r="D536" t="s">
+        <v>967</v>
+      </c>
+      <c r="E536" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F536" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G536">
+        <v>1</v>
+      </c>
+      <c r="H536">
+        <v>1</v>
+      </c>
+      <c r="I536">
+        <v>1</v>
+      </c>
+      <c r="J536">
+        <v>1</v>
+      </c>
+      <c r="K536">
+        <v>1</v>
+      </c>
+      <c r="L536">
+        <v>1</v>
+      </c>
+      <c r="M536">
+        <v>1</v>
+      </c>
+      <c r="N536">
+        <v>1</v>
+      </c>
+      <c r="O536">
+        <v>1</v>
+      </c>
+      <c r="P536">
+        <v>1</v>
+      </c>
+      <c r="Q536">
+        <v>1</v>
+      </c>
+      <c r="R536">
+        <v>1</v>
+      </c>
+      <c r="S536">
+        <v>1</v>
+      </c>
+      <c r="T536">
+        <v>1</v>
+      </c>
+      <c r="U536">
+        <v>1</v>
+      </c>
+      <c r="V536">
+        <v>1</v>
+      </c>
+      <c r="W536">
+        <v>1</v>
+      </c>
+      <c r="X536">
+        <v>1</v>
+      </c>
+      <c r="Y536">
+        <v>1</v>
+      </c>
+      <c r="Z536">
+        <v>1</v>
+      </c>
+      <c r="AA536">
+        <v>1</v>
+      </c>
+      <c r="AB536">
+        <v>1</v>
+      </c>
+      <c r="AC536">
+        <v>1</v>
+      </c>
+      <c r="AD536">
+        <v>1</v>
+      </c>
+      <c r="AE536">
+        <v>1</v>
+      </c>
+      <c r="AF536">
+        <v>1</v>
+      </c>
+      <c r="AG536">
+        <v>1</v>
+      </c>
+      <c r="AH536">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="537" spans="1:34">
+      <c r="A537">
+        <v>2</v>
+      </c>
+      <c r="B537" t="s">
+        <v>762</v>
+      </c>
+      <c r="C537" t="s">
+        <v>937</v>
+      </c>
+      <c r="D537" t="s">
+        <v>961</v>
+      </c>
+      <c r="E537" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F537" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G537">
+        <v>1</v>
+      </c>
+      <c r="H537">
+        <v>1</v>
+      </c>
+      <c r="I537">
+        <v>1</v>
+      </c>
+      <c r="J537">
+        <v>1</v>
+      </c>
+      <c r="K537">
+        <v>1</v>
+      </c>
+      <c r="L537">
+        <v>1</v>
+      </c>
+      <c r="M537">
+        <v>1</v>
+      </c>
+      <c r="N537">
+        <v>1</v>
+      </c>
+      <c r="O537">
+        <v>1</v>
+      </c>
+      <c r="P537">
+        <v>1</v>
+      </c>
+      <c r="Q537">
+        <v>1</v>
+      </c>
+      <c r="R537">
+        <v>1</v>
+      </c>
+      <c r="S537">
+        <v>1</v>
+      </c>
+      <c r="T537">
+        <v>1</v>
+      </c>
+      <c r="U537">
+        <v>1</v>
+      </c>
+      <c r="V537">
+        <v>1</v>
+      </c>
+      <c r="W537">
+        <v>1</v>
+      </c>
+      <c r="X537">
+        <v>1</v>
+      </c>
+      <c r="Y537">
+        <v>1</v>
+      </c>
+      <c r="Z537">
+        <v>1</v>
+      </c>
+      <c r="AA537">
+        <v>1</v>
+      </c>
+      <c r="AB537">
+        <v>1</v>
+      </c>
+      <c r="AC537">
+        <v>1</v>
+      </c>
+      <c r="AD537">
+        <v>1</v>
+      </c>
+      <c r="AE537">
+        <v>1</v>
+      </c>
+      <c r="AF537">
+        <v>1</v>
+      </c>
+      <c r="AG537">
+        <v>1</v>
+      </c>
+      <c r="AH537">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="538" spans="1:34">
+      <c r="A538">
+        <v>1</v>
+      </c>
+      <c r="B538" t="s">
+        <v>762</v>
+      </c>
+      <c r="C538" t="s">
+        <v>937</v>
+      </c>
+      <c r="D538" t="s">
+        <v>964</v>
+      </c>
+      <c r="E538" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F538" t="s">
+        <v>590</v>
+      </c>
+      <c r="G538">
+        <v>0.95</v>
+      </c>
+      <c r="H538">
+        <v>0.95</v>
+      </c>
+      <c r="I538">
+        <v>0.95</v>
+      </c>
+      <c r="J538">
+        <v>0.95</v>
+      </c>
+      <c r="K538">
+        <v>0.95</v>
+      </c>
+      <c r="L538">
+        <v>0.95</v>
+      </c>
+      <c r="M538">
+        <v>0.95</v>
+      </c>
+      <c r="N538">
+        <v>0.95</v>
+      </c>
+      <c r="O538">
+        <v>0.95</v>
+      </c>
+      <c r="P538">
+        <v>0.95</v>
+      </c>
+      <c r="Q538">
+        <v>0.95</v>
+      </c>
+      <c r="R538">
+        <v>0.95</v>
+      </c>
+      <c r="S538">
+        <v>0.95</v>
+      </c>
+      <c r="T538">
+        <v>0.95</v>
+      </c>
+      <c r="U538">
+        <v>0.95</v>
+      </c>
+      <c r="V538">
+        <v>0.95</v>
+      </c>
+      <c r="W538">
+        <v>0.95</v>
+      </c>
+      <c r="X538">
+        <v>0.95</v>
+      </c>
+      <c r="Y538">
+        <v>0.95</v>
+      </c>
+      <c r="Z538">
+        <v>0.95</v>
+      </c>
+      <c r="AA538">
+        <v>0.95</v>
+      </c>
+      <c r="AB538">
+        <v>0.95</v>
+      </c>
+      <c r="AC538">
+        <v>0.95</v>
+      </c>
+      <c r="AD538">
+        <v>0.95</v>
+      </c>
+      <c r="AE538">
+        <v>0.95</v>
+      </c>
+      <c r="AF538">
+        <v>0.95</v>
+      </c>
+      <c r="AG538">
+        <v>0.95</v>
+      </c>
+      <c r="AH538">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="539" spans="1:34">
+      <c r="A539">
+        <v>2</v>
+      </c>
+      <c r="B539" t="s">
+        <v>762</v>
+      </c>
+      <c r="C539" t="s">
+        <v>937</v>
+      </c>
+      <c r="D539" t="s">
+        <v>968</v>
+      </c>
+      <c r="E539" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F539" t="s">
+        <v>590</v>
+      </c>
+      <c r="G539">
+        <v>0.95</v>
+      </c>
+      <c r="H539">
+        <v>0.95</v>
+      </c>
+      <c r="I539">
+        <v>0.95</v>
+      </c>
+      <c r="J539">
+        <v>0.95</v>
+      </c>
+      <c r="K539">
+        <v>0.95</v>
+      </c>
+      <c r="L539">
+        <v>0.95</v>
+      </c>
+      <c r="M539">
+        <v>0.95</v>
+      </c>
+      <c r="N539">
+        <v>0.95</v>
+      </c>
+      <c r="O539">
+        <v>0.95</v>
+      </c>
+      <c r="P539">
+        <v>0.95</v>
+      </c>
+      <c r="Q539">
+        <v>0.95</v>
+      </c>
+      <c r="R539">
+        <v>0.95</v>
+      </c>
+      <c r="S539">
+        <v>0.95</v>
+      </c>
+      <c r="T539">
+        <v>0.95</v>
+      </c>
+      <c r="U539">
+        <v>0.95</v>
+      </c>
+      <c r="V539">
+        <v>0.95</v>
+      </c>
+      <c r="W539">
+        <v>0.95</v>
+      </c>
+      <c r="X539">
+        <v>0.95</v>
+      </c>
+      <c r="Y539">
+        <v>0.95</v>
+      </c>
+      <c r="Z539">
+        <v>0.95</v>
+      </c>
+      <c r="AA539">
+        <v>0.95</v>
+      </c>
+      <c r="AB539">
+        <v>0.95</v>
+      </c>
+      <c r="AC539">
+        <v>0.95</v>
+      </c>
+      <c r="AD539">
+        <v>0.95</v>
+      </c>
+      <c r="AE539">
+        <v>0.95</v>
+      </c>
+      <c r="AF539">
+        <v>0.95</v>
+      </c>
+      <c r="AG539">
+        <v>0.95</v>
+      </c>
+      <c r="AH539">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="540" spans="1:34">
+      <c r="A540">
+        <v>1</v>
+      </c>
+      <c r="B540" t="s">
+        <v>763</v>
+      </c>
+      <c r="C540" t="s">
+        <v>938</v>
+      </c>
+      <c r="D540" t="s">
+        <v>967</v>
+      </c>
+      <c r="E540" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F540" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G540">
+        <v>1</v>
+      </c>
+      <c r="H540">
+        <v>1</v>
+      </c>
+      <c r="I540">
+        <v>1</v>
+      </c>
+      <c r="J540">
+        <v>1</v>
+      </c>
+      <c r="K540">
+        <v>1</v>
+      </c>
+      <c r="L540">
+        <v>1</v>
+      </c>
+      <c r="M540">
+        <v>1</v>
+      </c>
+      <c r="N540">
+        <v>1</v>
+      </c>
+      <c r="O540">
+        <v>1</v>
+      </c>
+      <c r="P540">
+        <v>1</v>
+      </c>
+      <c r="Q540">
+        <v>1</v>
+      </c>
+      <c r="R540">
+        <v>1</v>
+      </c>
+      <c r="S540">
+        <v>1</v>
+      </c>
+      <c r="T540">
+        <v>1</v>
+      </c>
+      <c r="U540">
+        <v>1</v>
+      </c>
+      <c r="V540">
+        <v>1</v>
+      </c>
+      <c r="W540">
+        <v>1</v>
+      </c>
+      <c r="X540">
+        <v>1</v>
+      </c>
+      <c r="Y540">
+        <v>1</v>
+      </c>
+      <c r="Z540">
+        <v>1</v>
+      </c>
+      <c r="AA540">
+        <v>1</v>
+      </c>
+      <c r="AB540">
+        <v>1</v>
+      </c>
+      <c r="AC540">
+        <v>1</v>
+      </c>
+      <c r="AD540">
+        <v>1</v>
+      </c>
+      <c r="AE540">
+        <v>1</v>
+      </c>
+      <c r="AF540">
+        <v>1</v>
+      </c>
+      <c r="AG540">
+        <v>1</v>
+      </c>
+      <c r="AH540">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="541" spans="1:34">
+      <c r="A541">
+        <v>2</v>
+      </c>
+      <c r="B541" t="s">
+        <v>763</v>
+      </c>
+      <c r="C541" t="s">
+        <v>938</v>
+      </c>
+      <c r="D541" t="s">
+        <v>965</v>
+      </c>
+      <c r="E541" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F541" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G541">
+        <v>1</v>
+      </c>
+      <c r="H541">
+        <v>1</v>
+      </c>
+      <c r="I541">
+        <v>1</v>
+      </c>
+      <c r="J541">
+        <v>1</v>
+      </c>
+      <c r="K541">
+        <v>1</v>
+      </c>
+      <c r="L541">
+        <v>1</v>
+      </c>
+      <c r="M541">
+        <v>1</v>
+      </c>
+      <c r="N541">
+        <v>1</v>
+      </c>
+      <c r="O541">
+        <v>1</v>
+      </c>
+      <c r="P541">
+        <v>1</v>
+      </c>
+      <c r="Q541">
+        <v>1</v>
+      </c>
+      <c r="R541">
+        <v>1</v>
+      </c>
+      <c r="S541">
+        <v>1</v>
+      </c>
+      <c r="T541">
+        <v>1</v>
+      </c>
+      <c r="U541">
+        <v>1</v>
+      </c>
+      <c r="V541">
+        <v>1</v>
+      </c>
+      <c r="W541">
+        <v>1</v>
+      </c>
+      <c r="X541">
+        <v>1</v>
+      </c>
+      <c r="Y541">
+        <v>1</v>
+      </c>
+      <c r="Z541">
+        <v>1</v>
+      </c>
+      <c r="AA541">
+        <v>1</v>
+      </c>
+      <c r="AB541">
+        <v>1</v>
+      </c>
+      <c r="AC541">
+        <v>1</v>
+      </c>
+      <c r="AD541">
+        <v>1</v>
+      </c>
+      <c r="AE541">
+        <v>1</v>
+      </c>
+      <c r="AF541">
+        <v>1</v>
+      </c>
+      <c r="AG541">
+        <v>1</v>
+      </c>
+      <c r="AH541">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542" spans="1:34">
+      <c r="A542">
+        <v>1</v>
+      </c>
+      <c r="B542" t="s">
+        <v>763</v>
+      </c>
+      <c r="C542" t="s">
+        <v>938</v>
+      </c>
+      <c r="D542" t="s">
+        <v>966</v>
+      </c>
+      <c r="E542" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F542" t="s">
+        <v>590</v>
+      </c>
+      <c r="G542">
+        <v>0.95</v>
+      </c>
+      <c r="H542">
+        <v>0.95</v>
+      </c>
+      <c r="I542">
+        <v>0.95</v>
+      </c>
+      <c r="J542">
+        <v>0.95</v>
+      </c>
+      <c r="K542">
+        <v>0.95</v>
+      </c>
+      <c r="L542">
+        <v>0.95</v>
+      </c>
+      <c r="M542">
+        <v>0.95</v>
+      </c>
+      <c r="N542">
+        <v>0.95</v>
+      </c>
+      <c r="O542">
+        <v>0.95</v>
+      </c>
+      <c r="P542">
+        <v>0.95</v>
+      </c>
+      <c r="Q542">
+        <v>0.95</v>
+      </c>
+      <c r="R542">
+        <v>0.95</v>
+      </c>
+      <c r="S542">
+        <v>0.95</v>
+      </c>
+      <c r="T542">
+        <v>0.95</v>
+      </c>
+      <c r="U542">
+        <v>0.95</v>
+      </c>
+      <c r="V542">
+        <v>0.95</v>
+      </c>
+      <c r="W542">
+        <v>0.95</v>
+      </c>
+      <c r="X542">
+        <v>0.95</v>
+      </c>
+      <c r="Y542">
+        <v>0.95</v>
+      </c>
+      <c r="Z542">
+        <v>0.95</v>
+      </c>
+      <c r="AA542">
+        <v>0.95</v>
+      </c>
+      <c r="AB542">
+        <v>0.95</v>
+      </c>
+      <c r="AC542">
+        <v>0.95</v>
+      </c>
+      <c r="AD542">
+        <v>0.95</v>
+      </c>
+      <c r="AE542">
+        <v>0.95</v>
+      </c>
+      <c r="AF542">
+        <v>0.95</v>
+      </c>
+      <c r="AG542">
+        <v>0.95</v>
+      </c>
+      <c r="AH542">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="543" spans="1:34">
+      <c r="A543">
+        <v>2</v>
+      </c>
+      <c r="B543" t="s">
+        <v>763</v>
+      </c>
+      <c r="C543" t="s">
+        <v>938</v>
+      </c>
+      <c r="D543" t="s">
+        <v>968</v>
+      </c>
+      <c r="E543" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F543" t="s">
+        <v>590</v>
+      </c>
+      <c r="G543">
+        <v>0.95</v>
+      </c>
+      <c r="H543">
+        <v>0.95</v>
+      </c>
+      <c r="I543">
+        <v>0.95</v>
+      </c>
+      <c r="J543">
+        <v>0.95</v>
+      </c>
+      <c r="K543">
+        <v>0.95</v>
+      </c>
+      <c r="L543">
+        <v>0.95</v>
+      </c>
+      <c r="M543">
+        <v>0.95</v>
+      </c>
+      <c r="N543">
+        <v>0.95</v>
+      </c>
+      <c r="O543">
+        <v>0.95</v>
+      </c>
+      <c r="P543">
+        <v>0.95</v>
+      </c>
+      <c r="Q543">
+        <v>0.95</v>
+      </c>
+      <c r="R543">
+        <v>0.95</v>
+      </c>
+      <c r="S543">
+        <v>0.95</v>
+      </c>
+      <c r="T543">
+        <v>0.95</v>
+      </c>
+      <c r="U543">
+        <v>0.95</v>
+      </c>
+      <c r="V543">
+        <v>0.95</v>
+      </c>
+      <c r="W543">
+        <v>0.95</v>
+      </c>
+      <c r="X543">
+        <v>0.95</v>
+      </c>
+      <c r="Y543">
+        <v>0.95</v>
+      </c>
+      <c r="Z543">
+        <v>0.95</v>
+      </c>
+      <c r="AA543">
+        <v>0.95</v>
+      </c>
+      <c r="AB543">
+        <v>0.95</v>
+      </c>
+      <c r="AC543">
+        <v>0.95</v>
+      </c>
+      <c r="AD543">
+        <v>0.95</v>
+      </c>
+      <c r="AE543">
+        <v>0.95</v>
+      </c>
+      <c r="AF543">
+        <v>0.95</v>
+      </c>
+      <c r="AG543">
+        <v>0.95</v>
+      </c>
+      <c r="AH543">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="544" spans="1:34">
+      <c r="A544">
+        <v>1</v>
+      </c>
+      <c r="B544" t="s">
+        <v>764</v>
+      </c>
+      <c r="C544" t="s">
+        <v>939</v>
+      </c>
+      <c r="D544" t="s">
+        <v>979</v>
+      </c>
+      <c r="E544" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F544" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G544">
+        <v>1</v>
+      </c>
+      <c r="H544">
+        <v>1</v>
+      </c>
+      <c r="I544">
+        <v>1</v>
+      </c>
+      <c r="J544">
+        <v>1</v>
+      </c>
+      <c r="K544">
+        <v>1</v>
+      </c>
+      <c r="L544">
+        <v>1</v>
+      </c>
+      <c r="M544">
+        <v>1</v>
+      </c>
+      <c r="N544">
+        <v>1</v>
+      </c>
+      <c r="O544">
+        <v>1</v>
+      </c>
+      <c r="P544">
+        <v>1</v>
+      </c>
+      <c r="Q544">
+        <v>1</v>
+      </c>
+      <c r="R544">
+        <v>1</v>
+      </c>
+      <c r="S544">
+        <v>1</v>
+      </c>
+      <c r="T544">
+        <v>1</v>
+      </c>
+      <c r="U544">
+        <v>1</v>
+      </c>
+      <c r="V544">
+        <v>1</v>
+      </c>
+      <c r="W544">
+        <v>1</v>
+      </c>
+      <c r="X544">
+        <v>1</v>
+      </c>
+      <c r="Y544">
+        <v>1</v>
+      </c>
+      <c r="Z544">
+        <v>1</v>
+      </c>
+      <c r="AA544">
+        <v>1</v>
+      </c>
+      <c r="AB544">
+        <v>1</v>
+      </c>
+      <c r="AC544">
+        <v>1</v>
+      </c>
+      <c r="AD544">
+        <v>1</v>
+      </c>
+      <c r="AE544">
+        <v>1</v>
+      </c>
+      <c r="AF544">
+        <v>1</v>
+      </c>
+      <c r="AG544">
+        <v>1</v>
+      </c>
+      <c r="AH544">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="545" spans="1:34">
+      <c r="A545">
+        <v>2</v>
+      </c>
+      <c r="B545" t="s">
+        <v>764</v>
+      </c>
+      <c r="C545" t="s">
+        <v>939</v>
+      </c>
+      <c r="D545" t="s">
+        <v>971</v>
+      </c>
+      <c r="E545" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F545" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G545">
+        <v>1</v>
+      </c>
+      <c r="H545">
+        <v>1</v>
+      </c>
+      <c r="I545">
+        <v>1</v>
+      </c>
+      <c r="J545">
+        <v>1</v>
+      </c>
+      <c r="K545">
+        <v>1</v>
+      </c>
+      <c r="L545">
+        <v>1</v>
+      </c>
+      <c r="M545">
+        <v>1</v>
+      </c>
+      <c r="N545">
+        <v>1</v>
+      </c>
+      <c r="O545">
+        <v>1</v>
+      </c>
+      <c r="P545">
+        <v>1</v>
+      </c>
+      <c r="Q545">
+        <v>1</v>
+      </c>
+      <c r="R545">
+        <v>1</v>
+      </c>
+      <c r="S545">
+        <v>1</v>
+      </c>
+      <c r="T545">
+        <v>1</v>
+      </c>
+      <c r="U545">
+        <v>1</v>
+      </c>
+      <c r="V545">
+        <v>1</v>
+      </c>
+      <c r="W545">
+        <v>1</v>
+      </c>
+      <c r="X545">
+        <v>1</v>
+      </c>
+      <c r="Y545">
+        <v>1</v>
+      </c>
+      <c r="Z545">
+        <v>1</v>
+      </c>
+      <c r="AA545">
+        <v>1</v>
+      </c>
+      <c r="AB545">
+        <v>1</v>
+      </c>
+      <c r="AC545">
+        <v>1</v>
+      </c>
+      <c r="AD545">
+        <v>1</v>
+      </c>
+      <c r="AE545">
+        <v>1</v>
+      </c>
+      <c r="AF545">
+        <v>1</v>
+      </c>
+      <c r="AG545">
+        <v>1</v>
+      </c>
+      <c r="AH545">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="546" spans="1:34">
+      <c r="A546">
+        <v>1</v>
+      </c>
+      <c r="B546" t="s">
+        <v>764</v>
+      </c>
+      <c r="C546" t="s">
+        <v>939</v>
+      </c>
+      <c r="D546" t="s">
+        <v>972</v>
+      </c>
+      <c r="E546" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F546" t="s">
+        <v>590</v>
+      </c>
+      <c r="G546">
+        <v>0.95</v>
+      </c>
+      <c r="H546">
+        <v>0.95</v>
+      </c>
+      <c r="I546">
+        <v>0.95</v>
+      </c>
+      <c r="J546">
+        <v>0.95</v>
+      </c>
+      <c r="K546">
+        <v>0.95</v>
+      </c>
+      <c r="L546">
+        <v>0.95</v>
+      </c>
+      <c r="M546">
+        <v>0.95</v>
+      </c>
+      <c r="N546">
+        <v>0.95</v>
+      </c>
+      <c r="O546">
+        <v>0.95</v>
+      </c>
+      <c r="P546">
+        <v>0.95</v>
+      </c>
+      <c r="Q546">
+        <v>0.95</v>
+      </c>
+      <c r="R546">
+        <v>0.95</v>
+      </c>
+      <c r="S546">
+        <v>0.95</v>
+      </c>
+      <c r="T546">
+        <v>0.95</v>
+      </c>
+      <c r="U546">
+        <v>0.95</v>
+      </c>
+      <c r="V546">
+        <v>0.95</v>
+      </c>
+      <c r="W546">
+        <v>0.95</v>
+      </c>
+      <c r="X546">
+        <v>0.95</v>
+      </c>
+      <c r="Y546">
+        <v>0.95</v>
+      </c>
+      <c r="Z546">
+        <v>0.95</v>
+      </c>
+      <c r="AA546">
+        <v>0.95</v>
+      </c>
+      <c r="AB546">
+        <v>0.95</v>
+      </c>
+      <c r="AC546">
+        <v>0.95</v>
+      </c>
+      <c r="AD546">
+        <v>0.95</v>
+      </c>
+      <c r="AE546">
+        <v>0.95</v>
+      </c>
+      <c r="AF546">
+        <v>0.95</v>
+      </c>
+      <c r="AG546">
+        <v>0.95</v>
+      </c>
+      <c r="AH546">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="547" spans="1:34">
+      <c r="A547">
+        <v>2</v>
+      </c>
+      <c r="B547" t="s">
+        <v>764</v>
+      </c>
+      <c r="C547" t="s">
+        <v>939</v>
+      </c>
+      <c r="D547" t="s">
+        <v>980</v>
+      </c>
+      <c r="E547" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F547" t="s">
+        <v>590</v>
+      </c>
+      <c r="G547">
+        <v>0.95</v>
+      </c>
+      <c r="H547">
+        <v>0.95</v>
+      </c>
+      <c r="I547">
+        <v>0.95</v>
+      </c>
+      <c r="J547">
+        <v>0.95</v>
+      </c>
+      <c r="K547">
+        <v>0.95</v>
+      </c>
+      <c r="L547">
+        <v>0.95</v>
+      </c>
+      <c r="M547">
+        <v>0.95</v>
+      </c>
+      <c r="N547">
+        <v>0.95</v>
+      </c>
+      <c r="O547">
+        <v>0.95</v>
+      </c>
+      <c r="P547">
+        <v>0.95</v>
+      </c>
+      <c r="Q547">
+        <v>0.95</v>
+      </c>
+      <c r="R547">
+        <v>0.95</v>
+      </c>
+      <c r="S547">
+        <v>0.95</v>
+      </c>
+      <c r="T547">
+        <v>0.95</v>
+      </c>
+      <c r="U547">
+        <v>0.95</v>
+      </c>
+      <c r="V547">
+        <v>0.95</v>
+      </c>
+      <c r="W547">
+        <v>0.95</v>
+      </c>
+      <c r="X547">
+        <v>0.95</v>
+      </c>
+      <c r="Y547">
+        <v>0.95</v>
+      </c>
+      <c r="Z547">
+        <v>0.95</v>
+      </c>
+      <c r="AA547">
+        <v>0.95</v>
+      </c>
+      <c r="AB547">
+        <v>0.95</v>
+      </c>
+      <c r="AC547">
+        <v>0.95</v>
+      </c>
+      <c r="AD547">
+        <v>0.95</v>
+      </c>
+      <c r="AE547">
+        <v>0.95</v>
+      </c>
+      <c r="AF547">
+        <v>0.95</v>
+      </c>
+      <c r="AG547">
+        <v>0.95</v>
+      </c>
+      <c r="AH547">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="548" spans="1:34">
+      <c r="A548">
+        <v>1</v>
+      </c>
+      <c r="B548" t="s">
+        <v>765</v>
+      </c>
+      <c r="C548" t="s">
+        <v>940</v>
+      </c>
+      <c r="D548" t="s">
+        <v>975</v>
+      </c>
+      <c r="E548" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F548" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G548">
+        <v>1</v>
+      </c>
+      <c r="H548">
+        <v>1</v>
+      </c>
+      <c r="I548">
+        <v>1</v>
+      </c>
+      <c r="J548">
+        <v>1</v>
+      </c>
+      <c r="K548">
+        <v>1</v>
+      </c>
+      <c r="L548">
+        <v>1</v>
+      </c>
+      <c r="M548">
+        <v>1</v>
+      </c>
+      <c r="N548">
+        <v>1</v>
+      </c>
+      <c r="O548">
+        <v>1</v>
+      </c>
+      <c r="P548">
+        <v>1</v>
+      </c>
+      <c r="Q548">
+        <v>1</v>
+      </c>
+      <c r="R548">
+        <v>1</v>
+      </c>
+      <c r="S548">
+        <v>1</v>
+      </c>
+      <c r="T548">
+        <v>1</v>
+      </c>
+      <c r="U548">
+        <v>1</v>
+      </c>
+      <c r="V548">
+        <v>1</v>
+      </c>
+      <c r="W548">
+        <v>1</v>
+      </c>
+      <c r="X548">
+        <v>1</v>
+      </c>
+      <c r="Y548">
+        <v>1</v>
+      </c>
+      <c r="Z548">
+        <v>1</v>
+      </c>
+      <c r="AA548">
+        <v>1</v>
+      </c>
+      <c r="AB548">
+        <v>1</v>
+      </c>
+      <c r="AC548">
+        <v>1</v>
+      </c>
+      <c r="AD548">
+        <v>1</v>
+      </c>
+      <c r="AE548">
+        <v>1</v>
+      </c>
+      <c r="AF548">
+        <v>1</v>
+      </c>
+      <c r="AG548">
+        <v>1</v>
+      </c>
+      <c r="AH548">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="549" spans="1:34">
+      <c r="A549">
+        <v>2</v>
+      </c>
+      <c r="B549" t="s">
+        <v>765</v>
+      </c>
+      <c r="C549" t="s">
+        <v>940</v>
+      </c>
+      <c r="D549" t="s">
+        <v>961</v>
+      </c>
+      <c r="E549" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F549" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G549">
+        <v>1</v>
+      </c>
+      <c r="H549">
+        <v>1</v>
+      </c>
+      <c r="I549">
+        <v>1</v>
+      </c>
+      <c r="J549">
+        <v>1</v>
+      </c>
+      <c r="K549">
+        <v>1</v>
+      </c>
+      <c r="L549">
+        <v>1</v>
+      </c>
+      <c r="M549">
+        <v>1</v>
+      </c>
+      <c r="N549">
+        <v>1</v>
+      </c>
+      <c r="O549">
+        <v>1</v>
+      </c>
+      <c r="P549">
+        <v>1</v>
+      </c>
+      <c r="Q549">
+        <v>1</v>
+      </c>
+      <c r="R549">
+        <v>1</v>
+      </c>
+      <c r="S549">
+        <v>1</v>
+      </c>
+      <c r="T549">
+        <v>1</v>
+      </c>
+      <c r="U549">
+        <v>1</v>
+      </c>
+      <c r="V549">
+        <v>1</v>
+      </c>
+      <c r="W549">
+        <v>1</v>
+      </c>
+      <c r="X549">
+        <v>1</v>
+      </c>
+      <c r="Y549">
+        <v>1</v>
+      </c>
+      <c r="Z549">
+        <v>1</v>
+      </c>
+      <c r="AA549">
+        <v>1</v>
+      </c>
+      <c r="AB549">
+        <v>1</v>
+      </c>
+      <c r="AC549">
+        <v>1</v>
+      </c>
+      <c r="AD549">
+        <v>1</v>
+      </c>
+      <c r="AE549">
+        <v>1</v>
+      </c>
+      <c r="AF549">
+        <v>1</v>
+      </c>
+      <c r="AG549">
+        <v>1</v>
+      </c>
+      <c r="AH549">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="550" spans="1:34">
+      <c r="A550">
+        <v>1</v>
+      </c>
+      <c r="B550" t="s">
+        <v>765</v>
+      </c>
+      <c r="C550" t="s">
+        <v>940</v>
+      </c>
+      <c r="D550" t="s">
+        <v>964</v>
+      </c>
+      <c r="E550" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F550" t="s">
+        <v>590</v>
+      </c>
+      <c r="G550">
+        <v>0.95</v>
+      </c>
+      <c r="H550">
+        <v>0.95</v>
+      </c>
+      <c r="I550">
+        <v>0.95</v>
+      </c>
+      <c r="J550">
+        <v>0.95</v>
+      </c>
+      <c r="K550">
+        <v>0.95</v>
+      </c>
+      <c r="L550">
+        <v>0.95</v>
+      </c>
+      <c r="M550">
+        <v>0.95</v>
+      </c>
+      <c r="N550">
+        <v>0.95</v>
+      </c>
+      <c r="O550">
+        <v>0.95</v>
+      </c>
+      <c r="P550">
+        <v>0.95</v>
+      </c>
+      <c r="Q550">
+        <v>0.95</v>
+      </c>
+      <c r="R550">
+        <v>0.95</v>
+      </c>
+      <c r="S550">
+        <v>0.95</v>
+      </c>
+      <c r="T550">
+        <v>0.95</v>
+      </c>
+      <c r="U550">
+        <v>0.95</v>
+      </c>
+      <c r="V550">
+        <v>0.95</v>
+      </c>
+      <c r="W550">
+        <v>0.95</v>
+      </c>
+      <c r="X550">
+        <v>0.95</v>
+      </c>
+      <c r="Y550">
+        <v>0.95</v>
+      </c>
+      <c r="Z550">
+        <v>0.95</v>
+      </c>
+      <c r="AA550">
+        <v>0.95</v>
+      </c>
+      <c r="AB550">
+        <v>0.95</v>
+      </c>
+      <c r="AC550">
+        <v>0.95</v>
+      </c>
+      <c r="AD550">
+        <v>0.95</v>
+      </c>
+      <c r="AE550">
+        <v>0.95</v>
+      </c>
+      <c r="AF550">
+        <v>0.95</v>
+      </c>
+      <c r="AG550">
+        <v>0.95</v>
+      </c>
+      <c r="AH550">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="551" spans="1:34">
+      <c r="A551">
+        <v>2</v>
+      </c>
+      <c r="B551" t="s">
+        <v>765</v>
+      </c>
+      <c r="C551" t="s">
+        <v>940</v>
+      </c>
+      <c r="D551" t="s">
+        <v>976</v>
+      </c>
+      <c r="E551" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F551" t="s">
+        <v>590</v>
+      </c>
+      <c r="G551">
+        <v>0.95</v>
+      </c>
+      <c r="H551">
+        <v>0.95</v>
+      </c>
+      <c r="I551">
+        <v>0.95</v>
+      </c>
+      <c r="J551">
+        <v>0.95</v>
+      </c>
+      <c r="K551">
+        <v>0.95</v>
+      </c>
+      <c r="L551">
+        <v>0.95</v>
+      </c>
+      <c r="M551">
+        <v>0.95</v>
+      </c>
+      <c r="N551">
+        <v>0.95</v>
+      </c>
+      <c r="O551">
+        <v>0.95</v>
+      </c>
+      <c r="P551">
+        <v>0.95</v>
+      </c>
+      <c r="Q551">
+        <v>0.95</v>
+      </c>
+      <c r="R551">
+        <v>0.95</v>
+      </c>
+      <c r="S551">
+        <v>0.95</v>
+      </c>
+      <c r="T551">
+        <v>0.95</v>
+      </c>
+      <c r="U551">
+        <v>0.95</v>
+      </c>
+      <c r="V551">
+        <v>0.95</v>
+      </c>
+      <c r="W551">
+        <v>0.95</v>
+      </c>
+      <c r="X551">
+        <v>0.95</v>
+      </c>
+      <c r="Y551">
+        <v>0.95</v>
+      </c>
+      <c r="Z551">
+        <v>0.95</v>
+      </c>
+      <c r="AA551">
+        <v>0.95</v>
+      </c>
+      <c r="AB551">
+        <v>0.95</v>
+      </c>
+      <c r="AC551">
+        <v>0.95</v>
+      </c>
+      <c r="AD551">
+        <v>0.95</v>
+      </c>
+      <c r="AE551">
+        <v>0.95</v>
+      </c>
+      <c r="AF551">
+        <v>0.95</v>
+      </c>
+      <c r="AG551">
+        <v>0.95</v>
+      </c>
+      <c r="AH551">
         <v>0.95</v>
       </c>
     </row>

--- a/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Projections_COMPLETED.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Projections_COMPLETED.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4415" uniqueCount="1254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4175" uniqueCount="1254">
   <si>
     <t>Mode.Operation</t>
   </si>
@@ -18708,7 +18708,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH551"/>
+  <dimension ref="A1:AH503"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:34">
@@ -71020,4998 +71020,6 @@
         <v>0.95</v>
       </c>
       <c r="AH503">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="504" spans="1:34">
-      <c r="A504">
-        <v>1</v>
-      </c>
-      <c r="B504" t="s">
-        <v>750</v>
-      </c>
-      <c r="C504" t="s">
-        <v>925</v>
-      </c>
-      <c r="D504" t="s">
-        <v>395</v>
-      </c>
-      <c r="E504" t="s">
-        <v>534</v>
-      </c>
-      <c r="F504" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G504">
-        <v>1</v>
-      </c>
-      <c r="H504">
-        <v>1</v>
-      </c>
-      <c r="I504">
-        <v>1</v>
-      </c>
-      <c r="J504">
-        <v>1</v>
-      </c>
-      <c r="K504">
-        <v>1</v>
-      </c>
-      <c r="L504">
-        <v>1</v>
-      </c>
-      <c r="M504">
-        <v>1</v>
-      </c>
-      <c r="N504">
-        <v>1</v>
-      </c>
-      <c r="O504">
-        <v>1</v>
-      </c>
-      <c r="P504">
-        <v>1</v>
-      </c>
-      <c r="Q504">
-        <v>1</v>
-      </c>
-      <c r="R504">
-        <v>1</v>
-      </c>
-      <c r="S504">
-        <v>1</v>
-      </c>
-      <c r="T504">
-        <v>1</v>
-      </c>
-      <c r="U504">
-        <v>1</v>
-      </c>
-      <c r="V504">
-        <v>1</v>
-      </c>
-      <c r="W504">
-        <v>1</v>
-      </c>
-      <c r="X504">
-        <v>1</v>
-      </c>
-      <c r="Y504">
-        <v>1</v>
-      </c>
-      <c r="Z504">
-        <v>1</v>
-      </c>
-      <c r="AA504">
-        <v>1</v>
-      </c>
-      <c r="AB504">
-        <v>1</v>
-      </c>
-      <c r="AC504">
-        <v>1</v>
-      </c>
-      <c r="AD504">
-        <v>1</v>
-      </c>
-      <c r="AE504">
-        <v>1</v>
-      </c>
-      <c r="AF504">
-        <v>1</v>
-      </c>
-      <c r="AG504">
-        <v>1</v>
-      </c>
-      <c r="AH504">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="505" spans="1:34">
-      <c r="A505">
-        <v>1</v>
-      </c>
-      <c r="B505" t="s">
-        <v>750</v>
-      </c>
-      <c r="C505" t="s">
-        <v>925</v>
-      </c>
-      <c r="D505" t="s">
-        <v>954</v>
-      </c>
-      <c r="E505" t="s">
-        <v>994</v>
-      </c>
-      <c r="F505" t="s">
-        <v>590</v>
-      </c>
-      <c r="G505">
-        <v>1</v>
-      </c>
-      <c r="H505">
-        <v>1</v>
-      </c>
-      <c r="I505">
-        <v>1</v>
-      </c>
-      <c r="J505">
-        <v>1</v>
-      </c>
-      <c r="K505">
-        <v>1</v>
-      </c>
-      <c r="L505">
-        <v>1</v>
-      </c>
-      <c r="M505">
-        <v>1</v>
-      </c>
-      <c r="N505">
-        <v>1</v>
-      </c>
-      <c r="O505">
-        <v>1</v>
-      </c>
-      <c r="P505">
-        <v>1</v>
-      </c>
-      <c r="Q505">
-        <v>1</v>
-      </c>
-      <c r="R505">
-        <v>1</v>
-      </c>
-      <c r="S505">
-        <v>1</v>
-      </c>
-      <c r="T505">
-        <v>1</v>
-      </c>
-      <c r="U505">
-        <v>1</v>
-      </c>
-      <c r="V505">
-        <v>1</v>
-      </c>
-      <c r="W505">
-        <v>1</v>
-      </c>
-      <c r="X505">
-        <v>1</v>
-      </c>
-      <c r="Y505">
-        <v>1</v>
-      </c>
-      <c r="Z505">
-        <v>1</v>
-      </c>
-      <c r="AA505">
-        <v>1</v>
-      </c>
-      <c r="AB505">
-        <v>1</v>
-      </c>
-      <c r="AC505">
-        <v>1</v>
-      </c>
-      <c r="AD505">
-        <v>1</v>
-      </c>
-      <c r="AE505">
-        <v>1</v>
-      </c>
-      <c r="AF505">
-        <v>1</v>
-      </c>
-      <c r="AG505">
-        <v>1</v>
-      </c>
-      <c r="AH505">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="506" spans="1:34">
-      <c r="A506">
-        <v>1</v>
-      </c>
-      <c r="B506" t="s">
-        <v>751</v>
-      </c>
-      <c r="C506" t="s">
-        <v>926</v>
-      </c>
-      <c r="D506" t="s">
-        <v>328</v>
-      </c>
-      <c r="E506" t="s">
-        <v>467</v>
-      </c>
-      <c r="F506" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G506">
-        <v>2.3376</v>
-      </c>
-      <c r="H506">
-        <v>2.3376</v>
-      </c>
-      <c r="I506">
-        <v>2.3376</v>
-      </c>
-      <c r="J506">
-        <v>2.3376</v>
-      </c>
-      <c r="K506">
-        <v>2.3376</v>
-      </c>
-      <c r="L506">
-        <v>2.3376</v>
-      </c>
-      <c r="M506">
-        <v>2.3376</v>
-      </c>
-      <c r="N506">
-        <v>2.3376</v>
-      </c>
-      <c r="O506">
-        <v>2.3376</v>
-      </c>
-      <c r="P506">
-        <v>2.3376</v>
-      </c>
-      <c r="Q506">
-        <v>2.3376</v>
-      </c>
-      <c r="R506">
-        <v>2.3376</v>
-      </c>
-      <c r="S506">
-        <v>2.3376</v>
-      </c>
-      <c r="T506">
-        <v>2.3376</v>
-      </c>
-      <c r="U506">
-        <v>2.3376</v>
-      </c>
-      <c r="V506">
-        <v>2.3376</v>
-      </c>
-      <c r="W506">
-        <v>2.3376</v>
-      </c>
-      <c r="X506">
-        <v>2.3376</v>
-      </c>
-      <c r="Y506">
-        <v>2.3376</v>
-      </c>
-      <c r="Z506">
-        <v>2.3376</v>
-      </c>
-      <c r="AA506">
-        <v>2.3376</v>
-      </c>
-      <c r="AB506">
-        <v>2.3376</v>
-      </c>
-      <c r="AC506">
-        <v>2.3376</v>
-      </c>
-      <c r="AD506">
-        <v>2.3376</v>
-      </c>
-      <c r="AE506">
-        <v>2.3376</v>
-      </c>
-      <c r="AF506">
-        <v>2.3376</v>
-      </c>
-      <c r="AG506">
-        <v>2.3376</v>
-      </c>
-      <c r="AH506">
-        <v>2.3376</v>
-      </c>
-    </row>
-    <row r="507" spans="1:34">
-      <c r="A507">
-        <v>2</v>
-      </c>
-      <c r="B507" t="s">
-        <v>751</v>
-      </c>
-      <c r="C507" t="s">
-        <v>926</v>
-      </c>
-      <c r="D507" t="s">
-        <v>329</v>
-      </c>
-      <c r="E507" t="s">
-        <v>468</v>
-      </c>
-      <c r="F507" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G507">
-        <v>2.3376</v>
-      </c>
-      <c r="H507">
-        <v>2.3376</v>
-      </c>
-      <c r="I507">
-        <v>2.3376</v>
-      </c>
-      <c r="J507">
-        <v>2.3376</v>
-      </c>
-      <c r="K507">
-        <v>2.3376</v>
-      </c>
-      <c r="L507">
-        <v>2.3376</v>
-      </c>
-      <c r="M507">
-        <v>2.3376</v>
-      </c>
-      <c r="N507">
-        <v>2.3376</v>
-      </c>
-      <c r="O507">
-        <v>2.3376</v>
-      </c>
-      <c r="P507">
-        <v>2.3376</v>
-      </c>
-      <c r="Q507">
-        <v>2.3376</v>
-      </c>
-      <c r="R507">
-        <v>2.3376</v>
-      </c>
-      <c r="S507">
-        <v>2.3376</v>
-      </c>
-      <c r="T507">
-        <v>2.3376</v>
-      </c>
-      <c r="U507">
-        <v>2.3376</v>
-      </c>
-      <c r="V507">
-        <v>2.3376</v>
-      </c>
-      <c r="W507">
-        <v>2.3376</v>
-      </c>
-      <c r="X507">
-        <v>2.3376</v>
-      </c>
-      <c r="Y507">
-        <v>2.3376</v>
-      </c>
-      <c r="Z507">
-        <v>2.3376</v>
-      </c>
-      <c r="AA507">
-        <v>2.3376</v>
-      </c>
-      <c r="AB507">
-        <v>2.3376</v>
-      </c>
-      <c r="AC507">
-        <v>2.3376</v>
-      </c>
-      <c r="AD507">
-        <v>2.3376</v>
-      </c>
-      <c r="AE507">
-        <v>2.3376</v>
-      </c>
-      <c r="AF507">
-        <v>2.3376</v>
-      </c>
-      <c r="AG507">
-        <v>2.3376</v>
-      </c>
-      <c r="AH507">
-        <v>2.3376</v>
-      </c>
-    </row>
-    <row r="508" spans="1:34">
-      <c r="A508">
-        <v>1</v>
-      </c>
-      <c r="B508" t="s">
-        <v>751</v>
-      </c>
-      <c r="C508" t="s">
-        <v>926</v>
-      </c>
-      <c r="D508" t="s">
-        <v>941</v>
-      </c>
-      <c r="E508" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F508" t="s">
-        <v>590</v>
-      </c>
-      <c r="G508">
-        <v>1</v>
-      </c>
-      <c r="H508">
-        <v>1</v>
-      </c>
-      <c r="I508">
-        <v>1</v>
-      </c>
-      <c r="J508">
-        <v>1</v>
-      </c>
-      <c r="K508">
-        <v>1</v>
-      </c>
-      <c r="L508">
-        <v>1</v>
-      </c>
-      <c r="M508">
-        <v>1</v>
-      </c>
-      <c r="N508">
-        <v>1</v>
-      </c>
-      <c r="O508">
-        <v>1</v>
-      </c>
-      <c r="P508">
-        <v>1</v>
-      </c>
-      <c r="Q508">
-        <v>1</v>
-      </c>
-      <c r="R508">
-        <v>1</v>
-      </c>
-      <c r="S508">
-        <v>1</v>
-      </c>
-      <c r="T508">
-        <v>1</v>
-      </c>
-      <c r="U508">
-        <v>1</v>
-      </c>
-      <c r="V508">
-        <v>1</v>
-      </c>
-      <c r="W508">
-        <v>1</v>
-      </c>
-      <c r="X508">
-        <v>1</v>
-      </c>
-      <c r="Y508">
-        <v>1</v>
-      </c>
-      <c r="Z508">
-        <v>1</v>
-      </c>
-      <c r="AA508">
-        <v>1</v>
-      </c>
-      <c r="AB508">
-        <v>1</v>
-      </c>
-      <c r="AC508">
-        <v>1</v>
-      </c>
-      <c r="AD508">
-        <v>1</v>
-      </c>
-      <c r="AE508">
-        <v>1</v>
-      </c>
-      <c r="AF508">
-        <v>1</v>
-      </c>
-      <c r="AG508">
-        <v>1</v>
-      </c>
-      <c r="AH508">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="509" spans="1:34">
-      <c r="A509">
-        <v>2</v>
-      </c>
-      <c r="B509" t="s">
-        <v>751</v>
-      </c>
-      <c r="C509" t="s">
-        <v>926</v>
-      </c>
-      <c r="D509" t="s">
-        <v>941</v>
-      </c>
-      <c r="E509" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F509" t="s">
-        <v>590</v>
-      </c>
-      <c r="G509">
-        <v>1</v>
-      </c>
-      <c r="H509">
-        <v>1</v>
-      </c>
-      <c r="I509">
-        <v>1</v>
-      </c>
-      <c r="J509">
-        <v>1</v>
-      </c>
-      <c r="K509">
-        <v>1</v>
-      </c>
-      <c r="L509">
-        <v>1</v>
-      </c>
-      <c r="M509">
-        <v>1</v>
-      </c>
-      <c r="N509">
-        <v>1</v>
-      </c>
-      <c r="O509">
-        <v>1</v>
-      </c>
-      <c r="P509">
-        <v>1</v>
-      </c>
-      <c r="Q509">
-        <v>1</v>
-      </c>
-      <c r="R509">
-        <v>1</v>
-      </c>
-      <c r="S509">
-        <v>1</v>
-      </c>
-      <c r="T509">
-        <v>1</v>
-      </c>
-      <c r="U509">
-        <v>1</v>
-      </c>
-      <c r="V509">
-        <v>1</v>
-      </c>
-      <c r="W509">
-        <v>1</v>
-      </c>
-      <c r="X509">
-        <v>1</v>
-      </c>
-      <c r="Y509">
-        <v>1</v>
-      </c>
-      <c r="Z509">
-        <v>1</v>
-      </c>
-      <c r="AA509">
-        <v>1</v>
-      </c>
-      <c r="AB509">
-        <v>1</v>
-      </c>
-      <c r="AC509">
-        <v>1</v>
-      </c>
-      <c r="AD509">
-        <v>1</v>
-      </c>
-      <c r="AE509">
-        <v>1</v>
-      </c>
-      <c r="AF509">
-        <v>1</v>
-      </c>
-      <c r="AG509">
-        <v>1</v>
-      </c>
-      <c r="AH509">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="510" spans="1:34">
-      <c r="A510">
-        <v>1</v>
-      </c>
-      <c r="B510" t="s">
-        <v>752</v>
-      </c>
-      <c r="C510" t="s">
-        <v>927</v>
-      </c>
-      <c r="D510" t="s">
-        <v>328</v>
-      </c>
-      <c r="E510" t="s">
-        <v>467</v>
-      </c>
-      <c r="F510" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G510">
-        <v>2.3376</v>
-      </c>
-      <c r="H510">
-        <v>2.3376</v>
-      </c>
-      <c r="I510">
-        <v>2.3376</v>
-      </c>
-      <c r="J510">
-        <v>2.3376</v>
-      </c>
-      <c r="K510">
-        <v>2.3376</v>
-      </c>
-      <c r="L510">
-        <v>2.3376</v>
-      </c>
-      <c r="M510">
-        <v>2.3376</v>
-      </c>
-      <c r="N510">
-        <v>2.3376</v>
-      </c>
-      <c r="O510">
-        <v>2.3376</v>
-      </c>
-      <c r="P510">
-        <v>2.3376</v>
-      </c>
-      <c r="Q510">
-        <v>2.3376</v>
-      </c>
-      <c r="R510">
-        <v>2.3376</v>
-      </c>
-      <c r="S510">
-        <v>2.3376</v>
-      </c>
-      <c r="T510">
-        <v>2.3376</v>
-      </c>
-      <c r="U510">
-        <v>2.3376</v>
-      </c>
-      <c r="V510">
-        <v>2.3376</v>
-      </c>
-      <c r="W510">
-        <v>2.3376</v>
-      </c>
-      <c r="X510">
-        <v>2.3376</v>
-      </c>
-      <c r="Y510">
-        <v>2.3376</v>
-      </c>
-      <c r="Z510">
-        <v>2.3376</v>
-      </c>
-      <c r="AA510">
-        <v>2.3376</v>
-      </c>
-      <c r="AB510">
-        <v>2.3376</v>
-      </c>
-      <c r="AC510">
-        <v>2.3376</v>
-      </c>
-      <c r="AD510">
-        <v>2.3376</v>
-      </c>
-      <c r="AE510">
-        <v>2.3376</v>
-      </c>
-      <c r="AF510">
-        <v>2.3376</v>
-      </c>
-      <c r="AG510">
-        <v>2.3376</v>
-      </c>
-      <c r="AH510">
-        <v>2.3376</v>
-      </c>
-    </row>
-    <row r="511" spans="1:34">
-      <c r="A511">
-        <v>2</v>
-      </c>
-      <c r="B511" t="s">
-        <v>752</v>
-      </c>
-      <c r="C511" t="s">
-        <v>927</v>
-      </c>
-      <c r="D511" t="s">
-        <v>329</v>
-      </c>
-      <c r="E511" t="s">
-        <v>468</v>
-      </c>
-      <c r="F511" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G511">
-        <v>2.3376</v>
-      </c>
-      <c r="H511">
-        <v>2.3376</v>
-      </c>
-      <c r="I511">
-        <v>2.3376</v>
-      </c>
-      <c r="J511">
-        <v>2.3376</v>
-      </c>
-      <c r="K511">
-        <v>2.3376</v>
-      </c>
-      <c r="L511">
-        <v>2.3376</v>
-      </c>
-      <c r="M511">
-        <v>2.3376</v>
-      </c>
-      <c r="N511">
-        <v>2.3376</v>
-      </c>
-      <c r="O511">
-        <v>2.3376</v>
-      </c>
-      <c r="P511">
-        <v>2.3376</v>
-      </c>
-      <c r="Q511">
-        <v>2.3376</v>
-      </c>
-      <c r="R511">
-        <v>2.3376</v>
-      </c>
-      <c r="S511">
-        <v>2.3376</v>
-      </c>
-      <c r="T511">
-        <v>2.3376</v>
-      </c>
-      <c r="U511">
-        <v>2.3376</v>
-      </c>
-      <c r="V511">
-        <v>2.3376</v>
-      </c>
-      <c r="W511">
-        <v>2.3376</v>
-      </c>
-      <c r="X511">
-        <v>2.3376</v>
-      </c>
-      <c r="Y511">
-        <v>2.3376</v>
-      </c>
-      <c r="Z511">
-        <v>2.3376</v>
-      </c>
-      <c r="AA511">
-        <v>2.3376</v>
-      </c>
-      <c r="AB511">
-        <v>2.3376</v>
-      </c>
-      <c r="AC511">
-        <v>2.3376</v>
-      </c>
-      <c r="AD511">
-        <v>2.3376</v>
-      </c>
-      <c r="AE511">
-        <v>2.3376</v>
-      </c>
-      <c r="AF511">
-        <v>2.3376</v>
-      </c>
-      <c r="AG511">
-        <v>2.3376</v>
-      </c>
-      <c r="AH511">
-        <v>2.3376</v>
-      </c>
-    </row>
-    <row r="512" spans="1:34">
-      <c r="A512">
-        <v>1</v>
-      </c>
-      <c r="B512" t="s">
-        <v>752</v>
-      </c>
-      <c r="C512" t="s">
-        <v>927</v>
-      </c>
-      <c r="D512" t="s">
-        <v>949</v>
-      </c>
-      <c r="E512" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F512" t="s">
-        <v>590</v>
-      </c>
-      <c r="G512">
-        <v>1</v>
-      </c>
-      <c r="H512">
-        <v>1</v>
-      </c>
-      <c r="I512">
-        <v>1</v>
-      </c>
-      <c r="J512">
-        <v>1</v>
-      </c>
-      <c r="K512">
-        <v>1</v>
-      </c>
-      <c r="L512">
-        <v>1</v>
-      </c>
-      <c r="M512">
-        <v>1</v>
-      </c>
-      <c r="N512">
-        <v>1</v>
-      </c>
-      <c r="O512">
-        <v>1</v>
-      </c>
-      <c r="P512">
-        <v>1</v>
-      </c>
-      <c r="Q512">
-        <v>1</v>
-      </c>
-      <c r="R512">
-        <v>1</v>
-      </c>
-      <c r="S512">
-        <v>1</v>
-      </c>
-      <c r="T512">
-        <v>1</v>
-      </c>
-      <c r="U512">
-        <v>1</v>
-      </c>
-      <c r="V512">
-        <v>1</v>
-      </c>
-      <c r="W512">
-        <v>1</v>
-      </c>
-      <c r="X512">
-        <v>1</v>
-      </c>
-      <c r="Y512">
-        <v>1</v>
-      </c>
-      <c r="Z512">
-        <v>1</v>
-      </c>
-      <c r="AA512">
-        <v>1</v>
-      </c>
-      <c r="AB512">
-        <v>1</v>
-      </c>
-      <c r="AC512">
-        <v>1</v>
-      </c>
-      <c r="AD512">
-        <v>1</v>
-      </c>
-      <c r="AE512">
-        <v>1</v>
-      </c>
-      <c r="AF512">
-        <v>1</v>
-      </c>
-      <c r="AG512">
-        <v>1</v>
-      </c>
-      <c r="AH512">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="513" spans="1:34">
-      <c r="A513">
-        <v>2</v>
-      </c>
-      <c r="B513" t="s">
-        <v>752</v>
-      </c>
-      <c r="C513" t="s">
-        <v>927</v>
-      </c>
-      <c r="D513" t="s">
-        <v>949</v>
-      </c>
-      <c r="E513" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F513" t="s">
-        <v>590</v>
-      </c>
-      <c r="G513">
-        <v>1</v>
-      </c>
-      <c r="H513">
-        <v>1</v>
-      </c>
-      <c r="I513">
-        <v>1</v>
-      </c>
-      <c r="J513">
-        <v>1</v>
-      </c>
-      <c r="K513">
-        <v>1</v>
-      </c>
-      <c r="L513">
-        <v>1</v>
-      </c>
-      <c r="M513">
-        <v>1</v>
-      </c>
-      <c r="N513">
-        <v>1</v>
-      </c>
-      <c r="O513">
-        <v>1</v>
-      </c>
-      <c r="P513">
-        <v>1</v>
-      </c>
-      <c r="Q513">
-        <v>1</v>
-      </c>
-      <c r="R513">
-        <v>1</v>
-      </c>
-      <c r="S513">
-        <v>1</v>
-      </c>
-      <c r="T513">
-        <v>1</v>
-      </c>
-      <c r="U513">
-        <v>1</v>
-      </c>
-      <c r="V513">
-        <v>1</v>
-      </c>
-      <c r="W513">
-        <v>1</v>
-      </c>
-      <c r="X513">
-        <v>1</v>
-      </c>
-      <c r="Y513">
-        <v>1</v>
-      </c>
-      <c r="Z513">
-        <v>1</v>
-      </c>
-      <c r="AA513">
-        <v>1</v>
-      </c>
-      <c r="AB513">
-        <v>1</v>
-      </c>
-      <c r="AC513">
-        <v>1</v>
-      </c>
-      <c r="AD513">
-        <v>1</v>
-      </c>
-      <c r="AE513">
-        <v>1</v>
-      </c>
-      <c r="AF513">
-        <v>1</v>
-      </c>
-      <c r="AG513">
-        <v>1</v>
-      </c>
-      <c r="AH513">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="514" spans="1:34">
-      <c r="A514">
-        <v>1</v>
-      </c>
-      <c r="B514" t="s">
-        <v>753</v>
-      </c>
-      <c r="C514" t="s">
-        <v>928</v>
-      </c>
-      <c r="D514" t="s">
-        <v>333</v>
-      </c>
-      <c r="E514" t="s">
-        <v>472</v>
-      </c>
-      <c r="F514" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G514">
-        <v>2.8571</v>
-      </c>
-      <c r="H514">
-        <v>2.8571</v>
-      </c>
-      <c r="I514">
-        <v>2.8571</v>
-      </c>
-      <c r="J514">
-        <v>2.8571</v>
-      </c>
-      <c r="K514">
-        <v>2.8571</v>
-      </c>
-      <c r="L514">
-        <v>2.8571</v>
-      </c>
-      <c r="M514">
-        <v>2.8571</v>
-      </c>
-      <c r="N514">
-        <v>2.8571</v>
-      </c>
-      <c r="O514">
-        <v>2.8571</v>
-      </c>
-      <c r="P514">
-        <v>2.8571</v>
-      </c>
-      <c r="Q514">
-        <v>2.8571</v>
-      </c>
-      <c r="R514">
-        <v>2.8571</v>
-      </c>
-      <c r="S514">
-        <v>2.8571</v>
-      </c>
-      <c r="T514">
-        <v>2.8571</v>
-      </c>
-      <c r="U514">
-        <v>2.8571</v>
-      </c>
-      <c r="V514">
-        <v>2.8571</v>
-      </c>
-      <c r="W514">
-        <v>2.8571</v>
-      </c>
-      <c r="X514">
-        <v>2.8571</v>
-      </c>
-      <c r="Y514">
-        <v>2.8571</v>
-      </c>
-      <c r="Z514">
-        <v>2.8571</v>
-      </c>
-      <c r="AA514">
-        <v>2.8571</v>
-      </c>
-      <c r="AB514">
-        <v>2.8571</v>
-      </c>
-      <c r="AC514">
-        <v>2.8571</v>
-      </c>
-      <c r="AD514">
-        <v>2.8571</v>
-      </c>
-      <c r="AE514">
-        <v>2.8571</v>
-      </c>
-      <c r="AF514">
-        <v>2.8571</v>
-      </c>
-      <c r="AG514">
-        <v>2.8571</v>
-      </c>
-      <c r="AH514">
-        <v>2.8571</v>
-      </c>
-    </row>
-    <row r="515" spans="1:34">
-      <c r="A515">
-        <v>2</v>
-      </c>
-      <c r="B515" t="s">
-        <v>753</v>
-      </c>
-      <c r="C515" t="s">
-        <v>928</v>
-      </c>
-      <c r="D515" t="s">
-        <v>336</v>
-      </c>
-      <c r="E515" t="s">
-        <v>475</v>
-      </c>
-      <c r="F515" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G515">
-        <v>2.8571</v>
-      </c>
-      <c r="H515">
-        <v>2.8571</v>
-      </c>
-      <c r="I515">
-        <v>2.8571</v>
-      </c>
-      <c r="J515">
-        <v>2.8571</v>
-      </c>
-      <c r="K515">
-        <v>2.8571</v>
-      </c>
-      <c r="L515">
-        <v>2.8571</v>
-      </c>
-      <c r="M515">
-        <v>2.8571</v>
-      </c>
-      <c r="N515">
-        <v>2.8571</v>
-      </c>
-      <c r="O515">
-        <v>2.8571</v>
-      </c>
-      <c r="P515">
-        <v>2.8571</v>
-      </c>
-      <c r="Q515">
-        <v>2.8571</v>
-      </c>
-      <c r="R515">
-        <v>2.8571</v>
-      </c>
-      <c r="S515">
-        <v>2.8571</v>
-      </c>
-      <c r="T515">
-        <v>2.8571</v>
-      </c>
-      <c r="U515">
-        <v>2.8571</v>
-      </c>
-      <c r="V515">
-        <v>2.8571</v>
-      </c>
-      <c r="W515">
-        <v>2.8571</v>
-      </c>
-      <c r="X515">
-        <v>2.8571</v>
-      </c>
-      <c r="Y515">
-        <v>2.8571</v>
-      </c>
-      <c r="Z515">
-        <v>2.8571</v>
-      </c>
-      <c r="AA515">
-        <v>2.8571</v>
-      </c>
-      <c r="AB515">
-        <v>2.8571</v>
-      </c>
-      <c r="AC515">
-        <v>2.8571</v>
-      </c>
-      <c r="AD515">
-        <v>2.8571</v>
-      </c>
-      <c r="AE515">
-        <v>2.8571</v>
-      </c>
-      <c r="AF515">
-        <v>2.8571</v>
-      </c>
-      <c r="AG515">
-        <v>2.8571</v>
-      </c>
-      <c r="AH515">
-        <v>2.8571</v>
-      </c>
-    </row>
-    <row r="516" spans="1:34">
-      <c r="A516">
-        <v>1</v>
-      </c>
-      <c r="B516" t="s">
-        <v>753</v>
-      </c>
-      <c r="C516" t="s">
-        <v>928</v>
-      </c>
-      <c r="D516" t="s">
-        <v>949</v>
-      </c>
-      <c r="E516" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F516" t="s">
-        <v>590</v>
-      </c>
-      <c r="G516">
-        <v>1</v>
-      </c>
-      <c r="H516">
-        <v>1</v>
-      </c>
-      <c r="I516">
-        <v>1</v>
-      </c>
-      <c r="J516">
-        <v>1</v>
-      </c>
-      <c r="K516">
-        <v>1</v>
-      </c>
-      <c r="L516">
-        <v>1</v>
-      </c>
-      <c r="M516">
-        <v>1</v>
-      </c>
-      <c r="N516">
-        <v>1</v>
-      </c>
-      <c r="O516">
-        <v>1</v>
-      </c>
-      <c r="P516">
-        <v>1</v>
-      </c>
-      <c r="Q516">
-        <v>1</v>
-      </c>
-      <c r="R516">
-        <v>1</v>
-      </c>
-      <c r="S516">
-        <v>1</v>
-      </c>
-      <c r="T516">
-        <v>1</v>
-      </c>
-      <c r="U516">
-        <v>1</v>
-      </c>
-      <c r="V516">
-        <v>1</v>
-      </c>
-      <c r="W516">
-        <v>1</v>
-      </c>
-      <c r="X516">
-        <v>1</v>
-      </c>
-      <c r="Y516">
-        <v>1</v>
-      </c>
-      <c r="Z516">
-        <v>1</v>
-      </c>
-      <c r="AA516">
-        <v>1</v>
-      </c>
-      <c r="AB516">
-        <v>1</v>
-      </c>
-      <c r="AC516">
-        <v>1</v>
-      </c>
-      <c r="AD516">
-        <v>1</v>
-      </c>
-      <c r="AE516">
-        <v>1</v>
-      </c>
-      <c r="AF516">
-        <v>1</v>
-      </c>
-      <c r="AG516">
-        <v>1</v>
-      </c>
-      <c r="AH516">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="517" spans="1:34">
-      <c r="A517">
-        <v>2</v>
-      </c>
-      <c r="B517" t="s">
-        <v>753</v>
-      </c>
-      <c r="C517" t="s">
-        <v>928</v>
-      </c>
-      <c r="D517" t="s">
-        <v>949</v>
-      </c>
-      <c r="E517" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F517" t="s">
-        <v>590</v>
-      </c>
-      <c r="G517">
-        <v>1</v>
-      </c>
-      <c r="H517">
-        <v>1</v>
-      </c>
-      <c r="I517">
-        <v>1</v>
-      </c>
-      <c r="J517">
-        <v>1</v>
-      </c>
-      <c r="K517">
-        <v>1</v>
-      </c>
-      <c r="L517">
-        <v>1</v>
-      </c>
-      <c r="M517">
-        <v>1</v>
-      </c>
-      <c r="N517">
-        <v>1</v>
-      </c>
-      <c r="O517">
-        <v>1</v>
-      </c>
-      <c r="P517">
-        <v>1</v>
-      </c>
-      <c r="Q517">
-        <v>1</v>
-      </c>
-      <c r="R517">
-        <v>1</v>
-      </c>
-      <c r="S517">
-        <v>1</v>
-      </c>
-      <c r="T517">
-        <v>1</v>
-      </c>
-      <c r="U517">
-        <v>1</v>
-      </c>
-      <c r="V517">
-        <v>1</v>
-      </c>
-      <c r="W517">
-        <v>1</v>
-      </c>
-      <c r="X517">
-        <v>1</v>
-      </c>
-      <c r="Y517">
-        <v>1</v>
-      </c>
-      <c r="Z517">
-        <v>1</v>
-      </c>
-      <c r="AA517">
-        <v>1</v>
-      </c>
-      <c r="AB517">
-        <v>1</v>
-      </c>
-      <c r="AC517">
-        <v>1</v>
-      </c>
-      <c r="AD517">
-        <v>1</v>
-      </c>
-      <c r="AE517">
-        <v>1</v>
-      </c>
-      <c r="AF517">
-        <v>1</v>
-      </c>
-      <c r="AG517">
-        <v>1</v>
-      </c>
-      <c r="AH517">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="518" spans="1:34">
-      <c r="A518">
-        <v>1</v>
-      </c>
-      <c r="B518" t="s">
-        <v>754</v>
-      </c>
-      <c r="C518" t="s">
-        <v>929</v>
-      </c>
-      <c r="D518" t="s">
-        <v>333</v>
-      </c>
-      <c r="E518" t="s">
-        <v>472</v>
-      </c>
-      <c r="F518" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G518">
-        <v>2.88</v>
-      </c>
-      <c r="H518">
-        <v>2.88</v>
-      </c>
-      <c r="I518">
-        <v>2.88</v>
-      </c>
-      <c r="J518">
-        <v>2.88</v>
-      </c>
-      <c r="K518">
-        <v>2.88</v>
-      </c>
-      <c r="L518">
-        <v>2.88</v>
-      </c>
-      <c r="M518">
-        <v>2.88</v>
-      </c>
-      <c r="N518">
-        <v>2.88</v>
-      </c>
-      <c r="O518">
-        <v>2.88</v>
-      </c>
-      <c r="P518">
-        <v>2.88</v>
-      </c>
-      <c r="Q518">
-        <v>2.88</v>
-      </c>
-      <c r="R518">
-        <v>2.88</v>
-      </c>
-      <c r="S518">
-        <v>2.88</v>
-      </c>
-      <c r="T518">
-        <v>2.88</v>
-      </c>
-      <c r="U518">
-        <v>2.88</v>
-      </c>
-      <c r="V518">
-        <v>2.88</v>
-      </c>
-      <c r="W518">
-        <v>2.88</v>
-      </c>
-      <c r="X518">
-        <v>2.88</v>
-      </c>
-      <c r="Y518">
-        <v>2.88</v>
-      </c>
-      <c r="Z518">
-        <v>2.88</v>
-      </c>
-      <c r="AA518">
-        <v>2.88</v>
-      </c>
-      <c r="AB518">
-        <v>2.88</v>
-      </c>
-      <c r="AC518">
-        <v>2.88</v>
-      </c>
-      <c r="AD518">
-        <v>2.88</v>
-      </c>
-      <c r="AE518">
-        <v>2.88</v>
-      </c>
-      <c r="AF518">
-        <v>2.88</v>
-      </c>
-      <c r="AG518">
-        <v>2.88</v>
-      </c>
-      <c r="AH518">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="519" spans="1:34">
-      <c r="A519">
-        <v>2</v>
-      </c>
-      <c r="B519" t="s">
-        <v>754</v>
-      </c>
-      <c r="C519" t="s">
-        <v>929</v>
-      </c>
-      <c r="D519" t="s">
-        <v>336</v>
-      </c>
-      <c r="E519" t="s">
-        <v>475</v>
-      </c>
-      <c r="F519" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G519">
-        <v>2.88</v>
-      </c>
-      <c r="H519">
-        <v>2.88</v>
-      </c>
-      <c r="I519">
-        <v>2.88</v>
-      </c>
-      <c r="J519">
-        <v>2.88</v>
-      </c>
-      <c r="K519">
-        <v>2.88</v>
-      </c>
-      <c r="L519">
-        <v>2.88</v>
-      </c>
-      <c r="M519">
-        <v>2.88</v>
-      </c>
-      <c r="N519">
-        <v>2.88</v>
-      </c>
-      <c r="O519">
-        <v>2.88</v>
-      </c>
-      <c r="P519">
-        <v>2.88</v>
-      </c>
-      <c r="Q519">
-        <v>2.88</v>
-      </c>
-      <c r="R519">
-        <v>2.88</v>
-      </c>
-      <c r="S519">
-        <v>2.88</v>
-      </c>
-      <c r="T519">
-        <v>2.88</v>
-      </c>
-      <c r="U519">
-        <v>2.88</v>
-      </c>
-      <c r="V519">
-        <v>2.88</v>
-      </c>
-      <c r="W519">
-        <v>2.88</v>
-      </c>
-      <c r="X519">
-        <v>2.88</v>
-      </c>
-      <c r="Y519">
-        <v>2.88</v>
-      </c>
-      <c r="Z519">
-        <v>2.88</v>
-      </c>
-      <c r="AA519">
-        <v>2.88</v>
-      </c>
-      <c r="AB519">
-        <v>2.88</v>
-      </c>
-      <c r="AC519">
-        <v>2.88</v>
-      </c>
-      <c r="AD519">
-        <v>2.88</v>
-      </c>
-      <c r="AE519">
-        <v>2.88</v>
-      </c>
-      <c r="AF519">
-        <v>2.88</v>
-      </c>
-      <c r="AG519">
-        <v>2.88</v>
-      </c>
-      <c r="AH519">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="520" spans="1:34">
-      <c r="A520">
-        <v>1</v>
-      </c>
-      <c r="B520" t="s">
-        <v>754</v>
-      </c>
-      <c r="C520" t="s">
-        <v>929</v>
-      </c>
-      <c r="D520" t="s">
-        <v>950</v>
-      </c>
-      <c r="E520" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F520" t="s">
-        <v>590</v>
-      </c>
-      <c r="G520">
-        <v>1</v>
-      </c>
-      <c r="H520">
-        <v>1</v>
-      </c>
-      <c r="I520">
-        <v>1</v>
-      </c>
-      <c r="J520">
-        <v>1</v>
-      </c>
-      <c r="K520">
-        <v>1</v>
-      </c>
-      <c r="L520">
-        <v>1</v>
-      </c>
-      <c r="M520">
-        <v>1</v>
-      </c>
-      <c r="N520">
-        <v>1</v>
-      </c>
-      <c r="O520">
-        <v>1</v>
-      </c>
-      <c r="P520">
-        <v>1</v>
-      </c>
-      <c r="Q520">
-        <v>1</v>
-      </c>
-      <c r="R520">
-        <v>1</v>
-      </c>
-      <c r="S520">
-        <v>1</v>
-      </c>
-      <c r="T520">
-        <v>1</v>
-      </c>
-      <c r="U520">
-        <v>1</v>
-      </c>
-      <c r="V520">
-        <v>1</v>
-      </c>
-      <c r="W520">
-        <v>1</v>
-      </c>
-      <c r="X520">
-        <v>1</v>
-      </c>
-      <c r="Y520">
-        <v>1</v>
-      </c>
-      <c r="Z520">
-        <v>1</v>
-      </c>
-      <c r="AA520">
-        <v>1</v>
-      </c>
-      <c r="AB520">
-        <v>1</v>
-      </c>
-      <c r="AC520">
-        <v>1</v>
-      </c>
-      <c r="AD520">
-        <v>1</v>
-      </c>
-      <c r="AE520">
-        <v>1</v>
-      </c>
-      <c r="AF520">
-        <v>1</v>
-      </c>
-      <c r="AG520">
-        <v>1</v>
-      </c>
-      <c r="AH520">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="521" spans="1:34">
-      <c r="A521">
-        <v>2</v>
-      </c>
-      <c r="B521" t="s">
-        <v>754</v>
-      </c>
-      <c r="C521" t="s">
-        <v>929</v>
-      </c>
-      <c r="D521" t="s">
-        <v>950</v>
-      </c>
-      <c r="E521" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F521" t="s">
-        <v>590</v>
-      </c>
-      <c r="G521">
-        <v>1</v>
-      </c>
-      <c r="H521">
-        <v>1</v>
-      </c>
-      <c r="I521">
-        <v>1</v>
-      </c>
-      <c r="J521">
-        <v>1</v>
-      </c>
-      <c r="K521">
-        <v>1</v>
-      </c>
-      <c r="L521">
-        <v>1</v>
-      </c>
-      <c r="M521">
-        <v>1</v>
-      </c>
-      <c r="N521">
-        <v>1</v>
-      </c>
-      <c r="O521">
-        <v>1</v>
-      </c>
-      <c r="P521">
-        <v>1</v>
-      </c>
-      <c r="Q521">
-        <v>1</v>
-      </c>
-      <c r="R521">
-        <v>1</v>
-      </c>
-      <c r="S521">
-        <v>1</v>
-      </c>
-      <c r="T521">
-        <v>1</v>
-      </c>
-      <c r="U521">
-        <v>1</v>
-      </c>
-      <c r="V521">
-        <v>1</v>
-      </c>
-      <c r="W521">
-        <v>1</v>
-      </c>
-      <c r="X521">
-        <v>1</v>
-      </c>
-      <c r="Y521">
-        <v>1</v>
-      </c>
-      <c r="Z521">
-        <v>1</v>
-      </c>
-      <c r="AA521">
-        <v>1</v>
-      </c>
-      <c r="AB521">
-        <v>1</v>
-      </c>
-      <c r="AC521">
-        <v>1</v>
-      </c>
-      <c r="AD521">
-        <v>1</v>
-      </c>
-      <c r="AE521">
-        <v>1</v>
-      </c>
-      <c r="AF521">
-        <v>1</v>
-      </c>
-      <c r="AG521">
-        <v>1</v>
-      </c>
-      <c r="AH521">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="522" spans="1:34">
-      <c r="A522">
-        <v>1</v>
-      </c>
-      <c r="B522" t="s">
-        <v>755</v>
-      </c>
-      <c r="C522" t="s">
-        <v>930</v>
-      </c>
-      <c r="D522" t="s">
-        <v>393</v>
-      </c>
-      <c r="E522" t="s">
-        <v>532</v>
-      </c>
-      <c r="F522" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G522">
-        <v>1</v>
-      </c>
-      <c r="H522">
-        <v>1</v>
-      </c>
-      <c r="I522">
-        <v>1</v>
-      </c>
-      <c r="J522">
-        <v>1</v>
-      </c>
-      <c r="K522">
-        <v>1</v>
-      </c>
-      <c r="L522">
-        <v>1</v>
-      </c>
-      <c r="M522">
-        <v>1</v>
-      </c>
-      <c r="N522">
-        <v>1</v>
-      </c>
-      <c r="O522">
-        <v>1</v>
-      </c>
-      <c r="P522">
-        <v>1</v>
-      </c>
-      <c r="Q522">
-        <v>1</v>
-      </c>
-      <c r="R522">
-        <v>1</v>
-      </c>
-      <c r="S522">
-        <v>1</v>
-      </c>
-      <c r="T522">
-        <v>1</v>
-      </c>
-      <c r="U522">
-        <v>1</v>
-      </c>
-      <c r="V522">
-        <v>1</v>
-      </c>
-      <c r="W522">
-        <v>1</v>
-      </c>
-      <c r="X522">
-        <v>1</v>
-      </c>
-      <c r="Y522">
-        <v>1</v>
-      </c>
-      <c r="Z522">
-        <v>1</v>
-      </c>
-      <c r="AA522">
-        <v>1</v>
-      </c>
-      <c r="AB522">
-        <v>1</v>
-      </c>
-      <c r="AC522">
-        <v>1</v>
-      </c>
-      <c r="AD522">
-        <v>1</v>
-      </c>
-      <c r="AE522">
-        <v>1</v>
-      </c>
-      <c r="AF522">
-        <v>1</v>
-      </c>
-      <c r="AG522">
-        <v>1</v>
-      </c>
-      <c r="AH522">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="523" spans="1:34">
-      <c r="A523">
-        <v>1</v>
-      </c>
-      <c r="B523" t="s">
-        <v>755</v>
-      </c>
-      <c r="C523" t="s">
-        <v>930</v>
-      </c>
-      <c r="D523" t="s">
-        <v>952</v>
-      </c>
-      <c r="E523" t="s">
-        <v>992</v>
-      </c>
-      <c r="F523" t="s">
-        <v>590</v>
-      </c>
-      <c r="G523">
-        <v>1</v>
-      </c>
-      <c r="H523">
-        <v>1</v>
-      </c>
-      <c r="I523">
-        <v>1</v>
-      </c>
-      <c r="J523">
-        <v>1</v>
-      </c>
-      <c r="K523">
-        <v>1</v>
-      </c>
-      <c r="L523">
-        <v>1</v>
-      </c>
-      <c r="M523">
-        <v>1</v>
-      </c>
-      <c r="N523">
-        <v>1</v>
-      </c>
-      <c r="O523">
-        <v>1</v>
-      </c>
-      <c r="P523">
-        <v>1</v>
-      </c>
-      <c r="Q523">
-        <v>1</v>
-      </c>
-      <c r="R523">
-        <v>1</v>
-      </c>
-      <c r="S523">
-        <v>1</v>
-      </c>
-      <c r="T523">
-        <v>1</v>
-      </c>
-      <c r="U523">
-        <v>1</v>
-      </c>
-      <c r="V523">
-        <v>1</v>
-      </c>
-      <c r="W523">
-        <v>1</v>
-      </c>
-      <c r="X523">
-        <v>1</v>
-      </c>
-      <c r="Y523">
-        <v>1</v>
-      </c>
-      <c r="Z523">
-        <v>1</v>
-      </c>
-      <c r="AA523">
-        <v>1</v>
-      </c>
-      <c r="AB523">
-        <v>1</v>
-      </c>
-      <c r="AC523">
-        <v>1</v>
-      </c>
-      <c r="AD523">
-        <v>1</v>
-      </c>
-      <c r="AE523">
-        <v>1</v>
-      </c>
-      <c r="AF523">
-        <v>1</v>
-      </c>
-      <c r="AG523">
-        <v>1</v>
-      </c>
-      <c r="AH523">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="524" spans="1:34">
-      <c r="A524">
-        <v>1</v>
-      </c>
-      <c r="B524" t="s">
-        <v>756</v>
-      </c>
-      <c r="C524" t="s">
-        <v>931</v>
-      </c>
-      <c r="D524" t="s">
-        <v>394</v>
-      </c>
-      <c r="E524" t="s">
-        <v>533</v>
-      </c>
-      <c r="F524" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G524">
-        <v>1</v>
-      </c>
-      <c r="H524">
-        <v>1</v>
-      </c>
-      <c r="I524">
-        <v>1</v>
-      </c>
-      <c r="J524">
-        <v>1</v>
-      </c>
-      <c r="K524">
-        <v>1</v>
-      </c>
-      <c r="L524">
-        <v>1</v>
-      </c>
-      <c r="M524">
-        <v>1</v>
-      </c>
-      <c r="N524">
-        <v>1</v>
-      </c>
-      <c r="O524">
-        <v>1</v>
-      </c>
-      <c r="P524">
-        <v>1</v>
-      </c>
-      <c r="Q524">
-        <v>1</v>
-      </c>
-      <c r="R524">
-        <v>1</v>
-      </c>
-      <c r="S524">
-        <v>1</v>
-      </c>
-      <c r="T524">
-        <v>1</v>
-      </c>
-      <c r="U524">
-        <v>1</v>
-      </c>
-      <c r="V524">
-        <v>1</v>
-      </c>
-      <c r="W524">
-        <v>1</v>
-      </c>
-      <c r="X524">
-        <v>1</v>
-      </c>
-      <c r="Y524">
-        <v>1</v>
-      </c>
-      <c r="Z524">
-        <v>1</v>
-      </c>
-      <c r="AA524">
-        <v>1</v>
-      </c>
-      <c r="AB524">
-        <v>1</v>
-      </c>
-      <c r="AC524">
-        <v>1</v>
-      </c>
-      <c r="AD524">
-        <v>1</v>
-      </c>
-      <c r="AE524">
-        <v>1</v>
-      </c>
-      <c r="AF524">
-        <v>1</v>
-      </c>
-      <c r="AG524">
-        <v>1</v>
-      </c>
-      <c r="AH524">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="525" spans="1:34">
-      <c r="A525">
-        <v>1</v>
-      </c>
-      <c r="B525" t="s">
-        <v>756</v>
-      </c>
-      <c r="C525" t="s">
-        <v>931</v>
-      </c>
-      <c r="D525" t="s">
-        <v>953</v>
-      </c>
-      <c r="E525" t="s">
-        <v>993</v>
-      </c>
-      <c r="F525" t="s">
-        <v>590</v>
-      </c>
-      <c r="G525">
-        <v>1</v>
-      </c>
-      <c r="H525">
-        <v>1</v>
-      </c>
-      <c r="I525">
-        <v>1</v>
-      </c>
-      <c r="J525">
-        <v>1</v>
-      </c>
-      <c r="K525">
-        <v>1</v>
-      </c>
-      <c r="L525">
-        <v>1</v>
-      </c>
-      <c r="M525">
-        <v>1</v>
-      </c>
-      <c r="N525">
-        <v>1</v>
-      </c>
-      <c r="O525">
-        <v>1</v>
-      </c>
-      <c r="P525">
-        <v>1</v>
-      </c>
-      <c r="Q525">
-        <v>1</v>
-      </c>
-      <c r="R525">
-        <v>1</v>
-      </c>
-      <c r="S525">
-        <v>1</v>
-      </c>
-      <c r="T525">
-        <v>1</v>
-      </c>
-      <c r="U525">
-        <v>1</v>
-      </c>
-      <c r="V525">
-        <v>1</v>
-      </c>
-      <c r="W525">
-        <v>1</v>
-      </c>
-      <c r="X525">
-        <v>1</v>
-      </c>
-      <c r="Y525">
-        <v>1</v>
-      </c>
-      <c r="Z525">
-        <v>1</v>
-      </c>
-      <c r="AA525">
-        <v>1</v>
-      </c>
-      <c r="AB525">
-        <v>1</v>
-      </c>
-      <c r="AC525">
-        <v>1</v>
-      </c>
-      <c r="AD525">
-        <v>1</v>
-      </c>
-      <c r="AE525">
-        <v>1</v>
-      </c>
-      <c r="AF525">
-        <v>1</v>
-      </c>
-      <c r="AG525">
-        <v>1</v>
-      </c>
-      <c r="AH525">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="526" spans="1:34">
-      <c r="A526">
-        <v>1</v>
-      </c>
-      <c r="B526" t="s">
-        <v>757</v>
-      </c>
-      <c r="C526" t="s">
-        <v>932</v>
-      </c>
-      <c r="D526" t="s">
-        <v>395</v>
-      </c>
-      <c r="E526" t="s">
-        <v>534</v>
-      </c>
-      <c r="F526" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G526">
-        <v>1</v>
-      </c>
-      <c r="H526">
-        <v>1</v>
-      </c>
-      <c r="I526">
-        <v>1</v>
-      </c>
-      <c r="J526">
-        <v>1</v>
-      </c>
-      <c r="K526">
-        <v>1</v>
-      </c>
-      <c r="L526">
-        <v>1</v>
-      </c>
-      <c r="M526">
-        <v>1</v>
-      </c>
-      <c r="N526">
-        <v>1</v>
-      </c>
-      <c r="O526">
-        <v>1</v>
-      </c>
-      <c r="P526">
-        <v>1</v>
-      </c>
-      <c r="Q526">
-        <v>1</v>
-      </c>
-      <c r="R526">
-        <v>1</v>
-      </c>
-      <c r="S526">
-        <v>1</v>
-      </c>
-      <c r="T526">
-        <v>1</v>
-      </c>
-      <c r="U526">
-        <v>1</v>
-      </c>
-      <c r="V526">
-        <v>1</v>
-      </c>
-      <c r="W526">
-        <v>1</v>
-      </c>
-      <c r="X526">
-        <v>1</v>
-      </c>
-      <c r="Y526">
-        <v>1</v>
-      </c>
-      <c r="Z526">
-        <v>1</v>
-      </c>
-      <c r="AA526">
-        <v>1</v>
-      </c>
-      <c r="AB526">
-        <v>1</v>
-      </c>
-      <c r="AC526">
-        <v>1</v>
-      </c>
-      <c r="AD526">
-        <v>1</v>
-      </c>
-      <c r="AE526">
-        <v>1</v>
-      </c>
-      <c r="AF526">
-        <v>1</v>
-      </c>
-      <c r="AG526">
-        <v>1</v>
-      </c>
-      <c r="AH526">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="527" spans="1:34">
-      <c r="A527">
-        <v>1</v>
-      </c>
-      <c r="B527" t="s">
-        <v>757</v>
-      </c>
-      <c r="C527" t="s">
-        <v>932</v>
-      </c>
-      <c r="D527" t="s">
-        <v>954</v>
-      </c>
-      <c r="E527" t="s">
-        <v>994</v>
-      </c>
-      <c r="F527" t="s">
-        <v>590</v>
-      </c>
-      <c r="G527">
-        <v>1</v>
-      </c>
-      <c r="H527">
-        <v>1</v>
-      </c>
-      <c r="I527">
-        <v>1</v>
-      </c>
-      <c r="J527">
-        <v>1</v>
-      </c>
-      <c r="K527">
-        <v>1</v>
-      </c>
-      <c r="L527">
-        <v>1</v>
-      </c>
-      <c r="M527">
-        <v>1</v>
-      </c>
-      <c r="N527">
-        <v>1</v>
-      </c>
-      <c r="O527">
-        <v>1</v>
-      </c>
-      <c r="P527">
-        <v>1</v>
-      </c>
-      <c r="Q527">
-        <v>1</v>
-      </c>
-      <c r="R527">
-        <v>1</v>
-      </c>
-      <c r="S527">
-        <v>1</v>
-      </c>
-      <c r="T527">
-        <v>1</v>
-      </c>
-      <c r="U527">
-        <v>1</v>
-      </c>
-      <c r="V527">
-        <v>1</v>
-      </c>
-      <c r="W527">
-        <v>1</v>
-      </c>
-      <c r="X527">
-        <v>1</v>
-      </c>
-      <c r="Y527">
-        <v>1</v>
-      </c>
-      <c r="Z527">
-        <v>1</v>
-      </c>
-      <c r="AA527">
-        <v>1</v>
-      </c>
-      <c r="AB527">
-        <v>1</v>
-      </c>
-      <c r="AC527">
-        <v>1</v>
-      </c>
-      <c r="AD527">
-        <v>1</v>
-      </c>
-      <c r="AE527">
-        <v>1</v>
-      </c>
-      <c r="AF527">
-        <v>1</v>
-      </c>
-      <c r="AG527">
-        <v>1</v>
-      </c>
-      <c r="AH527">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="528" spans="1:34">
-      <c r="A528">
-        <v>1</v>
-      </c>
-      <c r="B528" t="s">
-        <v>758</v>
-      </c>
-      <c r="C528" t="s">
-        <v>933</v>
-      </c>
-      <c r="D528" t="s">
-        <v>396</v>
-      </c>
-      <c r="E528" t="s">
-        <v>535</v>
-      </c>
-      <c r="F528" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G528">
-        <v>1</v>
-      </c>
-      <c r="H528">
-        <v>1</v>
-      </c>
-      <c r="I528">
-        <v>1</v>
-      </c>
-      <c r="J528">
-        <v>1</v>
-      </c>
-      <c r="K528">
-        <v>1</v>
-      </c>
-      <c r="L528">
-        <v>1</v>
-      </c>
-      <c r="M528">
-        <v>1</v>
-      </c>
-      <c r="N528">
-        <v>1</v>
-      </c>
-      <c r="O528">
-        <v>1</v>
-      </c>
-      <c r="P528">
-        <v>1</v>
-      </c>
-      <c r="Q528">
-        <v>1</v>
-      </c>
-      <c r="R528">
-        <v>1</v>
-      </c>
-      <c r="S528">
-        <v>1</v>
-      </c>
-      <c r="T528">
-        <v>1</v>
-      </c>
-      <c r="U528">
-        <v>1</v>
-      </c>
-      <c r="V528">
-        <v>1</v>
-      </c>
-      <c r="W528">
-        <v>1</v>
-      </c>
-      <c r="X528">
-        <v>1</v>
-      </c>
-      <c r="Y528">
-        <v>1</v>
-      </c>
-      <c r="Z528">
-        <v>1</v>
-      </c>
-      <c r="AA528">
-        <v>1</v>
-      </c>
-      <c r="AB528">
-        <v>1</v>
-      </c>
-      <c r="AC528">
-        <v>1</v>
-      </c>
-      <c r="AD528">
-        <v>1</v>
-      </c>
-      <c r="AE528">
-        <v>1</v>
-      </c>
-      <c r="AF528">
-        <v>1</v>
-      </c>
-      <c r="AG528">
-        <v>1</v>
-      </c>
-      <c r="AH528">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="529" spans="1:34">
-      <c r="A529">
-        <v>1</v>
-      </c>
-      <c r="B529" t="s">
-        <v>758</v>
-      </c>
-      <c r="C529" t="s">
-        <v>933</v>
-      </c>
-      <c r="D529" t="s">
-        <v>955</v>
-      </c>
-      <c r="E529" t="s">
-        <v>995</v>
-      </c>
-      <c r="F529" t="s">
-        <v>590</v>
-      </c>
-      <c r="G529">
-        <v>1</v>
-      </c>
-      <c r="H529">
-        <v>1</v>
-      </c>
-      <c r="I529">
-        <v>1</v>
-      </c>
-      <c r="J529">
-        <v>1</v>
-      </c>
-      <c r="K529">
-        <v>1</v>
-      </c>
-      <c r="L529">
-        <v>1</v>
-      </c>
-      <c r="M529">
-        <v>1</v>
-      </c>
-      <c r="N529">
-        <v>1</v>
-      </c>
-      <c r="O529">
-        <v>1</v>
-      </c>
-      <c r="P529">
-        <v>1</v>
-      </c>
-      <c r="Q529">
-        <v>1</v>
-      </c>
-      <c r="R529">
-        <v>1</v>
-      </c>
-      <c r="S529">
-        <v>1</v>
-      </c>
-      <c r="T529">
-        <v>1</v>
-      </c>
-      <c r="U529">
-        <v>1</v>
-      </c>
-      <c r="V529">
-        <v>1</v>
-      </c>
-      <c r="W529">
-        <v>1</v>
-      </c>
-      <c r="X529">
-        <v>1</v>
-      </c>
-      <c r="Y529">
-        <v>1</v>
-      </c>
-      <c r="Z529">
-        <v>1</v>
-      </c>
-      <c r="AA529">
-        <v>1</v>
-      </c>
-      <c r="AB529">
-        <v>1</v>
-      </c>
-      <c r="AC529">
-        <v>1</v>
-      </c>
-      <c r="AD529">
-        <v>1</v>
-      </c>
-      <c r="AE529">
-        <v>1</v>
-      </c>
-      <c r="AF529">
-        <v>1</v>
-      </c>
-      <c r="AG529">
-        <v>1</v>
-      </c>
-      <c r="AH529">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="530" spans="1:34">
-      <c r="A530">
-        <v>1</v>
-      </c>
-      <c r="B530" t="s">
-        <v>759</v>
-      </c>
-      <c r="C530" t="s">
-        <v>934</v>
-      </c>
-      <c r="D530" t="s">
-        <v>397</v>
-      </c>
-      <c r="E530" t="s">
-        <v>536</v>
-      </c>
-      <c r="F530" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G530">
-        <v>1</v>
-      </c>
-      <c r="H530">
-        <v>1</v>
-      </c>
-      <c r="I530">
-        <v>1</v>
-      </c>
-      <c r="J530">
-        <v>1</v>
-      </c>
-      <c r="K530">
-        <v>1</v>
-      </c>
-      <c r="L530">
-        <v>1</v>
-      </c>
-      <c r="M530">
-        <v>1</v>
-      </c>
-      <c r="N530">
-        <v>1</v>
-      </c>
-      <c r="O530">
-        <v>1</v>
-      </c>
-      <c r="P530">
-        <v>1</v>
-      </c>
-      <c r="Q530">
-        <v>1</v>
-      </c>
-      <c r="R530">
-        <v>1</v>
-      </c>
-      <c r="S530">
-        <v>1</v>
-      </c>
-      <c r="T530">
-        <v>1</v>
-      </c>
-      <c r="U530">
-        <v>1</v>
-      </c>
-      <c r="V530">
-        <v>1</v>
-      </c>
-      <c r="W530">
-        <v>1</v>
-      </c>
-      <c r="X530">
-        <v>1</v>
-      </c>
-      <c r="Y530">
-        <v>1</v>
-      </c>
-      <c r="Z530">
-        <v>1</v>
-      </c>
-      <c r="AA530">
-        <v>1</v>
-      </c>
-      <c r="AB530">
-        <v>1</v>
-      </c>
-      <c r="AC530">
-        <v>1</v>
-      </c>
-      <c r="AD530">
-        <v>1</v>
-      </c>
-      <c r="AE530">
-        <v>1</v>
-      </c>
-      <c r="AF530">
-        <v>1</v>
-      </c>
-      <c r="AG530">
-        <v>1</v>
-      </c>
-      <c r="AH530">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="531" spans="1:34">
-      <c r="A531">
-        <v>1</v>
-      </c>
-      <c r="B531" t="s">
-        <v>759</v>
-      </c>
-      <c r="C531" t="s">
-        <v>934</v>
-      </c>
-      <c r="D531" t="s">
-        <v>956</v>
-      </c>
-      <c r="E531" t="s">
-        <v>996</v>
-      </c>
-      <c r="F531" t="s">
-        <v>590</v>
-      </c>
-      <c r="G531">
-        <v>1</v>
-      </c>
-      <c r="H531">
-        <v>1</v>
-      </c>
-      <c r="I531">
-        <v>1</v>
-      </c>
-      <c r="J531">
-        <v>1</v>
-      </c>
-      <c r="K531">
-        <v>1</v>
-      </c>
-      <c r="L531">
-        <v>1</v>
-      </c>
-      <c r="M531">
-        <v>1</v>
-      </c>
-      <c r="N531">
-        <v>1</v>
-      </c>
-      <c r="O531">
-        <v>1</v>
-      </c>
-      <c r="P531">
-        <v>1</v>
-      </c>
-      <c r="Q531">
-        <v>1</v>
-      </c>
-      <c r="R531">
-        <v>1</v>
-      </c>
-      <c r="S531">
-        <v>1</v>
-      </c>
-      <c r="T531">
-        <v>1</v>
-      </c>
-      <c r="U531">
-        <v>1</v>
-      </c>
-      <c r="V531">
-        <v>1</v>
-      </c>
-      <c r="W531">
-        <v>1</v>
-      </c>
-      <c r="X531">
-        <v>1</v>
-      </c>
-      <c r="Y531">
-        <v>1</v>
-      </c>
-      <c r="Z531">
-        <v>1</v>
-      </c>
-      <c r="AA531">
-        <v>1</v>
-      </c>
-      <c r="AB531">
-        <v>1</v>
-      </c>
-      <c r="AC531">
-        <v>1</v>
-      </c>
-      <c r="AD531">
-        <v>1</v>
-      </c>
-      <c r="AE531">
-        <v>1</v>
-      </c>
-      <c r="AF531">
-        <v>1</v>
-      </c>
-      <c r="AG531">
-        <v>1</v>
-      </c>
-      <c r="AH531">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="532" spans="1:34">
-      <c r="A532">
-        <v>1</v>
-      </c>
-      <c r="B532" t="s">
-        <v>760</v>
-      </c>
-      <c r="C532" t="s">
-        <v>935</v>
-      </c>
-      <c r="D532" t="s">
-        <v>439</v>
-      </c>
-      <c r="E532" t="s">
-        <v>578</v>
-      </c>
-      <c r="F532" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G532">
-        <v>1</v>
-      </c>
-      <c r="H532">
-        <v>1</v>
-      </c>
-      <c r="I532">
-        <v>1</v>
-      </c>
-      <c r="J532">
-        <v>1</v>
-      </c>
-      <c r="K532">
-        <v>1</v>
-      </c>
-      <c r="L532">
-        <v>1</v>
-      </c>
-      <c r="M532">
-        <v>1</v>
-      </c>
-      <c r="N532">
-        <v>1</v>
-      </c>
-      <c r="O532">
-        <v>1</v>
-      </c>
-      <c r="P532">
-        <v>1</v>
-      </c>
-      <c r="Q532">
-        <v>1</v>
-      </c>
-      <c r="R532">
-        <v>1</v>
-      </c>
-      <c r="S532">
-        <v>1</v>
-      </c>
-      <c r="T532">
-        <v>1</v>
-      </c>
-      <c r="U532">
-        <v>1</v>
-      </c>
-      <c r="V532">
-        <v>1</v>
-      </c>
-      <c r="W532">
-        <v>1</v>
-      </c>
-      <c r="X532">
-        <v>1</v>
-      </c>
-      <c r="Y532">
-        <v>1</v>
-      </c>
-      <c r="Z532">
-        <v>1</v>
-      </c>
-      <c r="AA532">
-        <v>1</v>
-      </c>
-      <c r="AB532">
-        <v>1</v>
-      </c>
-      <c r="AC532">
-        <v>1</v>
-      </c>
-      <c r="AD532">
-        <v>1</v>
-      </c>
-      <c r="AE532">
-        <v>1</v>
-      </c>
-      <c r="AF532">
-        <v>1</v>
-      </c>
-      <c r="AG532">
-        <v>1</v>
-      </c>
-      <c r="AH532">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="533" spans="1:34">
-      <c r="A533">
-        <v>1</v>
-      </c>
-      <c r="B533" t="s">
-        <v>760</v>
-      </c>
-      <c r="C533" t="s">
-        <v>935</v>
-      </c>
-      <c r="D533" t="s">
-        <v>960</v>
-      </c>
-      <c r="E533" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F533" t="s">
-        <v>590</v>
-      </c>
-      <c r="G533">
-        <v>1</v>
-      </c>
-      <c r="H533">
-        <v>1</v>
-      </c>
-      <c r="I533">
-        <v>1</v>
-      </c>
-      <c r="J533">
-        <v>1</v>
-      </c>
-      <c r="K533">
-        <v>1</v>
-      </c>
-      <c r="L533">
-        <v>1</v>
-      </c>
-      <c r="M533">
-        <v>1</v>
-      </c>
-      <c r="N533">
-        <v>1</v>
-      </c>
-      <c r="O533">
-        <v>1</v>
-      </c>
-      <c r="P533">
-        <v>1</v>
-      </c>
-      <c r="Q533">
-        <v>1</v>
-      </c>
-      <c r="R533">
-        <v>1</v>
-      </c>
-      <c r="S533">
-        <v>1</v>
-      </c>
-      <c r="T533">
-        <v>1</v>
-      </c>
-      <c r="U533">
-        <v>1</v>
-      </c>
-      <c r="V533">
-        <v>1</v>
-      </c>
-      <c r="W533">
-        <v>1</v>
-      </c>
-      <c r="X533">
-        <v>1</v>
-      </c>
-      <c r="Y533">
-        <v>1</v>
-      </c>
-      <c r="Z533">
-        <v>1</v>
-      </c>
-      <c r="AA533">
-        <v>1</v>
-      </c>
-      <c r="AB533">
-        <v>1</v>
-      </c>
-      <c r="AC533">
-        <v>1</v>
-      </c>
-      <c r="AD533">
-        <v>1</v>
-      </c>
-      <c r="AE533">
-        <v>1</v>
-      </c>
-      <c r="AF533">
-        <v>1</v>
-      </c>
-      <c r="AG533">
-        <v>1</v>
-      </c>
-      <c r="AH533">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="534" spans="1:34">
-      <c r="A534">
-        <v>1</v>
-      </c>
-      <c r="B534" t="s">
-        <v>761</v>
-      </c>
-      <c r="C534" t="s">
-        <v>936</v>
-      </c>
-      <c r="D534" t="s">
-        <v>449</v>
-      </c>
-      <c r="E534" t="s">
-        <v>588</v>
-      </c>
-      <c r="F534" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G534">
-        <v>1</v>
-      </c>
-      <c r="H534">
-        <v>1</v>
-      </c>
-      <c r="I534">
-        <v>1</v>
-      </c>
-      <c r="J534">
-        <v>1</v>
-      </c>
-      <c r="K534">
-        <v>1</v>
-      </c>
-      <c r="L534">
-        <v>1</v>
-      </c>
-      <c r="M534">
-        <v>1</v>
-      </c>
-      <c r="N534">
-        <v>1</v>
-      </c>
-      <c r="O534">
-        <v>1</v>
-      </c>
-      <c r="P534">
-        <v>1</v>
-      </c>
-      <c r="Q534">
-        <v>1</v>
-      </c>
-      <c r="R534">
-        <v>1</v>
-      </c>
-      <c r="S534">
-        <v>1</v>
-      </c>
-      <c r="T534">
-        <v>1</v>
-      </c>
-      <c r="U534">
-        <v>1</v>
-      </c>
-      <c r="V534">
-        <v>1</v>
-      </c>
-      <c r="W534">
-        <v>1</v>
-      </c>
-      <c r="X534">
-        <v>1</v>
-      </c>
-      <c r="Y534">
-        <v>1</v>
-      </c>
-      <c r="Z534">
-        <v>1</v>
-      </c>
-      <c r="AA534">
-        <v>1</v>
-      </c>
-      <c r="AB534">
-        <v>1</v>
-      </c>
-      <c r="AC534">
-        <v>1</v>
-      </c>
-      <c r="AD534">
-        <v>1</v>
-      </c>
-      <c r="AE534">
-        <v>1</v>
-      </c>
-      <c r="AF534">
-        <v>1</v>
-      </c>
-      <c r="AG534">
-        <v>1</v>
-      </c>
-      <c r="AH534">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="535" spans="1:34">
-      <c r="A535">
-        <v>1</v>
-      </c>
-      <c r="B535" t="s">
-        <v>761</v>
-      </c>
-      <c r="C535" t="s">
-        <v>936</v>
-      </c>
-      <c r="D535" t="s">
-        <v>960</v>
-      </c>
-      <c r="E535" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F535" t="s">
-        <v>590</v>
-      </c>
-      <c r="G535">
-        <v>1</v>
-      </c>
-      <c r="H535">
-        <v>1</v>
-      </c>
-      <c r="I535">
-        <v>1</v>
-      </c>
-      <c r="J535">
-        <v>1</v>
-      </c>
-      <c r="K535">
-        <v>1</v>
-      </c>
-      <c r="L535">
-        <v>1</v>
-      </c>
-      <c r="M535">
-        <v>1</v>
-      </c>
-      <c r="N535">
-        <v>1</v>
-      </c>
-      <c r="O535">
-        <v>1</v>
-      </c>
-      <c r="P535">
-        <v>1</v>
-      </c>
-      <c r="Q535">
-        <v>1</v>
-      </c>
-      <c r="R535">
-        <v>1</v>
-      </c>
-      <c r="S535">
-        <v>1</v>
-      </c>
-      <c r="T535">
-        <v>1</v>
-      </c>
-      <c r="U535">
-        <v>1</v>
-      </c>
-      <c r="V535">
-        <v>1</v>
-      </c>
-      <c r="W535">
-        <v>1</v>
-      </c>
-      <c r="X535">
-        <v>1</v>
-      </c>
-      <c r="Y535">
-        <v>1</v>
-      </c>
-      <c r="Z535">
-        <v>1</v>
-      </c>
-      <c r="AA535">
-        <v>1</v>
-      </c>
-      <c r="AB535">
-        <v>1</v>
-      </c>
-      <c r="AC535">
-        <v>1</v>
-      </c>
-      <c r="AD535">
-        <v>1</v>
-      </c>
-      <c r="AE535">
-        <v>1</v>
-      </c>
-      <c r="AF535">
-        <v>1</v>
-      </c>
-      <c r="AG535">
-        <v>1</v>
-      </c>
-      <c r="AH535">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="536" spans="1:34">
-      <c r="A536">
-        <v>1</v>
-      </c>
-      <c r="B536" t="s">
-        <v>762</v>
-      </c>
-      <c r="C536" t="s">
-        <v>937</v>
-      </c>
-      <c r="D536" t="s">
-        <v>967</v>
-      </c>
-      <c r="E536" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F536" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G536">
-        <v>1</v>
-      </c>
-      <c r="H536">
-        <v>1</v>
-      </c>
-      <c r="I536">
-        <v>1</v>
-      </c>
-      <c r="J536">
-        <v>1</v>
-      </c>
-      <c r="K536">
-        <v>1</v>
-      </c>
-      <c r="L536">
-        <v>1</v>
-      </c>
-      <c r="M536">
-        <v>1</v>
-      </c>
-      <c r="N536">
-        <v>1</v>
-      </c>
-      <c r="O536">
-        <v>1</v>
-      </c>
-      <c r="P536">
-        <v>1</v>
-      </c>
-      <c r="Q536">
-        <v>1</v>
-      </c>
-      <c r="R536">
-        <v>1</v>
-      </c>
-      <c r="S536">
-        <v>1</v>
-      </c>
-      <c r="T536">
-        <v>1</v>
-      </c>
-      <c r="U536">
-        <v>1</v>
-      </c>
-      <c r="V536">
-        <v>1</v>
-      </c>
-      <c r="W536">
-        <v>1</v>
-      </c>
-      <c r="X536">
-        <v>1</v>
-      </c>
-      <c r="Y536">
-        <v>1</v>
-      </c>
-      <c r="Z536">
-        <v>1</v>
-      </c>
-      <c r="AA536">
-        <v>1</v>
-      </c>
-      <c r="AB536">
-        <v>1</v>
-      </c>
-      <c r="AC536">
-        <v>1</v>
-      </c>
-      <c r="AD536">
-        <v>1</v>
-      </c>
-      <c r="AE536">
-        <v>1</v>
-      </c>
-      <c r="AF536">
-        <v>1</v>
-      </c>
-      <c r="AG536">
-        <v>1</v>
-      </c>
-      <c r="AH536">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="537" spans="1:34">
-      <c r="A537">
-        <v>2</v>
-      </c>
-      <c r="B537" t="s">
-        <v>762</v>
-      </c>
-      <c r="C537" t="s">
-        <v>937</v>
-      </c>
-      <c r="D537" t="s">
-        <v>961</v>
-      </c>
-      <c r="E537" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F537" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G537">
-        <v>1</v>
-      </c>
-      <c r="H537">
-        <v>1</v>
-      </c>
-      <c r="I537">
-        <v>1</v>
-      </c>
-      <c r="J537">
-        <v>1</v>
-      </c>
-      <c r="K537">
-        <v>1</v>
-      </c>
-      <c r="L537">
-        <v>1</v>
-      </c>
-      <c r="M537">
-        <v>1</v>
-      </c>
-      <c r="N537">
-        <v>1</v>
-      </c>
-      <c r="O537">
-        <v>1</v>
-      </c>
-      <c r="P537">
-        <v>1</v>
-      </c>
-      <c r="Q537">
-        <v>1</v>
-      </c>
-      <c r="R537">
-        <v>1</v>
-      </c>
-      <c r="S537">
-        <v>1</v>
-      </c>
-      <c r="T537">
-        <v>1</v>
-      </c>
-      <c r="U537">
-        <v>1</v>
-      </c>
-      <c r="V537">
-        <v>1</v>
-      </c>
-      <c r="W537">
-        <v>1</v>
-      </c>
-      <c r="X537">
-        <v>1</v>
-      </c>
-      <c r="Y537">
-        <v>1</v>
-      </c>
-      <c r="Z537">
-        <v>1</v>
-      </c>
-      <c r="AA537">
-        <v>1</v>
-      </c>
-      <c r="AB537">
-        <v>1</v>
-      </c>
-      <c r="AC537">
-        <v>1</v>
-      </c>
-      <c r="AD537">
-        <v>1</v>
-      </c>
-      <c r="AE537">
-        <v>1</v>
-      </c>
-      <c r="AF537">
-        <v>1</v>
-      </c>
-      <c r="AG537">
-        <v>1</v>
-      </c>
-      <c r="AH537">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="538" spans="1:34">
-      <c r="A538">
-        <v>1</v>
-      </c>
-      <c r="B538" t="s">
-        <v>762</v>
-      </c>
-      <c r="C538" t="s">
-        <v>937</v>
-      </c>
-      <c r="D538" t="s">
-        <v>964</v>
-      </c>
-      <c r="E538" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F538" t="s">
-        <v>590</v>
-      </c>
-      <c r="G538">
-        <v>0.95</v>
-      </c>
-      <c r="H538">
-        <v>0.95</v>
-      </c>
-      <c r="I538">
-        <v>0.95</v>
-      </c>
-      <c r="J538">
-        <v>0.95</v>
-      </c>
-      <c r="K538">
-        <v>0.95</v>
-      </c>
-      <c r="L538">
-        <v>0.95</v>
-      </c>
-      <c r="M538">
-        <v>0.95</v>
-      </c>
-      <c r="N538">
-        <v>0.95</v>
-      </c>
-      <c r="O538">
-        <v>0.95</v>
-      </c>
-      <c r="P538">
-        <v>0.95</v>
-      </c>
-      <c r="Q538">
-        <v>0.95</v>
-      </c>
-      <c r="R538">
-        <v>0.95</v>
-      </c>
-      <c r="S538">
-        <v>0.95</v>
-      </c>
-      <c r="T538">
-        <v>0.95</v>
-      </c>
-      <c r="U538">
-        <v>0.95</v>
-      </c>
-      <c r="V538">
-        <v>0.95</v>
-      </c>
-      <c r="W538">
-        <v>0.95</v>
-      </c>
-      <c r="X538">
-        <v>0.95</v>
-      </c>
-      <c r="Y538">
-        <v>0.95</v>
-      </c>
-      <c r="Z538">
-        <v>0.95</v>
-      </c>
-      <c r="AA538">
-        <v>0.95</v>
-      </c>
-      <c r="AB538">
-        <v>0.95</v>
-      </c>
-      <c r="AC538">
-        <v>0.95</v>
-      </c>
-      <c r="AD538">
-        <v>0.95</v>
-      </c>
-      <c r="AE538">
-        <v>0.95</v>
-      </c>
-      <c r="AF538">
-        <v>0.95</v>
-      </c>
-      <c r="AG538">
-        <v>0.95</v>
-      </c>
-      <c r="AH538">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="539" spans="1:34">
-      <c r="A539">
-        <v>2</v>
-      </c>
-      <c r="B539" t="s">
-        <v>762</v>
-      </c>
-      <c r="C539" t="s">
-        <v>937</v>
-      </c>
-      <c r="D539" t="s">
-        <v>968</v>
-      </c>
-      <c r="E539" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F539" t="s">
-        <v>590</v>
-      </c>
-      <c r="G539">
-        <v>0.95</v>
-      </c>
-      <c r="H539">
-        <v>0.95</v>
-      </c>
-      <c r="I539">
-        <v>0.95</v>
-      </c>
-      <c r="J539">
-        <v>0.95</v>
-      </c>
-      <c r="K539">
-        <v>0.95</v>
-      </c>
-      <c r="L539">
-        <v>0.95</v>
-      </c>
-      <c r="M539">
-        <v>0.95</v>
-      </c>
-      <c r="N539">
-        <v>0.95</v>
-      </c>
-      <c r="O539">
-        <v>0.95</v>
-      </c>
-      <c r="P539">
-        <v>0.95</v>
-      </c>
-      <c r="Q539">
-        <v>0.95</v>
-      </c>
-      <c r="R539">
-        <v>0.95</v>
-      </c>
-      <c r="S539">
-        <v>0.95</v>
-      </c>
-      <c r="T539">
-        <v>0.95</v>
-      </c>
-      <c r="U539">
-        <v>0.95</v>
-      </c>
-      <c r="V539">
-        <v>0.95</v>
-      </c>
-      <c r="W539">
-        <v>0.95</v>
-      </c>
-      <c r="X539">
-        <v>0.95</v>
-      </c>
-      <c r="Y539">
-        <v>0.95</v>
-      </c>
-      <c r="Z539">
-        <v>0.95</v>
-      </c>
-      <c r="AA539">
-        <v>0.95</v>
-      </c>
-      <c r="AB539">
-        <v>0.95</v>
-      </c>
-      <c r="AC539">
-        <v>0.95</v>
-      </c>
-      <c r="AD539">
-        <v>0.95</v>
-      </c>
-      <c r="AE539">
-        <v>0.95</v>
-      </c>
-      <c r="AF539">
-        <v>0.95</v>
-      </c>
-      <c r="AG539">
-        <v>0.95</v>
-      </c>
-      <c r="AH539">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="540" spans="1:34">
-      <c r="A540">
-        <v>1</v>
-      </c>
-      <c r="B540" t="s">
-        <v>763</v>
-      </c>
-      <c r="C540" t="s">
-        <v>938</v>
-      </c>
-      <c r="D540" t="s">
-        <v>967</v>
-      </c>
-      <c r="E540" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F540" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G540">
-        <v>1</v>
-      </c>
-      <c r="H540">
-        <v>1</v>
-      </c>
-      <c r="I540">
-        <v>1</v>
-      </c>
-      <c r="J540">
-        <v>1</v>
-      </c>
-      <c r="K540">
-        <v>1</v>
-      </c>
-      <c r="L540">
-        <v>1</v>
-      </c>
-      <c r="M540">
-        <v>1</v>
-      </c>
-      <c r="N540">
-        <v>1</v>
-      </c>
-      <c r="O540">
-        <v>1</v>
-      </c>
-      <c r="P540">
-        <v>1</v>
-      </c>
-      <c r="Q540">
-        <v>1</v>
-      </c>
-      <c r="R540">
-        <v>1</v>
-      </c>
-      <c r="S540">
-        <v>1</v>
-      </c>
-      <c r="T540">
-        <v>1</v>
-      </c>
-      <c r="U540">
-        <v>1</v>
-      </c>
-      <c r="V540">
-        <v>1</v>
-      </c>
-      <c r="W540">
-        <v>1</v>
-      </c>
-      <c r="X540">
-        <v>1</v>
-      </c>
-      <c r="Y540">
-        <v>1</v>
-      </c>
-      <c r="Z540">
-        <v>1</v>
-      </c>
-      <c r="AA540">
-        <v>1</v>
-      </c>
-      <c r="AB540">
-        <v>1</v>
-      </c>
-      <c r="AC540">
-        <v>1</v>
-      </c>
-      <c r="AD540">
-        <v>1</v>
-      </c>
-      <c r="AE540">
-        <v>1</v>
-      </c>
-      <c r="AF540">
-        <v>1</v>
-      </c>
-      <c r="AG540">
-        <v>1</v>
-      </c>
-      <c r="AH540">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="541" spans="1:34">
-      <c r="A541">
-        <v>2</v>
-      </c>
-      <c r="B541" t="s">
-        <v>763</v>
-      </c>
-      <c r="C541" t="s">
-        <v>938</v>
-      </c>
-      <c r="D541" t="s">
-        <v>965</v>
-      </c>
-      <c r="E541" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F541" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G541">
-        <v>1</v>
-      </c>
-      <c r="H541">
-        <v>1</v>
-      </c>
-      <c r="I541">
-        <v>1</v>
-      </c>
-      <c r="J541">
-        <v>1</v>
-      </c>
-      <c r="K541">
-        <v>1</v>
-      </c>
-      <c r="L541">
-        <v>1</v>
-      </c>
-      <c r="M541">
-        <v>1</v>
-      </c>
-      <c r="N541">
-        <v>1</v>
-      </c>
-      <c r="O541">
-        <v>1</v>
-      </c>
-      <c r="P541">
-        <v>1</v>
-      </c>
-      <c r="Q541">
-        <v>1</v>
-      </c>
-      <c r="R541">
-        <v>1</v>
-      </c>
-      <c r="S541">
-        <v>1</v>
-      </c>
-      <c r="T541">
-        <v>1</v>
-      </c>
-      <c r="U541">
-        <v>1</v>
-      </c>
-      <c r="V541">
-        <v>1</v>
-      </c>
-      <c r="W541">
-        <v>1</v>
-      </c>
-      <c r="X541">
-        <v>1</v>
-      </c>
-      <c r="Y541">
-        <v>1</v>
-      </c>
-      <c r="Z541">
-        <v>1</v>
-      </c>
-      <c r="AA541">
-        <v>1</v>
-      </c>
-      <c r="AB541">
-        <v>1</v>
-      </c>
-      <c r="AC541">
-        <v>1</v>
-      </c>
-      <c r="AD541">
-        <v>1</v>
-      </c>
-      <c r="AE541">
-        <v>1</v>
-      </c>
-      <c r="AF541">
-        <v>1</v>
-      </c>
-      <c r="AG541">
-        <v>1</v>
-      </c>
-      <c r="AH541">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="542" spans="1:34">
-      <c r="A542">
-        <v>1</v>
-      </c>
-      <c r="B542" t="s">
-        <v>763</v>
-      </c>
-      <c r="C542" t="s">
-        <v>938</v>
-      </c>
-      <c r="D542" t="s">
-        <v>966</v>
-      </c>
-      <c r="E542" t="s">
-        <v>1006</v>
-      </c>
-      <c r="F542" t="s">
-        <v>590</v>
-      </c>
-      <c r="G542">
-        <v>0.95</v>
-      </c>
-      <c r="H542">
-        <v>0.95</v>
-      </c>
-      <c r="I542">
-        <v>0.95</v>
-      </c>
-      <c r="J542">
-        <v>0.95</v>
-      </c>
-      <c r="K542">
-        <v>0.95</v>
-      </c>
-      <c r="L542">
-        <v>0.95</v>
-      </c>
-      <c r="M542">
-        <v>0.95</v>
-      </c>
-      <c r="N542">
-        <v>0.95</v>
-      </c>
-      <c r="O542">
-        <v>0.95</v>
-      </c>
-      <c r="P542">
-        <v>0.95</v>
-      </c>
-      <c r="Q542">
-        <v>0.95</v>
-      </c>
-      <c r="R542">
-        <v>0.95</v>
-      </c>
-      <c r="S542">
-        <v>0.95</v>
-      </c>
-      <c r="T542">
-        <v>0.95</v>
-      </c>
-      <c r="U542">
-        <v>0.95</v>
-      </c>
-      <c r="V542">
-        <v>0.95</v>
-      </c>
-      <c r="W542">
-        <v>0.95</v>
-      </c>
-      <c r="X542">
-        <v>0.95</v>
-      </c>
-      <c r="Y542">
-        <v>0.95</v>
-      </c>
-      <c r="Z542">
-        <v>0.95</v>
-      </c>
-      <c r="AA542">
-        <v>0.95</v>
-      </c>
-      <c r="AB542">
-        <v>0.95</v>
-      </c>
-      <c r="AC542">
-        <v>0.95</v>
-      </c>
-      <c r="AD542">
-        <v>0.95</v>
-      </c>
-      <c r="AE542">
-        <v>0.95</v>
-      </c>
-      <c r="AF542">
-        <v>0.95</v>
-      </c>
-      <c r="AG542">
-        <v>0.95</v>
-      </c>
-      <c r="AH542">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="543" spans="1:34">
-      <c r="A543">
-        <v>2</v>
-      </c>
-      <c r="B543" t="s">
-        <v>763</v>
-      </c>
-      <c r="C543" t="s">
-        <v>938</v>
-      </c>
-      <c r="D543" t="s">
-        <v>968</v>
-      </c>
-      <c r="E543" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F543" t="s">
-        <v>590</v>
-      </c>
-      <c r="G543">
-        <v>0.95</v>
-      </c>
-      <c r="H543">
-        <v>0.95</v>
-      </c>
-      <c r="I543">
-        <v>0.95</v>
-      </c>
-      <c r="J543">
-        <v>0.95</v>
-      </c>
-      <c r="K543">
-        <v>0.95</v>
-      </c>
-      <c r="L543">
-        <v>0.95</v>
-      </c>
-      <c r="M543">
-        <v>0.95</v>
-      </c>
-      <c r="N543">
-        <v>0.95</v>
-      </c>
-      <c r="O543">
-        <v>0.95</v>
-      </c>
-      <c r="P543">
-        <v>0.95</v>
-      </c>
-      <c r="Q543">
-        <v>0.95</v>
-      </c>
-      <c r="R543">
-        <v>0.95</v>
-      </c>
-      <c r="S543">
-        <v>0.95</v>
-      </c>
-      <c r="T543">
-        <v>0.95</v>
-      </c>
-      <c r="U543">
-        <v>0.95</v>
-      </c>
-      <c r="V543">
-        <v>0.95</v>
-      </c>
-      <c r="W543">
-        <v>0.95</v>
-      </c>
-      <c r="X543">
-        <v>0.95</v>
-      </c>
-      <c r="Y543">
-        <v>0.95</v>
-      </c>
-      <c r="Z543">
-        <v>0.95</v>
-      </c>
-      <c r="AA543">
-        <v>0.95</v>
-      </c>
-      <c r="AB543">
-        <v>0.95</v>
-      </c>
-      <c r="AC543">
-        <v>0.95</v>
-      </c>
-      <c r="AD543">
-        <v>0.95</v>
-      </c>
-      <c r="AE543">
-        <v>0.95</v>
-      </c>
-      <c r="AF543">
-        <v>0.95</v>
-      </c>
-      <c r="AG543">
-        <v>0.95</v>
-      </c>
-      <c r="AH543">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="544" spans="1:34">
-      <c r="A544">
-        <v>1</v>
-      </c>
-      <c r="B544" t="s">
-        <v>764</v>
-      </c>
-      <c r="C544" t="s">
-        <v>939</v>
-      </c>
-      <c r="D544" t="s">
-        <v>979</v>
-      </c>
-      <c r="E544" t="s">
-        <v>1019</v>
-      </c>
-      <c r="F544" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G544">
-        <v>1</v>
-      </c>
-      <c r="H544">
-        <v>1</v>
-      </c>
-      <c r="I544">
-        <v>1</v>
-      </c>
-      <c r="J544">
-        <v>1</v>
-      </c>
-      <c r="K544">
-        <v>1</v>
-      </c>
-      <c r="L544">
-        <v>1</v>
-      </c>
-      <c r="M544">
-        <v>1</v>
-      </c>
-      <c r="N544">
-        <v>1</v>
-      </c>
-      <c r="O544">
-        <v>1</v>
-      </c>
-      <c r="P544">
-        <v>1</v>
-      </c>
-      <c r="Q544">
-        <v>1</v>
-      </c>
-      <c r="R544">
-        <v>1</v>
-      </c>
-      <c r="S544">
-        <v>1</v>
-      </c>
-      <c r="T544">
-        <v>1</v>
-      </c>
-      <c r="U544">
-        <v>1</v>
-      </c>
-      <c r="V544">
-        <v>1</v>
-      </c>
-      <c r="W544">
-        <v>1</v>
-      </c>
-      <c r="X544">
-        <v>1</v>
-      </c>
-      <c r="Y544">
-        <v>1</v>
-      </c>
-      <c r="Z544">
-        <v>1</v>
-      </c>
-      <c r="AA544">
-        <v>1</v>
-      </c>
-      <c r="AB544">
-        <v>1</v>
-      </c>
-      <c r="AC544">
-        <v>1</v>
-      </c>
-      <c r="AD544">
-        <v>1</v>
-      </c>
-      <c r="AE544">
-        <v>1</v>
-      </c>
-      <c r="AF544">
-        <v>1</v>
-      </c>
-      <c r="AG544">
-        <v>1</v>
-      </c>
-      <c r="AH544">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="545" spans="1:34">
-      <c r="A545">
-        <v>2</v>
-      </c>
-      <c r="B545" t="s">
-        <v>764</v>
-      </c>
-      <c r="C545" t="s">
-        <v>939</v>
-      </c>
-      <c r="D545" t="s">
-        <v>971</v>
-      </c>
-      <c r="E545" t="s">
-        <v>1011</v>
-      </c>
-      <c r="F545" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G545">
-        <v>1</v>
-      </c>
-      <c r="H545">
-        <v>1</v>
-      </c>
-      <c r="I545">
-        <v>1</v>
-      </c>
-      <c r="J545">
-        <v>1</v>
-      </c>
-      <c r="K545">
-        <v>1</v>
-      </c>
-      <c r="L545">
-        <v>1</v>
-      </c>
-      <c r="M545">
-        <v>1</v>
-      </c>
-      <c r="N545">
-        <v>1</v>
-      </c>
-      <c r="O545">
-        <v>1</v>
-      </c>
-      <c r="P545">
-        <v>1</v>
-      </c>
-      <c r="Q545">
-        <v>1</v>
-      </c>
-      <c r="R545">
-        <v>1</v>
-      </c>
-      <c r="S545">
-        <v>1</v>
-      </c>
-      <c r="T545">
-        <v>1</v>
-      </c>
-      <c r="U545">
-        <v>1</v>
-      </c>
-      <c r="V545">
-        <v>1</v>
-      </c>
-      <c r="W545">
-        <v>1</v>
-      </c>
-      <c r="X545">
-        <v>1</v>
-      </c>
-      <c r="Y545">
-        <v>1</v>
-      </c>
-      <c r="Z545">
-        <v>1</v>
-      </c>
-      <c r="AA545">
-        <v>1</v>
-      </c>
-      <c r="AB545">
-        <v>1</v>
-      </c>
-      <c r="AC545">
-        <v>1</v>
-      </c>
-      <c r="AD545">
-        <v>1</v>
-      </c>
-      <c r="AE545">
-        <v>1</v>
-      </c>
-      <c r="AF545">
-        <v>1</v>
-      </c>
-      <c r="AG545">
-        <v>1</v>
-      </c>
-      <c r="AH545">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="546" spans="1:34">
-      <c r="A546">
-        <v>1</v>
-      </c>
-      <c r="B546" t="s">
-        <v>764</v>
-      </c>
-      <c r="C546" t="s">
-        <v>939</v>
-      </c>
-      <c r="D546" t="s">
-        <v>972</v>
-      </c>
-      <c r="E546" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F546" t="s">
-        <v>590</v>
-      </c>
-      <c r="G546">
-        <v>0.95</v>
-      </c>
-      <c r="H546">
-        <v>0.95</v>
-      </c>
-      <c r="I546">
-        <v>0.95</v>
-      </c>
-      <c r="J546">
-        <v>0.95</v>
-      </c>
-      <c r="K546">
-        <v>0.95</v>
-      </c>
-      <c r="L546">
-        <v>0.95</v>
-      </c>
-      <c r="M546">
-        <v>0.95</v>
-      </c>
-      <c r="N546">
-        <v>0.95</v>
-      </c>
-      <c r="O546">
-        <v>0.95</v>
-      </c>
-      <c r="P546">
-        <v>0.95</v>
-      </c>
-      <c r="Q546">
-        <v>0.95</v>
-      </c>
-      <c r="R546">
-        <v>0.95</v>
-      </c>
-      <c r="S546">
-        <v>0.95</v>
-      </c>
-      <c r="T546">
-        <v>0.95</v>
-      </c>
-      <c r="U546">
-        <v>0.95</v>
-      </c>
-      <c r="V546">
-        <v>0.95</v>
-      </c>
-      <c r="W546">
-        <v>0.95</v>
-      </c>
-      <c r="X546">
-        <v>0.95</v>
-      </c>
-      <c r="Y546">
-        <v>0.95</v>
-      </c>
-      <c r="Z546">
-        <v>0.95</v>
-      </c>
-      <c r="AA546">
-        <v>0.95</v>
-      </c>
-      <c r="AB546">
-        <v>0.95</v>
-      </c>
-      <c r="AC546">
-        <v>0.95</v>
-      </c>
-      <c r="AD546">
-        <v>0.95</v>
-      </c>
-      <c r="AE546">
-        <v>0.95</v>
-      </c>
-      <c r="AF546">
-        <v>0.95</v>
-      </c>
-      <c r="AG546">
-        <v>0.95</v>
-      </c>
-      <c r="AH546">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="547" spans="1:34">
-      <c r="A547">
-        <v>2</v>
-      </c>
-      <c r="B547" t="s">
-        <v>764</v>
-      </c>
-      <c r="C547" t="s">
-        <v>939</v>
-      </c>
-      <c r="D547" t="s">
-        <v>980</v>
-      </c>
-      <c r="E547" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F547" t="s">
-        <v>590</v>
-      </c>
-      <c r="G547">
-        <v>0.95</v>
-      </c>
-      <c r="H547">
-        <v>0.95</v>
-      </c>
-      <c r="I547">
-        <v>0.95</v>
-      </c>
-      <c r="J547">
-        <v>0.95</v>
-      </c>
-      <c r="K547">
-        <v>0.95</v>
-      </c>
-      <c r="L547">
-        <v>0.95</v>
-      </c>
-      <c r="M547">
-        <v>0.95</v>
-      </c>
-      <c r="N547">
-        <v>0.95</v>
-      </c>
-      <c r="O547">
-        <v>0.95</v>
-      </c>
-      <c r="P547">
-        <v>0.95</v>
-      </c>
-      <c r="Q547">
-        <v>0.95</v>
-      </c>
-      <c r="R547">
-        <v>0.95</v>
-      </c>
-      <c r="S547">
-        <v>0.95</v>
-      </c>
-      <c r="T547">
-        <v>0.95</v>
-      </c>
-      <c r="U547">
-        <v>0.95</v>
-      </c>
-      <c r="V547">
-        <v>0.95</v>
-      </c>
-      <c r="W547">
-        <v>0.95</v>
-      </c>
-      <c r="X547">
-        <v>0.95</v>
-      </c>
-      <c r="Y547">
-        <v>0.95</v>
-      </c>
-      <c r="Z547">
-        <v>0.95</v>
-      </c>
-      <c r="AA547">
-        <v>0.95</v>
-      </c>
-      <c r="AB547">
-        <v>0.95</v>
-      </c>
-      <c r="AC547">
-        <v>0.95</v>
-      </c>
-      <c r="AD547">
-        <v>0.95</v>
-      </c>
-      <c r="AE547">
-        <v>0.95</v>
-      </c>
-      <c r="AF547">
-        <v>0.95</v>
-      </c>
-      <c r="AG547">
-        <v>0.95</v>
-      </c>
-      <c r="AH547">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="548" spans="1:34">
-      <c r="A548">
-        <v>1</v>
-      </c>
-      <c r="B548" t="s">
-        <v>765</v>
-      </c>
-      <c r="C548" t="s">
-        <v>940</v>
-      </c>
-      <c r="D548" t="s">
-        <v>975</v>
-      </c>
-      <c r="E548" t="s">
-        <v>1015</v>
-      </c>
-      <c r="F548" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G548">
-        <v>1</v>
-      </c>
-      <c r="H548">
-        <v>1</v>
-      </c>
-      <c r="I548">
-        <v>1</v>
-      </c>
-      <c r="J548">
-        <v>1</v>
-      </c>
-      <c r="K548">
-        <v>1</v>
-      </c>
-      <c r="L548">
-        <v>1</v>
-      </c>
-      <c r="M548">
-        <v>1</v>
-      </c>
-      <c r="N548">
-        <v>1</v>
-      </c>
-      <c r="O548">
-        <v>1</v>
-      </c>
-      <c r="P548">
-        <v>1</v>
-      </c>
-      <c r="Q548">
-        <v>1</v>
-      </c>
-      <c r="R548">
-        <v>1</v>
-      </c>
-      <c r="S548">
-        <v>1</v>
-      </c>
-      <c r="T548">
-        <v>1</v>
-      </c>
-      <c r="U548">
-        <v>1</v>
-      </c>
-      <c r="V548">
-        <v>1</v>
-      </c>
-      <c r="W548">
-        <v>1</v>
-      </c>
-      <c r="X548">
-        <v>1</v>
-      </c>
-      <c r="Y548">
-        <v>1</v>
-      </c>
-      <c r="Z548">
-        <v>1</v>
-      </c>
-      <c r="AA548">
-        <v>1</v>
-      </c>
-      <c r="AB548">
-        <v>1</v>
-      </c>
-      <c r="AC548">
-        <v>1</v>
-      </c>
-      <c r="AD548">
-        <v>1</v>
-      </c>
-      <c r="AE548">
-        <v>1</v>
-      </c>
-      <c r="AF548">
-        <v>1</v>
-      </c>
-      <c r="AG548">
-        <v>1</v>
-      </c>
-      <c r="AH548">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="549" spans="1:34">
-      <c r="A549">
-        <v>2</v>
-      </c>
-      <c r="B549" t="s">
-        <v>765</v>
-      </c>
-      <c r="C549" t="s">
-        <v>940</v>
-      </c>
-      <c r="D549" t="s">
-        <v>961</v>
-      </c>
-      <c r="E549" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F549" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G549">
-        <v>1</v>
-      </c>
-      <c r="H549">
-        <v>1</v>
-      </c>
-      <c r="I549">
-        <v>1</v>
-      </c>
-      <c r="J549">
-        <v>1</v>
-      </c>
-      <c r="K549">
-        <v>1</v>
-      </c>
-      <c r="L549">
-        <v>1</v>
-      </c>
-      <c r="M549">
-        <v>1</v>
-      </c>
-      <c r="N549">
-        <v>1</v>
-      </c>
-      <c r="O549">
-        <v>1</v>
-      </c>
-      <c r="P549">
-        <v>1</v>
-      </c>
-      <c r="Q549">
-        <v>1</v>
-      </c>
-      <c r="R549">
-        <v>1</v>
-      </c>
-      <c r="S549">
-        <v>1</v>
-      </c>
-      <c r="T549">
-        <v>1</v>
-      </c>
-      <c r="U549">
-        <v>1</v>
-      </c>
-      <c r="V549">
-        <v>1</v>
-      </c>
-      <c r="W549">
-        <v>1</v>
-      </c>
-      <c r="X549">
-        <v>1</v>
-      </c>
-      <c r="Y549">
-        <v>1</v>
-      </c>
-      <c r="Z549">
-        <v>1</v>
-      </c>
-      <c r="AA549">
-        <v>1</v>
-      </c>
-      <c r="AB549">
-        <v>1</v>
-      </c>
-      <c r="AC549">
-        <v>1</v>
-      </c>
-      <c r="AD549">
-        <v>1</v>
-      </c>
-      <c r="AE549">
-        <v>1</v>
-      </c>
-      <c r="AF549">
-        <v>1</v>
-      </c>
-      <c r="AG549">
-        <v>1</v>
-      </c>
-      <c r="AH549">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="550" spans="1:34">
-      <c r="A550">
-        <v>1</v>
-      </c>
-      <c r="B550" t="s">
-        <v>765</v>
-      </c>
-      <c r="C550" t="s">
-        <v>940</v>
-      </c>
-      <c r="D550" t="s">
-        <v>964</v>
-      </c>
-      <c r="E550" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F550" t="s">
-        <v>590</v>
-      </c>
-      <c r="G550">
-        <v>0.95</v>
-      </c>
-      <c r="H550">
-        <v>0.95</v>
-      </c>
-      <c r="I550">
-        <v>0.95</v>
-      </c>
-      <c r="J550">
-        <v>0.95</v>
-      </c>
-      <c r="K550">
-        <v>0.95</v>
-      </c>
-      <c r="L550">
-        <v>0.95</v>
-      </c>
-      <c r="M550">
-        <v>0.95</v>
-      </c>
-      <c r="N550">
-        <v>0.95</v>
-      </c>
-      <c r="O550">
-        <v>0.95</v>
-      </c>
-      <c r="P550">
-        <v>0.95</v>
-      </c>
-      <c r="Q550">
-        <v>0.95</v>
-      </c>
-      <c r="R550">
-        <v>0.95</v>
-      </c>
-      <c r="S550">
-        <v>0.95</v>
-      </c>
-      <c r="T550">
-        <v>0.95</v>
-      </c>
-      <c r="U550">
-        <v>0.95</v>
-      </c>
-      <c r="V550">
-        <v>0.95</v>
-      </c>
-      <c r="W550">
-        <v>0.95</v>
-      </c>
-      <c r="X550">
-        <v>0.95</v>
-      </c>
-      <c r="Y550">
-        <v>0.95</v>
-      </c>
-      <c r="Z550">
-        <v>0.95</v>
-      </c>
-      <c r="AA550">
-        <v>0.95</v>
-      </c>
-      <c r="AB550">
-        <v>0.95</v>
-      </c>
-      <c r="AC550">
-        <v>0.95</v>
-      </c>
-      <c r="AD550">
-        <v>0.95</v>
-      </c>
-      <c r="AE550">
-        <v>0.95</v>
-      </c>
-      <c r="AF550">
-        <v>0.95</v>
-      </c>
-      <c r="AG550">
-        <v>0.95</v>
-      </c>
-      <c r="AH550">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="551" spans="1:34">
-      <c r="A551">
-        <v>2</v>
-      </c>
-      <c r="B551" t="s">
-        <v>765</v>
-      </c>
-      <c r="C551" t="s">
-        <v>940</v>
-      </c>
-      <c r="D551" t="s">
-        <v>976</v>
-      </c>
-      <c r="E551" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F551" t="s">
-        <v>590</v>
-      </c>
-      <c r="G551">
-        <v>0.95</v>
-      </c>
-      <c r="H551">
-        <v>0.95</v>
-      </c>
-      <c r="I551">
-        <v>0.95</v>
-      </c>
-      <c r="J551">
-        <v>0.95</v>
-      </c>
-      <c r="K551">
-        <v>0.95</v>
-      </c>
-      <c r="L551">
-        <v>0.95</v>
-      </c>
-      <c r="M551">
-        <v>0.95</v>
-      </c>
-      <c r="N551">
-        <v>0.95</v>
-      </c>
-      <c r="O551">
-        <v>0.95</v>
-      </c>
-      <c r="P551">
-        <v>0.95</v>
-      </c>
-      <c r="Q551">
-        <v>0.95</v>
-      </c>
-      <c r="R551">
-        <v>0.95</v>
-      </c>
-      <c r="S551">
-        <v>0.95</v>
-      </c>
-      <c r="T551">
-        <v>0.95</v>
-      </c>
-      <c r="U551">
-        <v>0.95</v>
-      </c>
-      <c r="V551">
-        <v>0.95</v>
-      </c>
-      <c r="W551">
-        <v>0.95</v>
-      </c>
-      <c r="X551">
-        <v>0.95</v>
-      </c>
-      <c r="Y551">
-        <v>0.95</v>
-      </c>
-      <c r="Z551">
-        <v>0.95</v>
-      </c>
-      <c r="AA551">
-        <v>0.95</v>
-      </c>
-      <c r="AB551">
-        <v>0.95</v>
-      </c>
-      <c r="AC551">
-        <v>0.95</v>
-      </c>
-      <c r="AD551">
-        <v>0.95</v>
-      </c>
-      <c r="AE551">
-        <v>0.95</v>
-      </c>
-      <c r="AF551">
-        <v>0.95</v>
-      </c>
-      <c r="AG551">
-        <v>0.95</v>
-      </c>
-      <c r="AH551">
         <v>0.95</v>
       </c>
     </row>
